--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -3537,7 +3537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3964,7 +3964,7 @@
         <v>123777</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0.54</v>
@@ -4025,10 +4025,10 @@
         <v>5320102</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>-9.109999999999999</v>
@@ -4086,10 +4086,10 @@
         <v>1012950</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>-6.61</v>
@@ -4391,7 +4391,7 @@
         <v>15850096</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>2.91</v>
@@ -4452,7 +4452,7 @@
         <v>920577</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>1.72</v>
@@ -4574,10 +4574,10 @@
         <v>1635814</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>-13.08</v>
@@ -4818,7 +4818,7 @@
         <v>64752764</v>
       </c>
       <c r="I21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>6.02</v>
@@ -5123,13 +5123,13 @@
         <v>701478</v>
       </c>
       <c r="I26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>2.26</v>
       </c>
       <c r="K26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -5550,7 +5550,7 @@
         <v>4413099</v>
       </c>
       <c r="I33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0.29</v>
@@ -5611,7 +5611,7 @@
         <v>2752879</v>
       </c>
       <c r="I34" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0.14</v>
@@ -5672,7 +5672,7 @@
         <v>6237475</v>
       </c>
       <c r="I35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>5.12</v>
@@ -5916,10 +5916,10 @@
         <v>4677978</v>
       </c>
       <c r="I39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>-9</v>
@@ -5977,10 +5977,10 @@
         <v>3334268</v>
       </c>
       <c r="I40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>-11.08</v>
@@ -6062,6 +6062,2446 @@
         <v>0</v>
       </c>
       <c r="Q41" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SETL.NS</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>296.5499877929688</v>
+      </c>
+      <c r="F42" t="n">
+        <v>296.5499877929688</v>
+      </c>
+      <c r="G42" t="n">
+        <v>287</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2530585</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="J42" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-24.25</v>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" t="b">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>VIPULLTD.NS</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>15.46000003814697</v>
+      </c>
+      <c r="F43" t="n">
+        <v>15.55000019073486</v>
+      </c>
+      <c r="G43" t="n">
+        <v>14.85999965667725</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1970909</v>
+      </c>
+      <c r="I43" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-12.36</v>
+      </c>
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" t="b">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CGCL.NS</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>227.7599945068359</v>
+      </c>
+      <c r="F44" t="n">
+        <v>228.9799957275391</v>
+      </c>
+      <c r="G44" t="n">
+        <v>224.8099975585938</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1900945</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="L44" t="b">
+        <v>0</v>
+      </c>
+      <c r="M44" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44" t="b">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MANBA.NS</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>138.3000030517578</v>
+      </c>
+      <c r="F45" t="n">
+        <v>142.9100036621094</v>
+      </c>
+      <c r="G45" t="n">
+        <v>138</v>
+      </c>
+      <c r="H45" t="n">
+        <v>235383</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" t="b">
+        <v>0</v>
+      </c>
+      <c r="N45" t="b">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>IRISDOREME.NS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>42.84999847412109</v>
+      </c>
+      <c r="F46" t="n">
+        <v>45.43999862670898</v>
+      </c>
+      <c r="G46" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>389940</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-3.34</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-11.03</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="b">
+        <v>0</v>
+      </c>
+      <c r="N46" t="b">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MANCREDIT.NS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>236.2899932861328</v>
+      </c>
+      <c r="F47" t="n">
+        <v>255.5299987792969</v>
+      </c>
+      <c r="G47" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1162933</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" t="b">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NACLIND.NS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>214.7200012207031</v>
+      </c>
+      <c r="F48" t="n">
+        <v>221.5099945068359</v>
+      </c>
+      <c r="G48" t="n">
+        <v>211.9900054931641</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1095905</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48" t="b">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>36</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GODREJPROP.NS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1968.699951171875</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1983.400024414062</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1946.599975585938</v>
+      </c>
+      <c r="H49" t="n">
+        <v>572960</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49" t="b">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>17</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AVG.NS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>209.0399932861328</v>
+      </c>
+      <c r="F50" t="n">
+        <v>210.3800048828125</v>
+      </c>
+      <c r="G50" t="n">
+        <v>202</v>
+      </c>
+      <c r="H50" t="n">
+        <v>119344</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-12.94</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" t="b">
+        <v>0</v>
+      </c>
+      <c r="N50" t="b">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>IOLCP.NS</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>150.3099975585938</v>
+      </c>
+      <c r="F51" t="n">
+        <v>151.1999969482422</v>
+      </c>
+      <c r="G51" t="n">
+        <v>143.0099945068359</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4070870</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="b">
+        <v>0</v>
+      </c>
+      <c r="N51" t="b">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>DELHIVERY.NS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>509.2999877929688</v>
+      </c>
+      <c r="F52" t="n">
+        <v>513.4000244140625</v>
+      </c>
+      <c r="G52" t="n">
+        <v>500.2000122070312</v>
+      </c>
+      <c r="H52" t="n">
+        <v>12862487</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" t="b">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AURUM.NS</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>227.8300018310547</v>
+      </c>
+      <c r="F53" t="n">
+        <v>232.8999938964844</v>
+      </c>
+      <c r="G53" t="n">
+        <v>226</v>
+      </c>
+      <c r="H53" t="n">
+        <v>168395</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MAHABANK.NS</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>91.04000091552734</v>
+      </c>
+      <c r="F54" t="n">
+        <v>91.88999938964844</v>
+      </c>
+      <c r="G54" t="n">
+        <v>90.59999847412109</v>
+      </c>
+      <c r="H54" t="n">
+        <v>9478200</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="J54" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" t="b">
+        <v>0</v>
+      </c>
+      <c r="N54" t="b">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>14</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AEROENTER.NS</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>136.6600036621094</v>
+      </c>
+      <c r="F55" t="n">
+        <v>143.8999938964844</v>
+      </c>
+      <c r="G55" t="n">
+        <v>135.1799926757812</v>
+      </c>
+      <c r="H55" t="n">
+        <v>873201</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-2.31</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="b">
+        <v>0</v>
+      </c>
+      <c r="N55" t="b">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>31</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MOREPENLAB.NS</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>59.79000091552734</v>
+      </c>
+      <c r="F56" t="n">
+        <v>62.38999938964844</v>
+      </c>
+      <c r="G56" t="n">
+        <v>59.27000045776367</v>
+      </c>
+      <c r="H56" t="n">
+        <v>14236617</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-4.61</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-15.19</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" t="b">
+        <v>0</v>
+      </c>
+      <c r="N56" t="b">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>WEWORK.NS</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>742.1500244140625</v>
+      </c>
+      <c r="F57" t="n">
+        <v>749.2999877929688</v>
+      </c>
+      <c r="G57" t="n">
+        <v>716.7000122070312</v>
+      </c>
+      <c r="H57" t="n">
+        <v>379252</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="J57" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-13.08</v>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57" t="b">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AEQUS.NS</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>230.4400024414062</v>
+      </c>
+      <c r="F58" t="n">
+        <v>240.5700073242188</v>
+      </c>
+      <c r="G58" t="n">
+        <v>228.3999938964844</v>
+      </c>
+      <c r="H58" t="n">
+        <v>6725563</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-3.75</v>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" t="b">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>UTKARSHBNK.NS</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>15.14000034332275</v>
+      </c>
+      <c r="F59" t="n">
+        <v>16.20000076293945</v>
+      </c>
+      <c r="G59" t="n">
+        <v>14.89999961853027</v>
+      </c>
+      <c r="H59" t="n">
+        <v>38635427</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="L59" t="b">
+        <v>0</v>
+      </c>
+      <c r="M59" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59" t="b">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SATIN.NS</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>259.6799926757812</v>
+      </c>
+      <c r="F60" t="n">
+        <v>261</v>
+      </c>
+      <c r="G60" t="n">
+        <v>252.8800048828125</v>
+      </c>
+      <c r="H60" t="n">
+        <v>955163</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-6.26</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" t="b">
+        <v>0</v>
+      </c>
+      <c r="N60" t="b">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SAKSOFT.NS</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>179.8600006103516</v>
+      </c>
+      <c r="F61" t="n">
+        <v>189.9499969482422</v>
+      </c>
+      <c r="G61" t="n">
+        <v>175.4900054931641</v>
+      </c>
+      <c r="H61" t="n">
+        <v>18019388</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-7.75</v>
+      </c>
+      <c r="J61" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-17.71</v>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" t="b">
+        <v>0</v>
+      </c>
+      <c r="N61" t="b">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>36</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>FUSION.NS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>216.2100067138672</v>
+      </c>
+      <c r="F62" t="n">
+        <v>217.8000030517578</v>
+      </c>
+      <c r="G62" t="n">
+        <v>203</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2507436</v>
+      </c>
+      <c r="I62" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J62" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-8.91</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" t="b">
+        <v>0</v>
+      </c>
+      <c r="N62" t="b">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>TARIL.NS</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>357.25</v>
+      </c>
+      <c r="F63" t="n">
+        <v>364.2000122070312</v>
+      </c>
+      <c r="G63" t="n">
+        <v>353</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3586752</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63" t="b">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EBGNG.NS</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>674.8499755859375</v>
+      </c>
+      <c r="F64" t="n">
+        <v>689.5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>661</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1942014</v>
+      </c>
+      <c r="I64" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-13.85</v>
+      </c>
+      <c r="L64" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" t="b">
+        <v>0</v>
+      </c>
+      <c r="N64" t="b">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BAJFINANCE.NS</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1018.400024414062</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1025.699951171875</v>
+      </c>
+      <c r="G65" t="n">
+        <v>993.4000244140625</v>
+      </c>
+      <c r="H65" t="n">
+        <v>8168258</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-3.99</v>
+      </c>
+      <c r="L65" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" t="b">
+        <v>0</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB.NS</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>206.2200012207031</v>
+      </c>
+      <c r="F66" t="n">
+        <v>207.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>198.0599975585938</v>
+      </c>
+      <c r="H66" t="n">
+        <v>526209</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" t="b">
+        <v>0</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KILITCH.NS</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>196.9900054931641</v>
+      </c>
+      <c r="F67" t="n">
+        <v>207.7700042724609</v>
+      </c>
+      <c r="G67" t="n">
+        <v>194.25</v>
+      </c>
+      <c r="H67" t="n">
+        <v>136445</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-4.15</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-9.83</v>
+      </c>
+      <c r="L67" t="b">
+        <v>0</v>
+      </c>
+      <c r="M67" t="b">
+        <v>0</v>
+      </c>
+      <c r="N67" t="b">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>AVL.NS</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>640.3499755859375</v>
+      </c>
+      <c r="F68" t="n">
+        <v>654.2999877929688</v>
+      </c>
+      <c r="G68" t="n">
+        <v>633.4000244140625</v>
+      </c>
+      <c r="H68" t="n">
+        <v>273943</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="L68" t="b">
+        <v>0</v>
+      </c>
+      <c r="M68" t="b">
+        <v>0</v>
+      </c>
+      <c r="N68" t="b">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BLUEJET.NS</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>568.2000122070312</v>
+      </c>
+      <c r="F69" t="n">
+        <v>574.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>553.0999755859375</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1218140</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-5.98</v>
+      </c>
+      <c r="L69" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69" t="b">
+        <v>0</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD.NS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2012.5</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2020.099975585938</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1977.199951171875</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1663054</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-5.64</v>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" t="b">
+        <v>0</v>
+      </c>
+      <c r="N70" t="b">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PIRAMALFIN.NS</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2181.300048828125</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2208.699951171875</v>
+      </c>
+      <c r="G71" t="n">
+        <v>2163</v>
+      </c>
+      <c r="H71" t="n">
+        <v>235925</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-3.01</v>
+      </c>
+      <c r="L71" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" t="b">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PRESTIGE.NS</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1674.099975585938</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1682.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1635.699951171875</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1774043</v>
+      </c>
+      <c r="I72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J72" t="n">
+        <v>3</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="L72" t="b">
+        <v>0</v>
+      </c>
+      <c r="M72" t="b">
+        <v>0</v>
+      </c>
+      <c r="N72" t="b">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>IBULLSLTD.NS</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>27.93000030517578</v>
+      </c>
+      <c r="F73" t="n">
+        <v>28.29999923706055</v>
+      </c>
+      <c r="G73" t="n">
+        <v>27.51000022888184</v>
+      </c>
+      <c r="H73" t="n">
+        <v>3853135</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-7.14</v>
+      </c>
+      <c r="L73" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73" t="b">
+        <v>0</v>
+      </c>
+      <c r="N73" t="b">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>20</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>TIRUPATIFL.NS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
+        <v>69.51999664306641</v>
+      </c>
+      <c r="F74" t="n">
+        <v>72.29000091552734</v>
+      </c>
+      <c r="G74" t="n">
+        <v>64.61000061035156</v>
+      </c>
+      <c r="H74" t="n">
+        <v>4918289</v>
+      </c>
+      <c r="I74" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="J74" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-24.41</v>
+      </c>
+      <c r="L74" t="b">
+        <v>1</v>
+      </c>
+      <c r="M74" t="b">
+        <v>0</v>
+      </c>
+      <c r="N74" t="b">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>13</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>T1_HIT_ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>RAMCOSYS.NS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>796.4000244140625</v>
+      </c>
+      <c r="F75" t="n">
+        <v>818.4000244140625</v>
+      </c>
+      <c r="G75" t="n">
+        <v>760.5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>7138769</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-10.75</v>
+      </c>
+      <c r="L75" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75" t="b">
+        <v>0</v>
+      </c>
+      <c r="N75" t="b">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>RML.NS</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1194.400024414062</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1215</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1173.099975585938</v>
+      </c>
+      <c r="H76" t="n">
+        <v>52617</v>
+      </c>
+      <c r="I76" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-6.11</v>
+      </c>
+      <c r="L76" t="b">
+        <v>0</v>
+      </c>
+      <c r="M76" t="b">
+        <v>0</v>
+      </c>
+      <c r="N76" t="b">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>VIYASH.NS</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>292.4500122070312</v>
+      </c>
+      <c r="F77" t="n">
+        <v>297</v>
+      </c>
+      <c r="G77" t="n">
+        <v>286.1499938964844</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3206127</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-6.56</v>
+      </c>
+      <c r="L77" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77" t="b">
+        <v>0</v>
+      </c>
+      <c r="N77" t="b">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>VENUSPIPES.NS</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1782.800048828125</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1812.900024414062</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1770</v>
+      </c>
+      <c r="H78" t="n">
+        <v>105764</v>
+      </c>
+      <c r="I78" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="L78" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78" t="b">
+        <v>0</v>
+      </c>
+      <c r="N78" t="b">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EMIL.NS</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>136.8999938964844</v>
+      </c>
+      <c r="F79" t="n">
+        <v>138</v>
+      </c>
+      <c r="G79" t="n">
+        <v>127.0999984741211</v>
+      </c>
+      <c r="H79" t="n">
+        <v>6392478</v>
+      </c>
+      <c r="I79" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79" t="b">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SGFIN.NS</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="n">
+        <v>661.0999755859375</v>
+      </c>
+      <c r="F80" t="n">
+        <v>684.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>655</v>
+      </c>
+      <c r="H80" t="n">
+        <v>452386</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-11.08</v>
+      </c>
+      <c r="L80" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>LTF.NS</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="n">
+        <v>315.25</v>
+      </c>
+      <c r="F81" t="n">
+        <v>316</v>
+      </c>
+      <c r="G81" t="n">
+        <v>311.25</v>
+      </c>
+      <c r="H81" t="n">
+        <v>4079003</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="L81" t="b">
+        <v>0</v>
+      </c>
+      <c r="M81" t="b">
+        <v>0</v>
+      </c>
+      <c r="N81" t="b">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -6221,7 +8661,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-01 16:04</t>
+          <t>2026-07-02 11:01</t>
         </is>
       </c>
     </row>

--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -16,6 +16,9 @@
     <sheet name="Sector Analysis" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Regime Analysis" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Monthly Report" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Portfolio Risk" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Benchmark" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Equity Curve" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3531,13 +3534,487 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Portfolio-level Risk Snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Open Positions</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Active Runners</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Exposure %</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Avg Return% (open)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Std Return% (open)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Worst Open Return %</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-8.31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VaR-95 (1-day, %)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>46.75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>── Top-5 Positions by symbol ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Days Held</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Return %</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FUSION.NS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>T1_HIT_ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMIL.NS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>T1_HIT_ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AVG.NS</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB.NS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IBULLSLTD.NS</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Strategy vs Benchmark (1Y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Benchmark symbol</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>^NSEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>^NSEI 1Y return %</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-4.47</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Strategy avg return % (closed)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alpha (strategy − benchmark)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>✓ Positive alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:01</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Equity Curve &amp; Risk-Adjusted Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Starting capital (₹)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ending capital (₹)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total P&amp;L (₹)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total P&amp;L %</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Trades counted</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Avg trade return %</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Std trade return %</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sharpe (annualised)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sortino (annualised)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Max drawdown %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Position size % used</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Trade Return %</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P&amp;L (₹)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Equity (₹)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:Q121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6468,7 +6945,7 @@
         <v>-3.45</v>
       </c>
       <c r="J48" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>-9.109999999999999</v>
@@ -7569,7 +8046,7 @@
         <v>2.74</v>
       </c>
       <c r="K66" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
@@ -8502,6 +8979,2446 @@
         <v>1</v>
       </c>
       <c r="Q81" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SETL.NS</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="F82" t="n">
+        <v>305.2999877929688</v>
+      </c>
+      <c r="G82" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="H82" t="n">
+        <v>2098935</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="J82" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-17.36</v>
+      </c>
+      <c r="L82" t="b">
+        <v>0</v>
+      </c>
+      <c r="M82" t="b">
+        <v>0</v>
+      </c>
+      <c r="N82" t="b">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P82" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>VIPULLTD.NS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" t="n">
+        <v>15.34000015258789</v>
+      </c>
+      <c r="F83" t="n">
+        <v>16</v>
+      </c>
+      <c r="G83" t="n">
+        <v>14.6899995803833</v>
+      </c>
+      <c r="H83" t="n">
+        <v>10396639</v>
+      </c>
+      <c r="I83" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="J83" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="L83" t="b">
+        <v>0</v>
+      </c>
+      <c r="M83" t="b">
+        <v>0</v>
+      </c>
+      <c r="N83" t="b">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="P83" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CGCL.NS</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" t="n">
+        <v>233.8699951171875</v>
+      </c>
+      <c r="F84" t="n">
+        <v>235.3399963378906</v>
+      </c>
+      <c r="G84" t="n">
+        <v>226.1999969482422</v>
+      </c>
+      <c r="H84" t="n">
+        <v>3415898</v>
+      </c>
+      <c r="I84" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="J84" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="L84" t="b">
+        <v>0</v>
+      </c>
+      <c r="M84" t="b">
+        <v>0</v>
+      </c>
+      <c r="N84" t="b">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="P84" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MANBA.NS</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" t="n">
+        <v>139.1499938964844</v>
+      </c>
+      <c r="F85" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>137</v>
+      </c>
+      <c r="H85" t="n">
+        <v>128347</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L85" t="b">
+        <v>0</v>
+      </c>
+      <c r="M85" t="b">
+        <v>0</v>
+      </c>
+      <c r="N85" t="b">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="P85" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>IRISDOREME.NS</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2</v>
+      </c>
+      <c r="E86" t="n">
+        <v>42.95999908447266</v>
+      </c>
+      <c r="F86" t="n">
+        <v>44.15000152587891</v>
+      </c>
+      <c r="G86" t="n">
+        <v>42.59999847412109</v>
+      </c>
+      <c r="H86" t="n">
+        <v>420207</v>
+      </c>
+      <c r="I86" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-11.03</v>
+      </c>
+      <c r="L86" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" t="b">
+        <v>0</v>
+      </c>
+      <c r="N86" t="b">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="P86" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MANCREDIT.NS</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" t="n">
+        <v>245.3300018310547</v>
+      </c>
+      <c r="F87" t="n">
+        <v>265</v>
+      </c>
+      <c r="G87" t="n">
+        <v>240.0200042724609</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1173608</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="L87" t="b">
+        <v>0</v>
+      </c>
+      <c r="M87" t="b">
+        <v>0</v>
+      </c>
+      <c r="N87" t="b">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>21</v>
+      </c>
+      <c r="P87" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NACLIND.NS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2</v>
+      </c>
+      <c r="E88" t="n">
+        <v>218.3999938964844</v>
+      </c>
+      <c r="F88" t="n">
+        <v>224.4700012207031</v>
+      </c>
+      <c r="G88" t="n">
+        <v>213.6000061035156</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1919921</v>
+      </c>
+      <c r="I88" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="J88" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="L88" t="b">
+        <v>0</v>
+      </c>
+      <c r="M88" t="b">
+        <v>0</v>
+      </c>
+      <c r="N88" t="b">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="P88" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GODREJPROP.NS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>2</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1996.400024414062</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2002.599975585938</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1970.5</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1001474</v>
+      </c>
+      <c r="I89" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="L89" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" t="b">
+        <v>0</v>
+      </c>
+      <c r="N89" t="b">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="P89" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>AVG.NS</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" t="n">
+        <v>224.2400054931641</v>
+      </c>
+      <c r="F90" t="n">
+        <v>229</v>
+      </c>
+      <c r="G90" t="n">
+        <v>208.7299957275391</v>
+      </c>
+      <c r="H90" t="n">
+        <v>354217</v>
+      </c>
+      <c r="I90" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="J90" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-12.94</v>
+      </c>
+      <c r="L90" t="b">
+        <v>0</v>
+      </c>
+      <c r="M90" t="b">
+        <v>0</v>
+      </c>
+      <c r="N90" t="b">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="P90" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>IOLCP.NS</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" t="n">
+        <v>142.9600067138672</v>
+      </c>
+      <c r="F91" t="n">
+        <v>150.8899993896484</v>
+      </c>
+      <c r="G91" t="n">
+        <v>140.2700042724609</v>
+      </c>
+      <c r="H91" t="n">
+        <v>4336773</v>
+      </c>
+      <c r="I91" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="L91" t="b">
+        <v>0</v>
+      </c>
+      <c r="M91" t="b">
+        <v>0</v>
+      </c>
+      <c r="N91" t="b">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="P91" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>DELHIVERY.NS</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" t="n">
+        <v>507.4500122070312</v>
+      </c>
+      <c r="F92" t="n">
+        <v>515</v>
+      </c>
+      <c r="G92" t="n">
+        <v>502.8500061035156</v>
+      </c>
+      <c r="H92" t="n">
+        <v>8379741</v>
+      </c>
+      <c r="I92" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="L92" t="b">
+        <v>0</v>
+      </c>
+      <c r="M92" t="b">
+        <v>0</v>
+      </c>
+      <c r="N92" t="b">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>18</v>
+      </c>
+      <c r="P92" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>AURUM.NS</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>2</v>
+      </c>
+      <c r="E93" t="n">
+        <v>231.8999938964844</v>
+      </c>
+      <c r="F93" t="n">
+        <v>237</v>
+      </c>
+      <c r="G93" t="n">
+        <v>227.2299957275391</v>
+      </c>
+      <c r="H93" t="n">
+        <v>211926</v>
+      </c>
+      <c r="I93" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L93" t="b">
+        <v>0</v>
+      </c>
+      <c r="M93" t="b">
+        <v>0</v>
+      </c>
+      <c r="N93" t="b">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="P93" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MAHABANK.NS</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>2</v>
+      </c>
+      <c r="E94" t="n">
+        <v>88.52999877929688</v>
+      </c>
+      <c r="F94" t="n">
+        <v>91.48000335693359</v>
+      </c>
+      <c r="G94" t="n">
+        <v>88.18000030517578</v>
+      </c>
+      <c r="H94" t="n">
+        <v>16120019</v>
+      </c>
+      <c r="I94" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="J94" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="L94" t="b">
+        <v>0</v>
+      </c>
+      <c r="M94" t="b">
+        <v>0</v>
+      </c>
+      <c r="N94" t="b">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="P94" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>AEROENTER.NS</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" t="n">
+        <v>130.6499938964844</v>
+      </c>
+      <c r="F95" t="n">
+        <v>138.0899963378906</v>
+      </c>
+      <c r="G95" t="n">
+        <v>128.3500061035156</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1091886</v>
+      </c>
+      <c r="I95" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="L95" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" t="b">
+        <v>0</v>
+      </c>
+      <c r="N95" t="b">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>37</v>
+      </c>
+      <c r="P95" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MOREPENLAB.NS</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" t="n">
+        <v>59.06999969482422</v>
+      </c>
+      <c r="F96" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="G96" t="n">
+        <v>58.81000137329102</v>
+      </c>
+      <c r="H96" t="n">
+        <v>9442332</v>
+      </c>
+      <c r="I96" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="L96" t="b">
+        <v>0</v>
+      </c>
+      <c r="M96" t="b">
+        <v>0</v>
+      </c>
+      <c r="N96" t="b">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="P96" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>WEWORK.NS</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>2</v>
+      </c>
+      <c r="E97" t="n">
+        <v>739.6500244140625</v>
+      </c>
+      <c r="F97" t="n">
+        <v>764</v>
+      </c>
+      <c r="G97" t="n">
+        <v>731.0499877929688</v>
+      </c>
+      <c r="H97" t="n">
+        <v>319687</v>
+      </c>
+      <c r="I97" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L97" t="b">
+        <v>0</v>
+      </c>
+      <c r="M97" t="b">
+        <v>0</v>
+      </c>
+      <c r="N97" t="b">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>15</v>
+      </c>
+      <c r="P97" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>AEQUS.NS</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" t="n">
+        <v>236.5399932861328</v>
+      </c>
+      <c r="F98" t="n">
+        <v>240.3000030517578</v>
+      </c>
+      <c r="G98" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="H98" t="n">
+        <v>10530811</v>
+      </c>
+      <c r="I98" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="L98" t="b">
+        <v>0</v>
+      </c>
+      <c r="M98" t="b">
+        <v>0</v>
+      </c>
+      <c r="N98" t="b">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="P98" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>UTKARSHBNK.NS</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" t="n">
+        <v>15.06999969482422</v>
+      </c>
+      <c r="F99" t="n">
+        <v>15.35999965667725</v>
+      </c>
+      <c r="G99" t="n">
+        <v>14.96000003814697</v>
+      </c>
+      <c r="H99" t="n">
+        <v>7987727</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="L99" t="b">
+        <v>0</v>
+      </c>
+      <c r="M99" t="b">
+        <v>0</v>
+      </c>
+      <c r="N99" t="b">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="P99" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SATIN.NS</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>2</v>
+      </c>
+      <c r="E100" t="n">
+        <v>254.8000030517578</v>
+      </c>
+      <c r="F100" t="n">
+        <v>262.0199890136719</v>
+      </c>
+      <c r="G100" t="n">
+        <v>252.3099975585938</v>
+      </c>
+      <c r="H100" t="n">
+        <v>665874</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J100" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-6.26</v>
+      </c>
+      <c r="L100" t="b">
+        <v>0</v>
+      </c>
+      <c r="M100" t="b">
+        <v>0</v>
+      </c>
+      <c r="N100" t="b">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>18</v>
+      </c>
+      <c r="P100" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SAKSOFT.NS</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" t="n">
+        <v>178.9799957275391</v>
+      </c>
+      <c r="F101" t="n">
+        <v>189.8999938964844</v>
+      </c>
+      <c r="G101" t="n">
+        <v>176.2400054931641</v>
+      </c>
+      <c r="H101" t="n">
+        <v>15053759</v>
+      </c>
+      <c r="I101" t="n">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="J101" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="L101" t="b">
+        <v>0</v>
+      </c>
+      <c r="M101" t="b">
+        <v>0</v>
+      </c>
+      <c r="N101" t="b">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="P101" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>FUSION.NS</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>2</v>
+      </c>
+      <c r="E102" t="n">
+        <v>229.3999938964844</v>
+      </c>
+      <c r="F102" t="n">
+        <v>234.3000030517578</v>
+      </c>
+      <c r="G102" t="n">
+        <v>216.3999938964844</v>
+      </c>
+      <c r="H102" t="n">
+        <v>3234066</v>
+      </c>
+      <c r="I102" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J102" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K102" t="n">
+        <v>-8.91</v>
+      </c>
+      <c r="L102" t="b">
+        <v>1</v>
+      </c>
+      <c r="M102" t="b">
+        <v>0</v>
+      </c>
+      <c r="N102" t="b">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="P102" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>T1_HIT_ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>TARIL.NS</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>2</v>
+      </c>
+      <c r="E103" t="n">
+        <v>336.75</v>
+      </c>
+      <c r="F103" t="n">
+        <v>359.6499938964844</v>
+      </c>
+      <c r="G103" t="n">
+        <v>335.1499938964844</v>
+      </c>
+      <c r="H103" t="n">
+        <v>5859666</v>
+      </c>
+      <c r="I103" t="n">
+        <v>-6.18</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="L103" t="b">
+        <v>0</v>
+      </c>
+      <c r="M103" t="b">
+        <v>0</v>
+      </c>
+      <c r="N103" t="b">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="P103" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EBGNG.NS</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>2</v>
+      </c>
+      <c r="E104" t="n">
+        <v>641.1500244140625</v>
+      </c>
+      <c r="F104" t="n">
+        <v>675.5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>641.1500244140625</v>
+      </c>
+      <c r="H104" t="n">
+        <v>478721</v>
+      </c>
+      <c r="I104" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="J104" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K104" t="n">
+        <v>-13.35</v>
+      </c>
+      <c r="L104" t="b">
+        <v>0</v>
+      </c>
+      <c r="M104" t="b">
+        <v>0</v>
+      </c>
+      <c r="N104" t="b">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="P104" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>BAJFINANCE.NS</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1031.400024414062</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1017.599975585938</v>
+      </c>
+      <c r="H105" t="n">
+        <v>9398215</v>
+      </c>
+      <c r="I105" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="K105" t="n">
+        <v>-3.83</v>
+      </c>
+      <c r="L105" t="b">
+        <v>0</v>
+      </c>
+      <c r="M105" t="b">
+        <v>0</v>
+      </c>
+      <c r="N105" t="b">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="P105" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB.NS</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" t="n">
+        <v>214.1600036621094</v>
+      </c>
+      <c r="F106" t="n">
+        <v>216.8300018310547</v>
+      </c>
+      <c r="G106" t="n">
+        <v>206.8600006103516</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1599671</v>
+      </c>
+      <c r="I106" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="J106" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="K106" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L106" t="b">
+        <v>0</v>
+      </c>
+      <c r="M106" t="b">
+        <v>0</v>
+      </c>
+      <c r="N106" t="b">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="P106" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>KILITCH.NS</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" t="n">
+        <v>188.4499969482422</v>
+      </c>
+      <c r="F107" t="n">
+        <v>197.9499969482422</v>
+      </c>
+      <c r="G107" t="n">
+        <v>187.1499938964844</v>
+      </c>
+      <c r="H107" t="n">
+        <v>42003</v>
+      </c>
+      <c r="I107" t="n">
+        <v>-8.31</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-9.33</v>
+      </c>
+      <c r="L107" t="b">
+        <v>0</v>
+      </c>
+      <c r="M107" t="b">
+        <v>0</v>
+      </c>
+      <c r="N107" t="b">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="P107" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>AVL.NS</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" t="n">
+        <v>638.5499877929688</v>
+      </c>
+      <c r="F108" t="n">
+        <v>654.9000244140625</v>
+      </c>
+      <c r="G108" t="n">
+        <v>633.5</v>
+      </c>
+      <c r="H108" t="n">
+        <v>226014</v>
+      </c>
+      <c r="I108" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="J108" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="L108" t="b">
+        <v>0</v>
+      </c>
+      <c r="M108" t="b">
+        <v>0</v>
+      </c>
+      <c r="N108" t="b">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="P108" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>BLUEJET.NS</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" t="n">
+        <v>556</v>
+      </c>
+      <c r="F109" t="n">
+        <v>577.9500122070312</v>
+      </c>
+      <c r="G109" t="n">
+        <v>551.0999755859375</v>
+      </c>
+      <c r="H109" t="n">
+        <v>445432</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J109" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-5.98</v>
+      </c>
+      <c r="L109" t="b">
+        <v>0</v>
+      </c>
+      <c r="M109" t="b">
+        <v>0</v>
+      </c>
+      <c r="N109" t="b">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>17</v>
+      </c>
+      <c r="P109" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD.NS</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>2</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2047.599975585938</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2059.89990234375</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2011.099975585938</v>
+      </c>
+      <c r="H110" t="n">
+        <v>802227</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="L110" t="b">
+        <v>0</v>
+      </c>
+      <c r="M110" t="b">
+        <v>0</v>
+      </c>
+      <c r="N110" t="b">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="P110" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>PIRAMALFIN.NS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2137.699951171875</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2199</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2126.10009765625</v>
+      </c>
+      <c r="H111" t="n">
+        <v>642054</v>
+      </c>
+      <c r="I111" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="L111" t="b">
+        <v>0</v>
+      </c>
+      <c r="M111" t="b">
+        <v>0</v>
+      </c>
+      <c r="N111" t="b">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="P111" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>PRESTIGE.NS</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1668</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1698.900024414062</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1647.800048828125</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1047148</v>
+      </c>
+      <c r="I112" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J112" t="n">
+        <v>3</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="L112" t="b">
+        <v>0</v>
+      </c>
+      <c r="M112" t="b">
+        <v>0</v>
+      </c>
+      <c r="N112" t="b">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="P112" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>IBULLSLTD.NS</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>2</v>
+      </c>
+      <c r="E113" t="n">
+        <v>29.29999923706055</v>
+      </c>
+      <c r="F113" t="n">
+        <v>29.31999969482422</v>
+      </c>
+      <c r="G113" t="n">
+        <v>27.70000076293945</v>
+      </c>
+      <c r="H113" t="n">
+        <v>18144850</v>
+      </c>
+      <c r="I113" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="J113" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="L113" t="b">
+        <v>0</v>
+      </c>
+      <c r="M113" t="b">
+        <v>0</v>
+      </c>
+      <c r="N113" t="b">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="P113" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TIRUPATIFL.NS</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>2</v>
+      </c>
+      <c r="E114" t="n">
+        <v>66.81999969482422</v>
+      </c>
+      <c r="F114" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="G114" t="n">
+        <v>65</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2180435</v>
+      </c>
+      <c r="I114" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="J114" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="L114" t="b">
+        <v>0</v>
+      </c>
+      <c r="M114" t="b">
+        <v>0</v>
+      </c>
+      <c r="N114" t="b">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="P114" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>RAMCOSYS.NS</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" t="n">
+        <v>799.5999755859375</v>
+      </c>
+      <c r="F115" t="n">
+        <v>821.4500122070312</v>
+      </c>
+      <c r="G115" t="n">
+        <v>785.1500244140625</v>
+      </c>
+      <c r="H115" t="n">
+        <v>3407847</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J115" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="L115" t="b">
+        <v>0</v>
+      </c>
+      <c r="M115" t="b">
+        <v>0</v>
+      </c>
+      <c r="N115" t="b">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="P115" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>RML.NS</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>2</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1206.800048828125</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1249</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1196.400024414062</v>
+      </c>
+      <c r="H116" t="n">
+        <v>76190</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-6.11</v>
+      </c>
+      <c r="L116" t="b">
+        <v>0</v>
+      </c>
+      <c r="M116" t="b">
+        <v>0</v>
+      </c>
+      <c r="N116" t="b">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="P116" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>VIYASH.NS</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" t="n">
+        <v>294.1499938964844</v>
+      </c>
+      <c r="F117" t="n">
+        <v>295.8999938964844</v>
+      </c>
+      <c r="G117" t="n">
+        <v>288.2000122070312</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1556829</v>
+      </c>
+      <c r="I117" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J117" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-6.38</v>
+      </c>
+      <c r="L117" t="b">
+        <v>0</v>
+      </c>
+      <c r="M117" t="b">
+        <v>0</v>
+      </c>
+      <c r="N117" t="b">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="P117" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>VENUSPIPES.NS</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>2</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1783.199951171875</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1810.800048828125</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1780</v>
+      </c>
+      <c r="H118" t="n">
+        <v>58533</v>
+      </c>
+      <c r="I118" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-5.86</v>
+      </c>
+      <c r="L118" t="b">
+        <v>0</v>
+      </c>
+      <c r="M118" t="b">
+        <v>0</v>
+      </c>
+      <c r="N118" t="b">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="P118" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>EMIL.NS</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" t="n">
+        <v>140.6799926757812</v>
+      </c>
+      <c r="F119" t="n">
+        <v>143.6499938964844</v>
+      </c>
+      <c r="G119" t="n">
+        <v>134.8999938964844</v>
+      </c>
+      <c r="H119" t="n">
+        <v>4691115</v>
+      </c>
+      <c r="I119" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="J119" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="K119" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L119" t="b">
+        <v>1</v>
+      </c>
+      <c r="M119" t="b">
+        <v>0</v>
+      </c>
+      <c r="N119" t="b">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P119" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>T1_HIT_ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SGFIN.NS</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="n">
+        <v>673.7999877929688</v>
+      </c>
+      <c r="F120" t="n">
+        <v>682.25</v>
+      </c>
+      <c r="G120" t="n">
+        <v>654</v>
+      </c>
+      <c r="H120" t="n">
+        <v>271906</v>
+      </c>
+      <c r="I120" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J120" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K120" t="n">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="L120" t="b">
+        <v>0</v>
+      </c>
+      <c r="M120" t="b">
+        <v>0</v>
+      </c>
+      <c r="N120" t="b">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="P120" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>LTF.NS</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>2</v>
+      </c>
+      <c r="E121" t="n">
+        <v>327</v>
+      </c>
+      <c r="F121" t="n">
+        <v>329</v>
+      </c>
+      <c r="G121" t="n">
+        <v>317.75</v>
+      </c>
+      <c r="H121" t="n">
+        <v>8792592</v>
+      </c>
+      <c r="I121" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="J121" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="K121" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="L121" t="b">
+        <v>0</v>
+      </c>
+      <c r="M121" t="b">
+        <v>0</v>
+      </c>
+      <c r="N121" t="b">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="P121" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q121" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -8518,7 +11435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8566,7 +11483,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Win Rate %</t>
+          <t>Runners Active</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -8576,7 +11493,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Avg Return %</t>
+          <t>Win Rate %</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -8586,7 +11503,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Avg Win %</t>
+          <t>Avg Return %</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -8596,7 +11513,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Avg Loss %</t>
+          <t>Avg Win %</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -8606,7 +11523,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Avg Max Gain %</t>
+          <t>Avg Loss %</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -8616,7 +11533,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Avg Max DD %</t>
+          <t>Avg Runner Ret%</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -8626,7 +11543,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T1 Hit Rate %</t>
+          <t>Avg T2-Exit Ret%</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -8636,7 +11553,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T2 Hit Rate %</t>
+          <t>Avg Max Gain %</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -8646,7 +11563,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stop Hit Rate %</t>
+          <t>Avg Max DD %</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -8656,12 +11573,42 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>T1 Hit Rate %</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T2 Hit Rate %</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stop Hit Rate %</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-07-02 11:01</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-03 11:01</t>
         </is>
       </c>
     </row>

--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -3550,6 +3550,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -3628,10 +3629,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-03 11:01</t>
-        </is>
-      </c>
-    </row>
+          <t>2026-07-03 13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -3772,6 +3775,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -3834,7 +3838,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-03 11:01</t>
+          <t>2026-07-03 13:24</t>
         </is>
       </c>
     </row>
@@ -3859,6 +3863,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -3977,10 +3982,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-03 11:01</t>
-        </is>
-      </c>
-    </row>
+          <t>2026-07-03 13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -4014,7 +4021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q121"/>
+  <dimension ref="A1:Q161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9385,7 +9392,7 @@
         <v>-1.79</v>
       </c>
       <c r="J88" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>-9.109999999999999</v>
@@ -10486,7 +10493,7 @@
         <v>6.69</v>
       </c>
       <c r="K106" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
@@ -11419,6 +11426,2446 @@
         <v>2</v>
       </c>
       <c r="Q121" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SETL.NS</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>2</v>
+      </c>
+      <c r="E122" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="F122" t="n">
+        <v>305.2999877929688</v>
+      </c>
+      <c r="G122" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2098935</v>
+      </c>
+      <c r="I122" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="J122" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-17.36</v>
+      </c>
+      <c r="L122" t="b">
+        <v>0</v>
+      </c>
+      <c r="M122" t="b">
+        <v>0</v>
+      </c>
+      <c r="N122" t="b">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P122" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>VIPULLTD.NS</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" t="n">
+        <v>15.34000015258789</v>
+      </c>
+      <c r="F123" t="n">
+        <v>16</v>
+      </c>
+      <c r="G123" t="n">
+        <v>14.6899995803833</v>
+      </c>
+      <c r="H123" t="n">
+        <v>10396639</v>
+      </c>
+      <c r="I123" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="J123" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K123" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="L123" t="b">
+        <v>0</v>
+      </c>
+      <c r="M123" t="b">
+        <v>0</v>
+      </c>
+      <c r="N123" t="b">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="P123" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CGCL.NS</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="n">
+        <v>233.8699951171875</v>
+      </c>
+      <c r="F124" t="n">
+        <v>235.3399963378906</v>
+      </c>
+      <c r="G124" t="n">
+        <v>226.1999969482422</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3415898</v>
+      </c>
+      <c r="I124" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="J124" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="L124" t="b">
+        <v>0</v>
+      </c>
+      <c r="M124" t="b">
+        <v>0</v>
+      </c>
+      <c r="N124" t="b">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="P124" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>MANBA.NS</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>2</v>
+      </c>
+      <c r="E125" t="n">
+        <v>139.1499938964844</v>
+      </c>
+      <c r="F125" t="n">
+        <v>140.5</v>
+      </c>
+      <c r="G125" t="n">
+        <v>137</v>
+      </c>
+      <c r="H125" t="n">
+        <v>128347</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K125" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="L125" t="b">
+        <v>0</v>
+      </c>
+      <c r="M125" t="b">
+        <v>0</v>
+      </c>
+      <c r="N125" t="b">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="P125" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>IRISDOREME.NS</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" t="n">
+        <v>42.95999908447266</v>
+      </c>
+      <c r="F126" t="n">
+        <v>44.15000152587891</v>
+      </c>
+      <c r="G126" t="n">
+        <v>42.59999847412109</v>
+      </c>
+      <c r="H126" t="n">
+        <v>420207</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-11.03</v>
+      </c>
+      <c r="L126" t="b">
+        <v>0</v>
+      </c>
+      <c r="M126" t="b">
+        <v>0</v>
+      </c>
+      <c r="N126" t="b">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="P126" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>MANCREDIT.NS</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>2</v>
+      </c>
+      <c r="E127" t="n">
+        <v>245.3300018310547</v>
+      </c>
+      <c r="F127" t="n">
+        <v>265</v>
+      </c>
+      <c r="G127" t="n">
+        <v>240.0200042724609</v>
+      </c>
+      <c r="H127" t="n">
+        <v>1173608</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="L127" t="b">
+        <v>0</v>
+      </c>
+      <c r="M127" t="b">
+        <v>0</v>
+      </c>
+      <c r="N127" t="b">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>21</v>
+      </c>
+      <c r="P127" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>NACLIND.NS</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" t="n">
+        <v>218.3999938964844</v>
+      </c>
+      <c r="F128" t="n">
+        <v>224.4700012207031</v>
+      </c>
+      <c r="G128" t="n">
+        <v>213.6000061035156</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1919921</v>
+      </c>
+      <c r="I128" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="L128" t="b">
+        <v>0</v>
+      </c>
+      <c r="M128" t="b">
+        <v>0</v>
+      </c>
+      <c r="N128" t="b">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="P128" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>GODREJPROP.NS</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>2</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1996.400024414062</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2002.599975585938</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1970.5</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1001474</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K129" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="L129" t="b">
+        <v>0</v>
+      </c>
+      <c r="M129" t="b">
+        <v>0</v>
+      </c>
+      <c r="N129" t="b">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="P129" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>AVG.NS</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" t="n">
+        <v>224.2400054931641</v>
+      </c>
+      <c r="F130" t="n">
+        <v>229</v>
+      </c>
+      <c r="G130" t="n">
+        <v>208.7299957275391</v>
+      </c>
+      <c r="H130" t="n">
+        <v>354217</v>
+      </c>
+      <c r="I130" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="J130" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="K130" t="n">
+        <v>-12.94</v>
+      </c>
+      <c r="L130" t="b">
+        <v>0</v>
+      </c>
+      <c r="M130" t="b">
+        <v>0</v>
+      </c>
+      <c r="N130" t="b">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="P130" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>IOLCP.NS</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>2</v>
+      </c>
+      <c r="E131" t="n">
+        <v>142.9600067138672</v>
+      </c>
+      <c r="F131" t="n">
+        <v>150.8899993896484</v>
+      </c>
+      <c r="G131" t="n">
+        <v>140.2700042724609</v>
+      </c>
+      <c r="H131" t="n">
+        <v>4336773</v>
+      </c>
+      <c r="I131" t="n">
+        <v>-2.89</v>
+      </c>
+      <c r="J131" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K131" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="L131" t="b">
+        <v>0</v>
+      </c>
+      <c r="M131" t="b">
+        <v>0</v>
+      </c>
+      <c r="N131" t="b">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="P131" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DELHIVERY.NS</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>2</v>
+      </c>
+      <c r="E132" t="n">
+        <v>507.4500122070312</v>
+      </c>
+      <c r="F132" t="n">
+        <v>515</v>
+      </c>
+      <c r="G132" t="n">
+        <v>502.8500061035156</v>
+      </c>
+      <c r="H132" t="n">
+        <v>8379741</v>
+      </c>
+      <c r="I132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K132" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="L132" t="b">
+        <v>0</v>
+      </c>
+      <c r="M132" t="b">
+        <v>0</v>
+      </c>
+      <c r="N132" t="b">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>18</v>
+      </c>
+      <c r="P132" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>AURUM.NS</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>2</v>
+      </c>
+      <c r="E133" t="n">
+        <v>231.8999938964844</v>
+      </c>
+      <c r="F133" t="n">
+        <v>237</v>
+      </c>
+      <c r="G133" t="n">
+        <v>227.2299957275391</v>
+      </c>
+      <c r="H133" t="n">
+        <v>211926</v>
+      </c>
+      <c r="I133" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="K133" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="L133" t="b">
+        <v>0</v>
+      </c>
+      <c r="M133" t="b">
+        <v>0</v>
+      </c>
+      <c r="N133" t="b">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="P133" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>MAHABANK.NS</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>2</v>
+      </c>
+      <c r="E134" t="n">
+        <v>88.52999877929688</v>
+      </c>
+      <c r="F134" t="n">
+        <v>91.48000335693359</v>
+      </c>
+      <c r="G134" t="n">
+        <v>88.18000030517578</v>
+      </c>
+      <c r="H134" t="n">
+        <v>16120019</v>
+      </c>
+      <c r="I134" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="K134" t="n">
+        <v>-2.93</v>
+      </c>
+      <c r="L134" t="b">
+        <v>0</v>
+      </c>
+      <c r="M134" t="b">
+        <v>0</v>
+      </c>
+      <c r="N134" t="b">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="P134" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>AEROENTER.NS</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" t="n">
+        <v>130.6499938964844</v>
+      </c>
+      <c r="F135" t="n">
+        <v>138.0899963378906</v>
+      </c>
+      <c r="G135" t="n">
+        <v>128.3500061035156</v>
+      </c>
+      <c r="H135" t="n">
+        <v>1091886</v>
+      </c>
+      <c r="I135" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="J135" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="K135" t="n">
+        <v>-6.61</v>
+      </c>
+      <c r="L135" t="b">
+        <v>0</v>
+      </c>
+      <c r="M135" t="b">
+        <v>0</v>
+      </c>
+      <c r="N135" t="b">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>37</v>
+      </c>
+      <c r="P135" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>MOREPENLAB.NS</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" t="n">
+        <v>59.06999969482422</v>
+      </c>
+      <c r="F136" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="G136" t="n">
+        <v>58.81000137329102</v>
+      </c>
+      <c r="H136" t="n">
+        <v>9442332</v>
+      </c>
+      <c r="I136" t="n">
+        <v>-5.76</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>-12.8</v>
+      </c>
+      <c r="L136" t="b">
+        <v>0</v>
+      </c>
+      <c r="M136" t="b">
+        <v>0</v>
+      </c>
+      <c r="N136" t="b">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="P136" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>WEWORK.NS</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" t="n">
+        <v>739.6500244140625</v>
+      </c>
+      <c r="F137" t="n">
+        <v>764</v>
+      </c>
+      <c r="G137" t="n">
+        <v>731.0499877929688</v>
+      </c>
+      <c r="H137" t="n">
+        <v>319687</v>
+      </c>
+      <c r="I137" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J137" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="K137" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L137" t="b">
+        <v>0</v>
+      </c>
+      <c r="M137" t="b">
+        <v>0</v>
+      </c>
+      <c r="N137" t="b">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>15</v>
+      </c>
+      <c r="P137" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>AEQUS.NS</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>2</v>
+      </c>
+      <c r="E138" t="n">
+        <v>236.5399932861328</v>
+      </c>
+      <c r="F138" t="n">
+        <v>240.3000030517578</v>
+      </c>
+      <c r="G138" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="H138" t="n">
+        <v>10530811</v>
+      </c>
+      <c r="I138" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K138" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="L138" t="b">
+        <v>0</v>
+      </c>
+      <c r="M138" t="b">
+        <v>0</v>
+      </c>
+      <c r="N138" t="b">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="P138" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>UTKARSHBNK.NS</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>2</v>
+      </c>
+      <c r="E139" t="n">
+        <v>15.06999969482422</v>
+      </c>
+      <c r="F139" t="n">
+        <v>15.35999965667725</v>
+      </c>
+      <c r="G139" t="n">
+        <v>14.96000003814697</v>
+      </c>
+      <c r="H139" t="n">
+        <v>7987727</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K139" t="n">
+        <v>-3.77</v>
+      </c>
+      <c r="L139" t="b">
+        <v>0</v>
+      </c>
+      <c r="M139" t="b">
+        <v>0</v>
+      </c>
+      <c r="N139" t="b">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="P139" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SATIN.NS</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" t="n">
+        <v>254.8000030517578</v>
+      </c>
+      <c r="F140" t="n">
+        <v>262.0199890136719</v>
+      </c>
+      <c r="G140" t="n">
+        <v>252.3099975585938</v>
+      </c>
+      <c r="H140" t="n">
+        <v>665874</v>
+      </c>
+      <c r="I140" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J140" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K140" t="n">
+        <v>-6.26</v>
+      </c>
+      <c r="L140" t="b">
+        <v>0</v>
+      </c>
+      <c r="M140" t="b">
+        <v>0</v>
+      </c>
+      <c r="N140" t="b">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>18</v>
+      </c>
+      <c r="P140" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SAKSOFT.NS</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>2</v>
+      </c>
+      <c r="E141" t="n">
+        <v>178.9799957275391</v>
+      </c>
+      <c r="F141" t="n">
+        <v>189.8999938964844</v>
+      </c>
+      <c r="G141" t="n">
+        <v>176.2400054931641</v>
+      </c>
+      <c r="H141" t="n">
+        <v>15053759</v>
+      </c>
+      <c r="I141" t="n">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="J141" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="K141" t="n">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="L141" t="b">
+        <v>0</v>
+      </c>
+      <c r="M141" t="b">
+        <v>0</v>
+      </c>
+      <c r="N141" t="b">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="P141" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>FUSION.NS</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>2</v>
+      </c>
+      <c r="E142" t="n">
+        <v>229.3999938964844</v>
+      </c>
+      <c r="F142" t="n">
+        <v>234.3000030517578</v>
+      </c>
+      <c r="G142" t="n">
+        <v>216.3999938964844</v>
+      </c>
+      <c r="H142" t="n">
+        <v>3234066</v>
+      </c>
+      <c r="I142" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J142" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K142" t="n">
+        <v>-8.91</v>
+      </c>
+      <c r="L142" t="b">
+        <v>1</v>
+      </c>
+      <c r="M142" t="b">
+        <v>0</v>
+      </c>
+      <c r="N142" t="b">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="P142" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>T1_HIT_ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>TARIL.NS</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>2</v>
+      </c>
+      <c r="E143" t="n">
+        <v>336.75</v>
+      </c>
+      <c r="F143" t="n">
+        <v>359.6499938964844</v>
+      </c>
+      <c r="G143" t="n">
+        <v>335.1499938964844</v>
+      </c>
+      <c r="H143" t="n">
+        <v>5859666</v>
+      </c>
+      <c r="I143" t="n">
+        <v>-6.18</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>-7.29</v>
+      </c>
+      <c r="L143" t="b">
+        <v>0</v>
+      </c>
+      <c r="M143" t="b">
+        <v>0</v>
+      </c>
+      <c r="N143" t="b">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="P143" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EBGNG.NS</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" t="n">
+        <v>641.1500244140625</v>
+      </c>
+      <c r="F144" t="n">
+        <v>675.5</v>
+      </c>
+      <c r="G144" t="n">
+        <v>641.1500244140625</v>
+      </c>
+      <c r="H144" t="n">
+        <v>478721</v>
+      </c>
+      <c r="I144" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="J144" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K144" t="n">
+        <v>-13.35</v>
+      </c>
+      <c r="L144" t="b">
+        <v>0</v>
+      </c>
+      <c r="M144" t="b">
+        <v>0</v>
+      </c>
+      <c r="N144" t="b">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="P144" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BAJFINANCE.NS</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>2</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1031.400024414062</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1040</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1017.599975585938</v>
+      </c>
+      <c r="H145" t="n">
+        <v>9398215</v>
+      </c>
+      <c r="I145" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J145" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="K145" t="n">
+        <v>-3.83</v>
+      </c>
+      <c r="L145" t="b">
+        <v>0</v>
+      </c>
+      <c r="M145" t="b">
+        <v>0</v>
+      </c>
+      <c r="N145" t="b">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="P145" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB.NS</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>2</v>
+      </c>
+      <c r="E146" t="n">
+        <v>214.1600036621094</v>
+      </c>
+      <c r="F146" t="n">
+        <v>216.8300018310547</v>
+      </c>
+      <c r="G146" t="n">
+        <v>206.8600006103516</v>
+      </c>
+      <c r="H146" t="n">
+        <v>1599671</v>
+      </c>
+      <c r="I146" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="J146" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="K146" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L146" t="b">
+        <v>0</v>
+      </c>
+      <c r="M146" t="b">
+        <v>0</v>
+      </c>
+      <c r="N146" t="b">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="P146" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>KILITCH.NS</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>2</v>
+      </c>
+      <c r="E147" t="n">
+        <v>188.4499969482422</v>
+      </c>
+      <c r="F147" t="n">
+        <v>197.9499969482422</v>
+      </c>
+      <c r="G147" t="n">
+        <v>187.1499938964844</v>
+      </c>
+      <c r="H147" t="n">
+        <v>42003</v>
+      </c>
+      <c r="I147" t="n">
+        <v>-8.31</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>-9.33</v>
+      </c>
+      <c r="L147" t="b">
+        <v>0</v>
+      </c>
+      <c r="M147" t="b">
+        <v>0</v>
+      </c>
+      <c r="N147" t="b">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="P147" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>AVL.NS</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>2</v>
+      </c>
+      <c r="E148" t="n">
+        <v>638.5499877929688</v>
+      </c>
+      <c r="F148" t="n">
+        <v>654.9000244140625</v>
+      </c>
+      <c r="G148" t="n">
+        <v>633.5</v>
+      </c>
+      <c r="H148" t="n">
+        <v>226014</v>
+      </c>
+      <c r="I148" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="J148" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="K148" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="L148" t="b">
+        <v>0</v>
+      </c>
+      <c r="M148" t="b">
+        <v>0</v>
+      </c>
+      <c r="N148" t="b">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="P148" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BLUEJET.NS</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>2</v>
+      </c>
+      <c r="E149" t="n">
+        <v>556</v>
+      </c>
+      <c r="F149" t="n">
+        <v>577.9500122070312</v>
+      </c>
+      <c r="G149" t="n">
+        <v>551.0999755859375</v>
+      </c>
+      <c r="H149" t="n">
+        <v>445432</v>
+      </c>
+      <c r="I149" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="K149" t="n">
+        <v>-5.98</v>
+      </c>
+      <c r="L149" t="b">
+        <v>0</v>
+      </c>
+      <c r="M149" t="b">
+        <v>0</v>
+      </c>
+      <c r="N149" t="b">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>17</v>
+      </c>
+      <c r="P149" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD.NS</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>2</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2047.599975585938</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2059.89990234375</v>
+      </c>
+      <c r="G150" t="n">
+        <v>2011.099975585938</v>
+      </c>
+      <c r="H150" t="n">
+        <v>802227</v>
+      </c>
+      <c r="I150" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J150" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K150" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="L150" t="b">
+        <v>0</v>
+      </c>
+      <c r="M150" t="b">
+        <v>0</v>
+      </c>
+      <c r="N150" t="b">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="P150" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PIRAMALFIN.NS</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>2</v>
+      </c>
+      <c r="E151" t="n">
+        <v>2137.699951171875</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2199</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2126.10009765625</v>
+      </c>
+      <c r="H151" t="n">
+        <v>642054</v>
+      </c>
+      <c r="I151" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="L151" t="b">
+        <v>0</v>
+      </c>
+      <c r="M151" t="b">
+        <v>0</v>
+      </c>
+      <c r="N151" t="b">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="P151" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>PRESTIGE.NS</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>2</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1668</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1698.900024414062</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1647.800048828125</v>
+      </c>
+      <c r="H152" t="n">
+        <v>1047148</v>
+      </c>
+      <c r="I152" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J152" t="n">
+        <v>3</v>
+      </c>
+      <c r="K152" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="L152" t="b">
+        <v>0</v>
+      </c>
+      <c r="M152" t="b">
+        <v>0</v>
+      </c>
+      <c r="N152" t="b">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="P152" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>IBULLSLTD.NS</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>2</v>
+      </c>
+      <c r="E153" t="n">
+        <v>29.29999923706055</v>
+      </c>
+      <c r="F153" t="n">
+        <v>29.31999969482422</v>
+      </c>
+      <c r="G153" t="n">
+        <v>27.70000076293945</v>
+      </c>
+      <c r="H153" t="n">
+        <v>18144850</v>
+      </c>
+      <c r="I153" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="J153" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="K153" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="L153" t="b">
+        <v>0</v>
+      </c>
+      <c r="M153" t="b">
+        <v>0</v>
+      </c>
+      <c r="N153" t="b">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="P153" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>TIRUPATIFL.NS</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>2</v>
+      </c>
+      <c r="E154" t="n">
+        <v>66.81999969482422</v>
+      </c>
+      <c r="F154" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="G154" t="n">
+        <v>65</v>
+      </c>
+      <c r="H154" t="n">
+        <v>2180435</v>
+      </c>
+      <c r="I154" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="J154" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="K154" t="n">
+        <v>-9.380000000000001</v>
+      </c>
+      <c r="L154" t="b">
+        <v>0</v>
+      </c>
+      <c r="M154" t="b">
+        <v>0</v>
+      </c>
+      <c r="N154" t="b">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="P154" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>RAMCOSYS.NS</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>2</v>
+      </c>
+      <c r="E155" t="n">
+        <v>799.5999755859375</v>
+      </c>
+      <c r="F155" t="n">
+        <v>821.4500122070312</v>
+      </c>
+      <c r="G155" t="n">
+        <v>785.1500244140625</v>
+      </c>
+      <c r="H155" t="n">
+        <v>3407847</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J155" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="K155" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="L155" t="b">
+        <v>0</v>
+      </c>
+      <c r="M155" t="b">
+        <v>0</v>
+      </c>
+      <c r="N155" t="b">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="P155" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>RML.NS</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>2</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1206.800048828125</v>
+      </c>
+      <c r="F156" t="n">
+        <v>1249</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1196.400024414062</v>
+      </c>
+      <c r="H156" t="n">
+        <v>76190</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K156" t="n">
+        <v>-6.11</v>
+      </c>
+      <c r="L156" t="b">
+        <v>0</v>
+      </c>
+      <c r="M156" t="b">
+        <v>0</v>
+      </c>
+      <c r="N156" t="b">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="P156" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>VIYASH.NS</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>2</v>
+      </c>
+      <c r="E157" t="n">
+        <v>294.1499938964844</v>
+      </c>
+      <c r="F157" t="n">
+        <v>295.8999938964844</v>
+      </c>
+      <c r="G157" t="n">
+        <v>288.2000122070312</v>
+      </c>
+      <c r="H157" t="n">
+        <v>1556829</v>
+      </c>
+      <c r="I157" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J157" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="K157" t="n">
+        <v>-6.38</v>
+      </c>
+      <c r="L157" t="b">
+        <v>0</v>
+      </c>
+      <c r="M157" t="b">
+        <v>0</v>
+      </c>
+      <c r="N157" t="b">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="P157" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>VENUSPIPES.NS</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>2</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1783.199951171875</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1810.800048828125</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1780</v>
+      </c>
+      <c r="H158" t="n">
+        <v>58533</v>
+      </c>
+      <c r="I158" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>-5.86</v>
+      </c>
+      <c r="L158" t="b">
+        <v>0</v>
+      </c>
+      <c r="M158" t="b">
+        <v>0</v>
+      </c>
+      <c r="N158" t="b">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="P158" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>EMIL.NS</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>2</v>
+      </c>
+      <c r="E159" t="n">
+        <v>140.6799926757812</v>
+      </c>
+      <c r="F159" t="n">
+        <v>143.6499938964844</v>
+      </c>
+      <c r="G159" t="n">
+        <v>134.8999938964844</v>
+      </c>
+      <c r="H159" t="n">
+        <v>4691115</v>
+      </c>
+      <c r="I159" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="J159" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="K159" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L159" t="b">
+        <v>1</v>
+      </c>
+      <c r="M159" t="b">
+        <v>0</v>
+      </c>
+      <c r="N159" t="b">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P159" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>T1_HIT_ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SGFIN.NS</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>2</v>
+      </c>
+      <c r="E160" t="n">
+        <v>673.7999877929688</v>
+      </c>
+      <c r="F160" t="n">
+        <v>682.25</v>
+      </c>
+      <c r="G160" t="n">
+        <v>654</v>
+      </c>
+      <c r="H160" t="n">
+        <v>271906</v>
+      </c>
+      <c r="I160" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J160" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K160" t="n">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="L160" t="b">
+        <v>0</v>
+      </c>
+      <c r="M160" t="b">
+        <v>0</v>
+      </c>
+      <c r="N160" t="b">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="P160" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>LTF.NS</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>2</v>
+      </c>
+      <c r="E161" t="n">
+        <v>327</v>
+      </c>
+      <c r="F161" t="n">
+        <v>329</v>
+      </c>
+      <c r="G161" t="n">
+        <v>317.75</v>
+      </c>
+      <c r="H161" t="n">
+        <v>8792592</v>
+      </c>
+      <c r="I161" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="J161" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="K161" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="L161" t="b">
+        <v>0</v>
+      </c>
+      <c r="M161" t="b">
+        <v>0</v>
+      </c>
+      <c r="N161" t="b">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="P161" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q161" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -11608,7 +14055,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-03 11:01</t>
+          <t>2026-07-03 13:24</t>
         </is>
       </c>
     </row>

--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -1,29 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Tracking" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence Analysis" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TQ Analysis" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opp Score Analysis" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector Analysis" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regime Analysis" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Report" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekday Analysis" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holding Period Analysis" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Comparison" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conf x TQ Matrix" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalyst Analysis" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fail Reason Analysis" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regime x Sector" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence Trajectory" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Tracking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Performance Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Confidence Analysis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Sector Analysis" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Regime Analysis" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Monthly Report" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Weekday Analysis" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Holding Period Analysis" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Category Comparison" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Conf x TQ Matrix" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Catalyst Analysis" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Fail Reason Analysis" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Regime x Sector" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Confidence Trajectory" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Delivery Flow" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Sector Rotation" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Portfolio Metrics" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Backtest vs Live" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,13 +43,30 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -62,8 +81,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -598,7 +620,6 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 63.9, need 80)</t>
@@ -674,7 +695,6 @@
       <c r="Q3" t="n">
         <v>0.1</v>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 79.2, need 80)</t>
@@ -750,7 +770,6 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 77.5, need 80)</t>
@@ -826,7 +845,6 @@
       <c r="Q5" t="n">
         <v>0.17</v>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 79.2, need 80), RR_FAIL(got 1.83, need 2.0)</t>
@@ -902,7 +920,6 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 77.6, need 80), RR_FAIL(got 1.86, need 2.0)</t>
@@ -978,7 +995,6 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 51.8, need 80)</t>
@@ -1054,7 +1070,6 @@
       <c r="Q8" t="n">
         <v>3.4</v>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 75.7, need 80), RR_FAIL(got 1.68, need 2.0)</t>
@@ -1130,7 +1145,6 @@
       <c r="Q9" t="n">
         <v>0.47</v>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 51.3, need 80)</t>
@@ -1206,7 +1220,6 @@
       <c r="Q10" t="n">
         <v>0.82</v>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 73.9, need 80), RR_FAIL(got 1.44, need 2.0)</t>
@@ -1282,7 +1295,6 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 77.5, need 80), RR_FAIL(got 1.45, need 2.0)</t>
@@ -1358,7 +1370,6 @@
       <c r="Q12" t="n">
         <v>0.02</v>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 39.9, need 80)</t>
@@ -1434,7 +1445,6 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 77.2, need 80), RR_FAIL(got 1.43, need 2.0)</t>
@@ -1510,7 +1520,6 @@
       <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 77.6, need 80), RR_FAIL(got 1.41, need 2.0)</t>
@@ -1586,7 +1595,6 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 70.5, need 80), RR_FAIL(got 1.37, need 2.0)</t>
@@ -1662,7 +1670,6 @@
       <c r="Q16" t="n">
         <v>1.17</v>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 39.6, need 80)</t>
@@ -1738,7 +1745,6 @@
       <c r="Q17" t="n">
         <v>0.46</v>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 49.9, need 80)</t>
@@ -1814,7 +1820,6 @@
       <c r="Q18" t="n">
         <v>0.42</v>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 62.8, need 80), RR_FAIL(got 1.45, need 2.0)</t>
@@ -1890,7 +1895,6 @@
       <c r="Q19" t="n">
         <v>0.15</v>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 57.8, need 80), RR_FAIL(got 1.43, need 2.0)</t>
@@ -1966,7 +1970,6 @@
       <c r="Q20" t="n">
         <v>0.01</v>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 66.1, need 80), RR_FAIL(got 1.43, need 2.0)</t>
@@ -2042,7 +2045,6 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 58.1, need 80), RR_FAIL(got 1.93, need 2.0)</t>
@@ -2118,7 +2120,6 @@
       <c r="Q22" t="n">
         <v>0.08</v>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 63.7, need 80), RR_FAIL(got 1.43, need 2.0)</t>
@@ -2194,7 +2195,6 @@
       <c r="Q23" t="n">
         <v>0</v>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 63.8, need 80), RR_FAIL(got 1.42, need 2.0)</t>
@@ -2270,7 +2270,6 @@
       <c r="Q24" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 50.9, need 80), RR_FAIL(got 1.83, need 2.0)</t>
@@ -2346,7 +2345,6 @@
       <c r="Q25" t="n">
         <v>0.37</v>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 54.7, need 80), RR_FAIL(got 1.43, need 2.0)</t>
@@ -2422,7 +2420,6 @@
       <c r="Q26" t="n">
         <v>0</v>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 52.2, need 80), RR_FAIL(got 1.61, need 2.0)</t>
@@ -2498,7 +2495,6 @@
       <c r="Q27" t="n">
         <v>2.27</v>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 49.8, need 80), RR_FAIL(got 1.58, need 2.0)</t>
@@ -2574,7 +2570,6 @@
       <c r="Q28" t="n">
         <v>0</v>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 29.0, need 80)</t>
@@ -2650,7 +2645,6 @@
       <c r="Q29" t="n">
         <v>1.05</v>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 53.0, need 80), RR_FAIL(got 1.43, need 2.0)</t>
@@ -2726,7 +2720,6 @@
       <c r="Q30" t="n">
         <v>0.19</v>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 44.5, need 80), RR_FAIL(got 1.73, need 2.0)</t>
@@ -2802,7 +2795,6 @@
       <c r="Q31" t="n">
         <v>0.17</v>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 38.5, need 80)</t>
@@ -2878,7 +2870,6 @@
       <c r="Q32" t="n">
         <v>0.25</v>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 38.9, need 80), RR_FAIL(got 1.76, need 2.0)</t>
@@ -2954,7 +2945,6 @@
       <c r="Q33" t="n">
         <v>1.23</v>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 48.9, need 80), RR_FAIL(got 1.47, need 2.0)</t>
@@ -3030,7 +3020,6 @@
       <c r="Q34" t="n">
         <v>0.16</v>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 39.0, need 80), RR_FAIL(got 1.45, need 2.0)</t>
@@ -3106,7 +3095,6 @@
       <c r="Q35" t="n">
         <v>0</v>
       </c>
-      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 36.9, need 80), RR_FAIL(got 1.41, need 2.0)</t>
@@ -3182,7 +3170,6 @@
       <c r="Q36" t="n">
         <v>0</v>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 37.2, need 80), RR_FAIL(got 1.42, need 2.0)</t>
@@ -3258,7 +3245,6 @@
       <c r="Q37" t="n">
         <v>0</v>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 37.1, need 80), RR_FAIL(got 1.43, need 2.0)</t>
@@ -3334,7 +3320,6 @@
       <c r="Q38" t="n">
         <v>0</v>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 37.0, need 80), RR_FAIL(got 1.43, need 2.0)</t>
@@ -3410,7 +3395,6 @@
       <c r="Q39" t="n">
         <v>0</v>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 37.0, need 80), RR_FAIL(got 1.43, need 2.0)</t>
@@ -3486,7 +3470,6 @@
       <c r="Q40" t="n">
         <v>0</v>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 37.3, need 80), RR_FAIL(got 1.45, need 2.0)</t>
@@ -3562,7 +3545,6 @@
       <c r="Q41" t="n">
         <v>0</v>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 36.0, need 80), RR_FAIL(got 1.40, need 2.0)</t>
@@ -3638,7 +3620,6 @@
       <c r="Q42" t="n">
         <v>0.09</v>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 35.3, need 80), RR_FAIL(got 1.40, need 2.0)</t>
@@ -3714,7 +3695,6 @@
       <c r="Q43" t="n">
         <v>0</v>
       </c>
-      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
           <t>CONF_FAIL(got 28.8, need 80), RR_FAIL(got 1.38, need 2.0)</t>
@@ -3737,9 +3717,118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category Comparison — Do BUY, NEAR_MISS, WATCHLIST tiers differ?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Avg Confidence</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Avg TQ</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Avg Opp Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NEAR_MISS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>73.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>WATCHLIST</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F5" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>INSIGHT: BUY win rate should be &gt;= NEAR_MISS &gt;= WATCHLIST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>If NEAR_MISS matches BUY, the tier boundary is too strict.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3750,9 +3839,217 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Confidence × TQ Matrix — where do the two factors compound?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Each cell shows: Win Rate% (n=count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Confidence \ TQ</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Low TQ</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Mid TQ</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>High TQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Low Conf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mid Conf</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>High Conf</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Avg Return% matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Confidence \ TQ</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Low TQ</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Mid TQ</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>High TQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Low Conf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Mid Conf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>High Conf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>INSIGHT: If High×High dominates, tighten filter to require BOTH factors high.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3763,9 +4060,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Catalyst Analysis — which catalysts actually pay off?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Catalyst</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Best Trade%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No parseable catalyst data with outcomes yet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3776,9 +4115,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fail Reason Analysis — which amber flags actually predict losses?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Fail Reason</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Count in Buys+NearMiss</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No fail reasons observed in BUY/NEAR_MISS picks with outcomes. Either all promoted picks are clean, or data is thin.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3789,9 +4165,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Regime × Sector — which sectors win in each regime?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Cell = Avg Return% (n=count). Blank if &lt;2 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>No settled trades with Regime + Sector yet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3802,9 +4200,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Confidence Trajectory — does rising conf beat stable/falling?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Trajectory</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No confidence_history.json yet.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3815,9 +4255,827 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Rec Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Return%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Deliv %Today</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Deliv 20d Avg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SETL.NS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>51.77</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.93</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.178</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ACCUM</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GINNIFILA.NS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>60.28</v>
+      </c>
+      <c r="F3" t="n">
+        <v>56.06</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MUTHOOTMF.NS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="F4" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AEQUS.NS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>29.71</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GODREJPROP.NS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>52.37</v>
+      </c>
+      <c r="F6" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>STRONG_ACCUM</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AMAGI.NS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="F7" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INDOCO.NS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="F8" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.347</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>STRONG_ACCUM</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NACLIND.NS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LODHA.NS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>51.21</v>
+      </c>
+      <c r="F10" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.309</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>STRONG_ACCUM</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DLF.NS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="F11" t="n">
+        <v>44.95</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.193</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ACCUM</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IPCALAB.NS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>50.04</v>
+      </c>
+      <c r="F12" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AVG.NS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>49.16</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD.NS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>63.51</v>
+      </c>
+      <c r="F14" t="n">
+        <v>52.11</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ACCUM</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FUSION.NS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>52.22</v>
+      </c>
+      <c r="F15" t="n">
+        <v>53.56</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>PRESTIGE.NS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VIPULLTD.NS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>52.58</v>
+      </c>
+      <c r="F17" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM.NS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="F18" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SHILPAMED.NS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="F19" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMIL.NS</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="F20" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY.NS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="F21" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG.NS</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="F22" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL.NS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="F23" t="n">
+        <v>56.06</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3828,9 +5086,179 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Rank Today</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Rank 5d Ago</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Portfolio Exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>No history file at sector_rank_history.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PORTFOLIO METRICS (from Daily Tracking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Daily Tracking sheet is empty</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>BACKTEST vs LIVE DIVERGENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Backtest</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>(no backtest artefact found)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Run backtest_walkforward.py and export results.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3968,9 +5396,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Median Return%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Avg Max Gain%</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>T1 Hit%</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>T2 Hit%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>70-75</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>75-80</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>THRESHOLD SIMULATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note: Adjust thresholds in config based on above win rates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Never auto-modify — use statistical evidence only (3+ months data).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3981,9 +5541,269 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Avg Max Gain%</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CHEMICALS</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>HEALTHCARE</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LOGISTICS</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>METALS</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>(insufficient)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3994,9 +5814,58 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Regime</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Best Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4007,9 +5876,171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly Research Report — July 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Generated: 2026-07-04 04:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Picks</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Annualized%</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Best Trade%</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Worst Trade%</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Best Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>42</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TREND (last month vs previous)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Need at least 2 months of data for trend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LESSONS LEARNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1. Monitor win rates by confidence band (aim for 60%+ at min threshold)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2. Compare NEAR MISS vs BUY outcomes over time</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3. Track sector performance vs broad market</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4. Validate regime-specific thresholds after 3 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5. Never lower thresholds based on fewer than 20 closed trades</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4020,9 +6051,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Weekday Analysis — Does day-of-recommendation matter?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Weekday</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Best Trade%</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Worst Trade%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>42</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>INSIGHT: If Friday's Win Rate is &gt;5pts below the average, consider skipping Friday scans (weekend gap risk).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4033,9 +6133,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Holding Period Analysis — When do trades close out?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Holding Days</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>% of All Closed</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>No Daily Tracking data yet (need Holding Days column).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -26,6 +26,7 @@
     <sheet name="Sector Rotation" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Portfolio Metrics" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Backtest vs Live" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Weekly Factor Summary" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -81,11 +82,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3944,9 +3948,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -4338,7 +4340,6 @@
           <t>ACCUM</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4373,7 +4374,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4408,7 +4408,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4443,7 +4442,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4478,7 +4476,6 @@
           <t>STRONG_ACCUM</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4513,7 +4510,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4548,7 +4544,6 @@
           <t>STRONG_ACCUM</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4583,7 +4578,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4618,7 +4612,6 @@
           <t>STRONG_ACCUM</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4653,7 +4646,6 @@
           <t>ACCUM</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4688,7 +4680,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4723,7 +4714,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4758,7 +4748,6 @@
           <t>ACCUM</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4793,7 +4782,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4828,7 +4816,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4863,7 +4850,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4898,7 +4884,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4933,7 +4918,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4968,7 +4952,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5003,7 +4986,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5038,7 +5020,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5073,7 +5054,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5356,6 +5336,992 @@
       <c r="Q1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Weekly Factor Summary  (Jun 28 — Jul 04, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Recommendations in window: 42  |  Winners: 0  |  Losers: 0  |  Still Active: 42</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>All Picks (avg)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Winners (avg)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Losers (avg)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Still Active (avg)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>BUY (avg)</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>WATCHLIST (avg)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>N (All)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Opp Score</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="H5" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="H6" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TQ</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="H7" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H8" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pledge%</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="H10" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D/E</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H11" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>── Outcome factors (from Daily Tracking) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Return%</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Max Gain%</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Max DD%</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Remaining Upside%</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Holding Days</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Hit Rate % (settled only)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>── Factor → Return  (what does each factor level actually pay?) ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HIGH bucket</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HIGH avg Return%</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HIGH Hit Rate%</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>MID bucket</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>MID avg Return%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>LOW bucket</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>LOW avg Return%</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>LOW Hit Rate%</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Edge (HIGH−LOW Return%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Opp Score</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>≥ 70.10  (n=14)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>64.90 – 70.10  (n=13)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>≤ 64.90  (n=15)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>≥ 63.68  (n=14)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>39.92 – 63.68  (n=13)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>≤ 39.92  (n=15)</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TQ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>≥ 83.80  (n=14)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>81.90 – 83.80  (n=13)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>≤ 81.90  (n=15)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>R/R</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>≥ 1.83  (n=14)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.43 – 1.83  (n=11)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>≤ 1.43  (n=17)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Pledge%</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>≥ 0.00  (n=42)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.00 – 0.00  (n=0)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>≤ 0.00  (n=0)</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>≥ 6.79  (n=14)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.00 – 6.79  (n=5)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>≤ 0.00  (n=23)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>D/E</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>≥ 0.17  (n=15)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.00 – 0.17  (n=7)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>≤ 0.00  (n=20)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -3731,6 +3731,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -3818,6 +3819,7 @@
         <v>65.59999999999999</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -3860,6 +3862,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3948,7 +3951,10 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -4044,6 +4050,8 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -4072,6 +4080,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4099,6 +4108,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -4127,6 +4137,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4149,6 +4160,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -4184,6 +4196,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -4212,6 +4225,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4239,6 +4253,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -4257,7 +4272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4310,7 +4325,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SETL.NS</t>
+          <t>UTKARSHBNK.NS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4327,24 +4342,25 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>51.77</v>
+        <v>50.52</v>
       </c>
       <c r="F2" t="n">
-        <v>43.93</v>
+        <v>44.12</v>
       </c>
       <c r="G2" t="n">
-        <v>1.178</v>
+        <v>1.145</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ACCUM</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GINNIFILA.NS</t>
+          <t>SETL.NS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4361,24 +4377,25 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>60.28</v>
+        <v>51.77</v>
       </c>
       <c r="F3" t="n">
-        <v>56.06</v>
+        <v>43.93</v>
       </c>
       <c r="G3" t="n">
-        <v>1.075</v>
+        <v>1.178</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
+          <t>ACCUM</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MUTHOOTMF.NS</t>
+          <t>SIKA.NS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4395,24 +4412,25 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>45.31</v>
+        <v>11.16</v>
       </c>
       <c r="F4" t="n">
-        <v>49.7</v>
+        <v>42.97</v>
       </c>
       <c r="G4" t="n">
-        <v>0.912</v>
+        <v>0.26</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
+          <t>DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AEQUS.NS</t>
+          <t>GINNIFILA.NS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4429,24 +4447,25 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>21.9</v>
+        <v>60.28</v>
       </c>
       <c r="F5" t="n">
-        <v>29.71</v>
+        <v>56.06</v>
       </c>
       <c r="G5" t="n">
-        <v>0.737</v>
+        <v>1.075</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>WEAK</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GODREJPROP.NS</t>
+          <t>HIKAL.NS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4463,24 +4482,25 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>52.37</v>
+        <v>51.17</v>
       </c>
       <c r="F6" t="n">
-        <v>38.49</v>
+        <v>44.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.361</v>
+        <v>1.158</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>STRONG_ACCUM</t>
-        </is>
-      </c>
+          <t>ACCUM</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMAGI.NS</t>
+          <t>TARSONS.NS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -4497,24 +4517,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>43.31</v>
+        <v>31.57</v>
       </c>
       <c r="F7" t="n">
-        <v>38.56</v>
+        <v>39.75</v>
       </c>
       <c r="G7" t="n">
-        <v>1.123</v>
+        <v>0.794</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INDOCO.NS</t>
+          <t>MUTHOOTMF.NS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -4531,24 +4552,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>47.07</v>
+        <v>45.31</v>
       </c>
       <c r="F8" t="n">
-        <v>34.95</v>
+        <v>49.7</v>
       </c>
       <c r="G8" t="n">
-        <v>1.347</v>
+        <v>0.912</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>STRONG_ACCUM</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NACLIND.NS</t>
+          <t>AEQUS.NS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4565,24 +4587,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>25.5</v>
+        <v>21.9</v>
       </c>
       <c r="F9" t="n">
-        <v>36.06</v>
+        <v>29.71</v>
       </c>
       <c r="G9" t="n">
-        <v>0.707</v>
+        <v>0.737</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LODHA.NS</t>
+          <t>GODREJPROP.NS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4599,24 +4622,25 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>51.21</v>
+        <v>52.37</v>
       </c>
       <c r="F10" t="n">
-        <v>39.13</v>
+        <v>38.49</v>
       </c>
       <c r="G10" t="n">
-        <v>1.309</v>
+        <v>1.361</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>STRONG_ACCUM</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DLF.NS</t>
+          <t>LTF.NS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4633,24 +4657,25 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>53.64</v>
+        <v>39.56</v>
       </c>
       <c r="F11" t="n">
-        <v>44.95</v>
+        <v>41.73</v>
       </c>
       <c r="G11" t="n">
-        <v>1.193</v>
+        <v>0.948</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ACCUM</t>
-        </is>
-      </c>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IPCALAB.NS</t>
+          <t>AMAGI.NS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4667,24 +4692,25 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>50.04</v>
+        <v>43.31</v>
       </c>
       <c r="F12" t="n">
-        <v>50.71</v>
+        <v>38.56</v>
       </c>
       <c r="G12" t="n">
-        <v>0.987</v>
+        <v>1.123</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AVG.NS</t>
+          <t>CREDITACC.NS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4701,24 +4727,25 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>44.48</v>
+        <v>52.27</v>
       </c>
       <c r="F13" t="n">
-        <v>49.16</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>0.905</v>
+        <v>1.045</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PHOENIXLTD.NS</t>
+          <t>APLLTD.NS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4735,24 +4762,25 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>63.51</v>
+        <v>33.6</v>
       </c>
       <c r="F14" t="n">
-        <v>52.11</v>
+        <v>42.99</v>
       </c>
       <c r="G14" t="n">
-        <v>1.219</v>
+        <v>0.782</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>ACCUM</t>
-        </is>
-      </c>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FUSION.NS</t>
+          <t>COSMOFIRST.NS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4769,24 +4797,25 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>52.22</v>
+        <v>40.65</v>
       </c>
       <c r="F15" t="n">
-        <v>53.56</v>
+        <v>48.73</v>
       </c>
       <c r="G15" t="n">
-        <v>0.975</v>
+        <v>0.834</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PRESTIGE.NS</t>
+          <t>INDOCO.NS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4803,24 +4832,25 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>53.1</v>
+        <v>47.07</v>
       </c>
       <c r="F16" t="n">
-        <v>48.46</v>
+        <v>34.95</v>
       </c>
       <c r="G16" t="n">
-        <v>1.096</v>
+        <v>1.347</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
+          <t>STRONG_ACCUM</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>VIPULLTD.NS</t>
+          <t>NACLIND.NS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4837,24 +4867,25 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>52.58</v>
+        <v>25.5</v>
       </c>
       <c r="F17" t="n">
-        <v>62.27</v>
+        <v>36.06</v>
       </c>
       <c r="G17" t="n">
-        <v>0.844</v>
+        <v>0.707</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>WEAK</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM.NS</t>
+          <t>LODHA.NS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4871,24 +4902,25 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>41.81</v>
+        <v>51.21</v>
       </c>
       <c r="F18" t="n">
-        <v>48.87</v>
+        <v>39.13</v>
       </c>
       <c r="G18" t="n">
-        <v>0.855</v>
+        <v>1.309</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
+          <t>STRONG_ACCUM</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SHILPAMED.NS</t>
+          <t>DLF.NS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4905,24 +4937,25 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>45.91</v>
+        <v>53.64</v>
       </c>
       <c r="F19" t="n">
-        <v>41.23</v>
+        <v>44.95</v>
       </c>
       <c r="G19" t="n">
-        <v>1.113</v>
+        <v>1.193</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
+          <t>ACCUM</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EMIL.NS</t>
+          <t>JAGSNPHARM.NS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4939,24 +4972,25 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>37.27</v>
+        <v>20.15</v>
       </c>
       <c r="F20" t="n">
-        <v>49.86</v>
+        <v>39.03</v>
       </c>
       <c r="G20" t="n">
-        <v>0.747</v>
+        <v>0.516</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>WEAK</t>
-        </is>
-      </c>
+          <t>DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OBEROIRLTY.NS</t>
+          <t>IPCALAB.NS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4973,24 +5007,25 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>45.01</v>
+        <v>50.04</v>
       </c>
       <c r="F21" t="n">
-        <v>46.53</v>
+        <v>50.71</v>
       </c>
       <c r="G21" t="n">
-        <v>0.967</v>
+        <v>0.987</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TTKPRESTIG.NS</t>
+          <t>WEWORK.NS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5007,53 +5042,720 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>49.05</v>
+        <v>29.93</v>
       </c>
       <c r="F22" t="n">
-        <v>46.24</v>
+        <v>48.92</v>
       </c>
       <c r="G22" t="n">
-        <v>1.061</v>
+        <v>0.612</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
+          <t>DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>AVG.NS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>44.48</v>
+      </c>
+      <c r="F23" t="n">
+        <v>49.16</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD.NS</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>63.51</v>
+      </c>
+      <c r="F24" t="n">
+        <v>52.11</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.219</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ACCUM</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OPTIEMUS.NS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>49.04</v>
+      </c>
+      <c r="F25" t="n">
+        <v>44.93</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.091</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FUSION.NS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>52.22</v>
+      </c>
+      <c r="F26" t="n">
+        <v>53.56</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SAKSOFT.NS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="F27" t="n">
+        <v>37.19</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PRESTIGE.NS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.096</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>VIPULLTD.NS</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>52.58</v>
+      </c>
+      <c r="F29" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM.NS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>41.81</v>
+      </c>
+      <c r="F30" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SHILPAMED.NS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="F31" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EMIL.NS</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="F32" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY.NS</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="F33" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>IKS.NS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="F34" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AADHARHFC.NS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>42.07</v>
+      </c>
+      <c r="F35" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.754</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DELHIVERY.NS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="F36" t="n">
+        <v>52.81</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NUVAMA.NS</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>RISHABH.NS</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="F38" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>VIYASH.NS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="n">
+        <v>50.05</v>
+      </c>
+      <c r="F39" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG.NS</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="F40" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>GHCLTEXTIL.NS</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
         <v>54.31</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F41" t="n">
         <v>56.06</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G41" t="n">
         <v>0.969</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BANSALWIRE.NS</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="n">
+        <v>35.57</v>
+      </c>
+      <c r="F42" t="n">
+        <v>47.34</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.751</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>WEAK</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5119,45 +5821,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>PORTFOLIO METRICS (from Daily Tracking)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Interpretation</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>No data</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Daily Tracking sheet is empty</t>
         </is>
@@ -5174,65 +5880,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>BACKTEST vs LIVE DIVERGENCE</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Backtest</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>(no backtest artefact found)</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Run backtest_walkforward.py and export results.json</t>
         </is>
@@ -6362,7 +7072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6407,90 +7117,138 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Median Return%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Avg Max Gain%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>T1 Hit%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>T2 Hit%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>70-75</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B9" t="n">
         <v>2</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>75-80</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B10" t="n">
         <v>8</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>THRESHOLD SIMULATION</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Note: Adjust thresholds in config based on above win rates.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Never auto-modify — use statistical evidence only (3+ months data).</t>
         </is>
@@ -6507,7 +7265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6537,233 +7295,270 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Avg Max Gain%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>FINANCE</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B13" t="n">
         <v>7</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>DIVERSIFIED</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B14" t="n">
         <v>4</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>CHEMICALS</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B15" t="n">
         <v>2</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>HEALTHCARE</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B16" t="n">
         <v>9</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>REALTY</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B17" t="n">
         <v>9</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B18" t="n">
         <v>4</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>CONSUMER</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B19" t="n">
         <v>4</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>PHARMA</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B20" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>LOGISTICS</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B21" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>METALS</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B22" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
@@ -6780,7 +7575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6810,22 +7605,50 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Regime</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Avg Return%</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Win Rate%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Best Sector</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B4" t="n">
         <v>42</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6866,10 +7689,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-04 04:01</t>
-        </is>
-      </c>
-    </row>
+          <t>Generated: 2026-07-05 12:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6950,6 +7774,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -6964,6 +7789,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -7027,6 +7853,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -7081,6 +7908,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -7109,6 +7937,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -7136,6 +7965,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>

--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -27,6 +27,9 @@
     <sheet name="Portfolio Metrics" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Backtest vs Live" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Weekly Factor Summary" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Portfolio Risk" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Benchmark" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Equity Curve" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3731,7 +3734,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -3819,7 +3821,6 @@
         <v>65.59999999999999</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -3862,7 +3863,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3951,10 +3951,7 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -4050,8 +4047,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -4080,7 +4075,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4108,7 +4102,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -4137,7 +4130,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4160,7 +4152,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -4196,7 +4187,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -4225,7 +4215,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4253,7 +4242,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -4355,7 +4343,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4390,7 +4377,6 @@
           <t>ACCUM</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4425,7 +4411,6 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4460,7 +4445,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4495,7 +4479,6 @@
           <t>ACCUM</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4530,7 +4513,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4565,7 +4547,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4600,7 +4581,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4635,7 +4615,6 @@
           <t>STRONG_ACCUM</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4670,7 +4649,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4705,7 +4683,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4740,7 +4717,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4775,7 +4751,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4810,7 +4785,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4845,7 +4819,6 @@
           <t>STRONG_ACCUM</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4880,7 +4853,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4915,7 +4887,6 @@
           <t>STRONG_ACCUM</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4950,7 +4921,6 @@
           <t>ACCUM</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4985,7 +4955,6 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5020,7 +4989,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5055,7 +5023,6 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5090,7 +5057,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5125,7 +5091,6 @@
           <t>ACCUM</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5160,7 +5125,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5195,7 +5159,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5230,7 +5193,6 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5265,7 +5227,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5300,7 +5261,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5335,7 +5295,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5370,7 +5329,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5405,7 +5363,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5440,7 +5397,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5475,7 +5431,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5510,7 +5465,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5545,7 +5499,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5580,7 +5533,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5615,7 +5567,6 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5650,7 +5601,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5685,7 +5635,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5720,7 +5669,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5755,7 +5703,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5821,13 +5768,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A5:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -5880,13 +5823,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A5:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -5959,7 +5898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6046,6 +5985,2568 @@
       <c r="Q1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UTKARSHBNK.NS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15.06999969482422</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15.35999965667725</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14.96000003814697</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7989638</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SETL.NS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="F3" t="n">
+        <v>305.2999877929688</v>
+      </c>
+      <c r="G3" t="n">
+        <v>281.75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2100597</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-17.15</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SIKA.NS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1220.699951171875</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1359.400024414062</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1182.400024414062</v>
+      </c>
+      <c r="H4" t="n">
+        <v>954863</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-14.18</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GINNIFILA.NS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>54.65000152587891</v>
+      </c>
+      <c r="F5" t="n">
+        <v>55</v>
+      </c>
+      <c r="G5" t="n">
+        <v>51.47000122070312</v>
+      </c>
+      <c r="H5" t="n">
+        <v>546863</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-12.37</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HIKAL.NS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>222.1000061035156</v>
+      </c>
+      <c r="F6" t="n">
+        <v>225.75</v>
+      </c>
+      <c r="G6" t="n">
+        <v>220.3200073242188</v>
+      </c>
+      <c r="H6" t="n">
+        <v>122619</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-3.23</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TARSONS.NS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>266.6000061035156</v>
+      </c>
+      <c r="F7" t="n">
+        <v>269.7000122070312</v>
+      </c>
+      <c r="G7" t="n">
+        <v>261.1000061035156</v>
+      </c>
+      <c r="H7" t="n">
+        <v>107138</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-2.45</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MUTHOOTMF.NS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>221.4700012207031</v>
+      </c>
+      <c r="F8" t="n">
+        <v>230.8999938964844</v>
+      </c>
+      <c r="G8" t="n">
+        <v>218.9199981689453</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1079935</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-6.23</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" t="b">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AEQUS.NS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>236.5399932861328</v>
+      </c>
+      <c r="F9" t="n">
+        <v>240.3000030517578</v>
+      </c>
+      <c r="G9" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>10538903</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GODREJPROP.NS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1996.400024414062</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2002.599975585938</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1970.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1001835</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-8.33</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>17</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LTF.NS</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>327</v>
+      </c>
+      <c r="F11" t="n">
+        <v>329</v>
+      </c>
+      <c r="G11" t="n">
+        <v>317.75</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8797473</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AMAGI.NS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>532.5999755859375</v>
+      </c>
+      <c r="F12" t="n">
+        <v>545.3499755859375</v>
+      </c>
+      <c r="G12" t="n">
+        <v>523.1500244140625</v>
+      </c>
+      <c r="H12" t="n">
+        <v>198358</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CREDITACC.NS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1557.400024414062</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1589</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1539.900024414062</v>
+      </c>
+      <c r="H13" t="n">
+        <v>564628</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-8.07</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" t="b">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>APLLTD.NS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>823.7000122070312</v>
+      </c>
+      <c r="F14" t="n">
+        <v>834.1500244140625</v>
+      </c>
+      <c r="G14" t="n">
+        <v>809.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>143213</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>COSMOFIRST.NS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>853.0999755859375</v>
+      </c>
+      <c r="F15" t="n">
+        <v>861</v>
+      </c>
+      <c r="G15" t="n">
+        <v>808.9500122070312</v>
+      </c>
+      <c r="H15" t="n">
+        <v>384712</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>INDOCO.NS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>244</v>
+      </c>
+      <c r="F16" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>242.1000061035156</v>
+      </c>
+      <c r="H16" t="n">
+        <v>119288</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-4.07</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" t="b">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NACLIND.NS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>218.3999938964844</v>
+      </c>
+      <c r="F17" t="n">
+        <v>224.4700012207031</v>
+      </c>
+      <c r="G17" t="n">
+        <v>213.6000061035156</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1920501</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-7.45</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" t="b">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LODHA.NS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1057</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1062</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1015</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7862663</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-11.11</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>IBULLSLTD.NS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>29.29999923706055</v>
+      </c>
+      <c r="F19" t="n">
+        <v>29.31999969482422</v>
+      </c>
+      <c r="G19" t="n">
+        <v>27.70000076293945</v>
+      </c>
+      <c r="H19" t="n">
+        <v>18147140</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-7.95</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DLF.NS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>675.9000244140625</v>
+      </c>
+      <c r="F20" t="n">
+        <v>678</v>
+      </c>
+      <c r="G20" t="n">
+        <v>656.5999755859375</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6688508</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>JAGSNPHARM.NS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>236.6199951171875</v>
+      </c>
+      <c r="F21" t="n">
+        <v>240</v>
+      </c>
+      <c r="G21" t="n">
+        <v>230.2599945068359</v>
+      </c>
+      <c r="H21" t="n">
+        <v>266585</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>IPCALAB.NS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1778.900024414062</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1788.300048828125</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1719.400024414062</v>
+      </c>
+      <c r="H22" t="n">
+        <v>571448</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WEWORK.NS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>739.6500244140625</v>
+      </c>
+      <c r="F23" t="n">
+        <v>764</v>
+      </c>
+      <c r="G23" t="n">
+        <v>731.0499877929688</v>
+      </c>
+      <c r="H23" t="n">
+        <v>319687</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-12.29</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>18</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AVG.NS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>224.2400054931641</v>
+      </c>
+      <c r="F24" t="n">
+        <v>229</v>
+      </c>
+      <c r="G24" t="n">
+        <v>208.7299957275391</v>
+      </c>
+      <c r="H24" t="n">
+        <v>354217</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-20.3</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD.NS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2047.599975585938</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2059.89990234375</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2011.099975585938</v>
+      </c>
+      <c r="H25" t="n">
+        <v>802256</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OPTIEMUS.NS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>521.5499877929688</v>
+      </c>
+      <c r="F26" t="n">
+        <v>525</v>
+      </c>
+      <c r="G26" t="n">
+        <v>497.1499938964844</v>
+      </c>
+      <c r="H26" t="n">
+        <v>360371</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" t="b">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FUSION.NS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
+        <v>229.3999938964844</v>
+      </c>
+      <c r="F27" t="n">
+        <v>234.3000030517578</v>
+      </c>
+      <c r="G27" t="n">
+        <v>216.3999938964844</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3234298</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-19.03</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>20</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SAKSOFT.NS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>178.9799957275391</v>
+      </c>
+      <c r="F28" t="n">
+        <v>189.8999938964844</v>
+      </c>
+      <c r="G28" t="n">
+        <v>176.2400054931641</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15054872</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PRESTIGE.NS</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1668</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1698.900024414062</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1647.800048828125</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1047148</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-7.71</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>VIPULLTD.NS</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.34000015258789</v>
+      </c>
+      <c r="F30" t="n">
+        <v>16</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14.6899995803833</v>
+      </c>
+      <c r="H30" t="n">
+        <v>10397139</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-11.28</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM.NS</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="n">
+        <v>868.0499877929688</v>
+      </c>
+      <c r="F31" t="n">
+        <v>887</v>
+      </c>
+      <c r="G31" t="n">
+        <v>846</v>
+      </c>
+      <c r="H31" t="n">
+        <v>391301</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SHILPAMED.NS</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="n">
+        <v>608.9500122070312</v>
+      </c>
+      <c r="F32" t="n">
+        <v>610</v>
+      </c>
+      <c r="G32" t="n">
+        <v>593.9000244140625</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1296612</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EMIL.NS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>140.6799926757812</v>
+      </c>
+      <c r="F33" t="n">
+        <v>143.6499938964844</v>
+      </c>
+      <c r="G33" t="n">
+        <v>134.8999938964844</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4692023</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-17.32</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY.NS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1934.400024414062</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1944.300048828125</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1864.699951171875</v>
+      </c>
+      <c r="H34" t="n">
+        <v>900582</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-9.32</v>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>IKS.NS</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1861.199951171875</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1881</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1831.199951171875</v>
+      </c>
+      <c r="H35" t="n">
+        <v>450539</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-9.77</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AADHARHFC.NS</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>555.5999755859375</v>
+      </c>
+      <c r="F36" t="n">
+        <v>558.7999877929688</v>
+      </c>
+      <c r="G36" t="n">
+        <v>533.8499755859375</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1522557</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" t="b">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DELHIVERY.NS</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>507.4500122070312</v>
+      </c>
+      <c r="F37" t="n">
+        <v>515</v>
+      </c>
+      <c r="G37" t="n">
+        <v>502.8500061035156</v>
+      </c>
+      <c r="H37" t="n">
+        <v>8380203</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-8.65</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NUVAMA.NS</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1887.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1955</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1827.900024414062</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1946356</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-6.16</v>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" t="b">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>RISHABH.NS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>649.4500122070312</v>
+      </c>
+      <c r="F39" t="n">
+        <v>678</v>
+      </c>
+      <c r="G39" t="n">
+        <v>637.0499877929688</v>
+      </c>
+      <c r="H39" t="n">
+        <v>608943</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-11.92</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" t="b">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>VIYASH.NS</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>294.1499938964844</v>
+      </c>
+      <c r="F40" t="n">
+        <v>295.8999938964844</v>
+      </c>
+      <c r="G40" t="n">
+        <v>288.2000122070312</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1556970</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" t="b">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG.NS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>624.25</v>
+      </c>
+      <c r="F41" t="n">
+        <v>656</v>
+      </c>
+      <c r="G41" t="n">
+        <v>615.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>270739</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" t="b">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL.NS</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="F42" t="n">
+        <v>107.1999969482422</v>
+      </c>
+      <c r="G42" t="n">
+        <v>104.1500015258789</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1670514</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-11.09</v>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" t="b">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BANSALWIRE.NS</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>365.7999877929688</v>
+      </c>
+      <c r="F43" t="n">
+        <v>370</v>
+      </c>
+      <c r="G43" t="n">
+        <v>342.5499877929688</v>
+      </c>
+      <c r="H43" t="n">
+        <v>597812</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-8.75</v>
+      </c>
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" t="b">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>18</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -6061,7 +8562,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -7040,13 +9541,487 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Portfolio-level Risk Snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Open Positions</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Active Runners</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Exposure %</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Avg Return% (open)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Std Return% (open)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Worst Open Return %</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VaR-95 (1-day, %)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-05 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>── Top-5 Positions by symbol ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Days Held</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Return %</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UTKARSHBNK.NS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SETL.NS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SIKA.NS</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GINNIFILA.NS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HIKAL.NS</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Strategy vs Benchmark (1Y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Benchmark symbol</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>^NSEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>^NSEI 1Y return %</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-4.47</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Strategy avg return % (closed)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alpha (strategy − benchmark)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>✓ Positive alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-05 12:32</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Equity Curve &amp; Risk-Adjusted Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Starting capital (₹)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ending capital (₹)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total P&amp;L (₹)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total P&amp;L %</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Trades counted</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Avg trade return %</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Std trade return %</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sharpe (annualised)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sortino (annualised)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Max drawdown %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Position size % used</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-05 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Trade Return %</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P&amp;L (₹)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Equity (₹)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7058,6 +10033,168 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total Tracked</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Runners Active</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Win Rate %</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Avg Return %</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Avg Win %</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Avg Loss %</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Avg Runner Ret%</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Avg T2-Exit Ret%</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Avg Max Gain %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Avg Max DD %</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T1 Hit Rate %</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T2 Hit Rate %</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stop Hit Rate %</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-05 12:32</t>
         </is>
       </c>
     </row>
@@ -7117,12 +10254,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -7295,16 +10426,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -7605,7 +10726,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -7666,7 +10786,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -7693,7 +10813,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -7774,7 +10893,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -7789,7 +10907,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -7853,7 +10970,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -7908,7 +11024,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -7937,7 +11052,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -7965,7 +11079,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>

--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -3734,6 +3734,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -3821,6 +3822,7 @@
         <v>65.59999999999999</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -3863,6 +3865,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3898,12 +3901,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0% (n=28)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0% (n=6)</t>
         </is>
       </c>
     </row>
@@ -3920,12 +3923,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0% (n=6)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0% (n=2)</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3954,10 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -3994,12 +4000,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4016,12 +4022,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -4047,6 +4053,8 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -4075,6 +4083,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4102,6 +4111,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -4120,7 +4130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4130,6 +4140,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4152,10 +4163,362 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NEED 80)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>No fail reasons observed in BUY/NEAR_MISS picks with outcomes. Either all promoted picks are clean, or data is thin.</t>
+          <t>NEED 2.0)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(GOT 79.2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(GOT 77.5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(GOT 77.6</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RR_FAIL(GOT 1.43</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RR_FAIL(GOT 1.83</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RR_FAIL(GOT 1.86</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(GOT 75.7</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RR_FAIL(GOT 1.68</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(GOT 73.9</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RR_FAIL(GOT 1.44</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RR_FAIL(GOT 1.45</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(GOT 77.2</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RR_FAIL(GOT 1.41</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(GOT 70.5</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RR_FAIL(GOT 1.37</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(GOT 66.1</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>(n&lt;5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>INSIGHT: Any fail-flag with Win Rate &lt; 45% on 10+ picks should be promoted from amber warning to HARD BLOCK.</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4187,10 +4550,131 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>No settled trades with Regime + Sector yet.</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sector \ Regime</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CHEMICALS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>+0.0% (n=2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>+0.0% (n=4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>+0.0% (n=4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>+0.0% (n=7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HEALTHCARE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>+0.0% (n=9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>+0.0% (n=4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LOGISTICS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>METALS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>+0.0% (n=9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>INSIGHT: Green cells = sector works in that regime. Use this to overweight/skip sectors when regime flips.</t>
         </is>
       </c>
     </row>
@@ -4215,6 +4699,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4242,6 +4727,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -4343,6 +4829,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4377,6 +4864,7 @@
           <t>ACCUM</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4411,6 +4899,7 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4445,6 +4934,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4479,6 +4969,7 @@
           <t>ACCUM</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4513,6 +5004,7 @@
           <t>WEAK</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4547,6 +5039,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4581,6 +5074,7 @@
           <t>WEAK</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4615,6 +5109,7 @@
           <t>STRONG_ACCUM</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4649,6 +5144,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4683,6 +5179,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4717,6 +5214,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4751,6 +5249,7 @@
           <t>WEAK</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4785,6 +5284,7 @@
           <t>WEAK</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4819,6 +5319,7 @@
           <t>STRONG_ACCUM</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4853,6 +5354,7 @@
           <t>WEAK</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4887,6 +5389,7 @@
           <t>STRONG_ACCUM</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4921,6 +5424,7 @@
           <t>ACCUM</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4955,6 +5459,7 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4989,6 +5494,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5023,6 +5529,7 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5057,6 +5564,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5091,6 +5599,7 @@
           <t>ACCUM</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5125,6 +5634,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5159,6 +5669,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5193,6 +5704,7 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5227,6 +5739,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5261,6 +5774,7 @@
           <t>WEAK</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5295,6 +5809,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5329,6 +5844,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5363,6 +5879,7 @@
           <t>WEAK</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5397,6 +5914,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5431,6 +5949,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5465,6 +5984,7 @@
           <t>WEAK</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5499,6 +6019,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5533,6 +6054,7 @@
           <t>WEAK</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5567,6 +6089,7 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5601,6 +6124,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5635,6 +6159,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5669,6 +6194,7 @@
           <t>NEUTRAL</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5703,6 +6229,7 @@
           <t>WEAK</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5768,47 +6295,219 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A5:C8"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>PORTFOLIO METRICS (from Daily Tracking)</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Interpretation</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Daily Tracking sheet is empty</t>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total closed trades</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>42</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Sample size</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total return (cumulative)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sum of per-trade returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Avg return per trade</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>&gt;0.5% is decent</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Win rate</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>&gt;55% is strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Avg win</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Avg loss</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>should be &gt; -3% (stop discipline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Expectancy per trade</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>&gt;0 = profitable edge</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Profit factor</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>∞</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>&gt;1.5 healthy, &gt;2.0 excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (proxy)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>&gt;1.0 good, &gt;2.0 exceptional</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cumulative peak-to-trough</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Overall health score</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>3/10</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>WEAK</t>
         </is>
       </c>
     </row>
@@ -5823,65 +6522,73 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A5:E8"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>BACKTEST vs LIVE DIVERGENCE</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Backtest</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Live</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>(no backtest artefact found)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Run backtest_walkforward.py and export results.json</t>
         </is>
@@ -6020,7 +6727,7 @@
         <v>7989638</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0.46</v>
@@ -6142,7 +6849,7 @@
         <v>954863</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>2.79</v>
@@ -6447,7 +7154,7 @@
         <v>10538903</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>1.27</v>
@@ -6630,13 +7337,13 @@
         <v>198358</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>5.25</v>
       </c>
       <c r="K12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -6813,10 +7520,10 @@
         <v>384712</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>-7.6</v>
@@ -6935,7 +7642,7 @@
         <v>1920501</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>1.83</v>
@@ -7057,10 +7764,10 @@
         <v>18147140</v>
       </c>
       <c r="I19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>-7.95</v>
@@ -7179,7 +7886,7 @@
         <v>266585</v>
       </c>
       <c r="I21" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0.63</v>
@@ -7423,10 +8130,10 @@
         <v>802256</v>
       </c>
       <c r="I25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>-6.62</v>
@@ -7484,10 +8191,10 @@
         <v>360371</v>
       </c>
       <c r="I26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>-10.9</v>
@@ -7545,10 +8252,10 @@
         <v>3234298</v>
       </c>
       <c r="I27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>-19.03</v>
@@ -7606,13 +8313,13 @@
         <v>15054872</v>
       </c>
       <c r="I28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>15.49</v>
       </c>
       <c r="K28" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -7789,10 +8496,10 @@
         <v>391301</v>
       </c>
       <c r="I31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>-5.41</v>
@@ -7911,10 +8618,10 @@
         <v>4692023</v>
       </c>
       <c r="I33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>-17.32</v>
@@ -8033,10 +8740,10 @@
         <v>450539</v>
       </c>
       <c r="I35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>-9.77</v>
@@ -8094,10 +8801,10 @@
         <v>1522557</v>
       </c>
       <c r="I36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>-7.2</v>
@@ -8338,10 +9045,10 @@
         <v>1556970</v>
       </c>
       <c r="I40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>-8.279999999999999</v>
@@ -8521,10 +9228,10 @@
         <v>597812</v>
       </c>
       <c r="I43" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>-8.75</v>
@@ -8562,7 +9269,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -10209,7 +10916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10254,132 +10961,145 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Avg Return%</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Median Return%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Win Rate%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Avg Max Gain%</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>T1 Hit%</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>T2 Hit%</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>70-75</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B16" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>75-80</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B17" t="n">
         <v>8</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>THRESHOLD SIMULATION</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Note: Adjust thresholds in config based on above win rates.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Never auto-modify — use statistical evidence only (3+ months data).</t>
         </is>
@@ -10396,7 +11116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10426,260 +11146,281 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Avg Return%</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Win Rate%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Avg Max Gain%</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>FINANCE</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B24" t="n">
         <v>7</v>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>DIVERSIFIED</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B25" t="n">
         <v>4</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>CHEMICALS</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B26" t="n">
         <v>2</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>HEALTHCARE</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B27" t="n">
         <v>9</v>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>REALTY</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B28" t="n">
         <v>9</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B29" t="n">
         <v>4</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>CONSUMER</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B30" t="n">
         <v>4</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>PHARMA</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B31" t="n">
         <v>1</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>LOGISTICS</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B32" t="n">
         <v>1</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>METALS</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B33" t="n">
         <v>1</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>(n&lt;5)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>(insufficient)</t>
         </is>
@@ -10696,7 +11437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10726,51 +11467,54 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Regime</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Avg Return%</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Win Rate%</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Best Sector</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>SIDEWAYS</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B6" t="n">
         <v>42</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CHEMICALS (+0.0%)</t>
         </is>
       </c>
     </row>
@@ -10786,7 +11530,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -10809,10 +11553,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-05 12:28</t>
-        </is>
-      </c>
-    </row>
+          <t>Generated: 2026-07-05 12:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10889,10 +11634,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
+          <t>CHEMICALS (+0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -10907,6 +11653,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -10970,6 +11717,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -11024,6 +11772,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -11042,7 +11791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11052,6 +11801,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -11079,10 +11829,37 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>No Daily Tracking data yet (need Holding Days column).</t>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1-2 days</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>42</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AVG HOLDING PERIOD: 2.0 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>INSIGHT: If '11-15 days' bucket has poor win rate, TIME_EXIT_DAYS is likely too long — trim to 10.</t>
         </is>
       </c>
     </row>

--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -26,10 +26,10 @@
     <sheet name="Sector Rotation" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Portfolio Metrics" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="Backtest vs Live" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Weekly Factor Summary" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Portfolio Risk" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Benchmark" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Equity Curve" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Portfolio Risk" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Benchmark" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Equity Curve" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Weekly Factor Summary" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3734,7 +3734,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -3822,7 +3821,6 @@
         <v>65.59999999999999</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -3865,7 +3863,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3954,10 +3951,7 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -4053,8 +4047,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -4083,7 +4075,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4111,7 +4102,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -4140,7 +4130,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4550,7 +4539,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4641,7 +4629,6 @@
           <t>LOGISTICS</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4649,7 +4636,6 @@
           <t>METALS</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4657,7 +4643,6 @@
           <t>PHARMA</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4699,7 +4684,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -4727,7 +4711,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -4829,7 +4812,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4864,7 +4846,6 @@
           <t>ACCUM</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4899,7 +4880,6 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4934,7 +4914,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4969,7 +4948,6 @@
           <t>ACCUM</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5004,7 +4982,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5039,7 +5016,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5074,7 +5050,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5109,7 +5084,6 @@
           <t>STRONG_ACCUM</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5144,7 +5118,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5179,7 +5152,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5214,7 +5186,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5249,7 +5220,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5284,7 +5254,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5319,7 +5288,6 @@
           <t>STRONG_ACCUM</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5354,7 +5322,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5389,7 +5356,6 @@
           <t>STRONG_ACCUM</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5424,7 +5390,6 @@
           <t>ACCUM</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5459,7 +5424,6 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5494,7 +5458,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5529,7 +5492,6 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5564,7 +5526,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5599,7 +5560,6 @@
           <t>ACCUM</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5634,7 +5594,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5669,7 +5628,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5704,7 +5662,6 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5739,7 +5696,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5774,7 +5730,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5809,7 +5764,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5844,7 +5798,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5879,7 +5832,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5914,7 +5866,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5949,7 +5900,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5984,7 +5934,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6019,7 +5968,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6054,7 +6002,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6089,7 +6036,6 @@
           <t>DISTRIBUTION</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6124,7 +6070,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6159,7 +6104,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6194,7 +6138,6 @@
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6229,7 +6172,6 @@
           <t>WEAK</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6295,17 +6237,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A9:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -6407,7 +6341,6 @@
           <t>0.00%</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6522,17 +6455,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A9:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -9263,6 +9188,480 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Portfolio-level Risk Snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Open Positions</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Active Runners</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Exposure %</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Avg Return% (open)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Std Return% (open)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Worst Open Return %</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VaR-95 (1-day, %)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-05 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>── Top-5 Positions by symbol ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Days Held</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Return %</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UTKARSHBNK.NS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SETL.NS</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SIKA.NS</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GINNIFILA.NS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HIKAL.NS</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Strategy vs Benchmark (1Y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Benchmark symbol</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>^NSEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>^NSEI 1Y return %</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-4.47</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Strategy avg return % (closed)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alpha (strategy − benchmark)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>✓ Positive alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-05 12:32</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Equity Curve &amp; Risk-Adjusted Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Starting capital (₹)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ending capital (₹)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total P&amp;L (₹)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total P&amp;L %</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Trades counted</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Avg trade return %</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Std trade return %</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sharpe (annualised)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sortino (annualised)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Max drawdown %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Position size % used</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-05 12:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Trade Return %</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P&amp;L (₹)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Equity (₹)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9286,7 +9685,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Weekly Factor Summary  (Jun 28 — Jul 04, 2026)</t>
+          <t>Weekly Factor Summary  (Jun 29 — Jul 05, 2026)</t>
         </is>
       </c>
     </row>
@@ -9590,35 +9989,29 @@
           <t>Return%</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G14" t="n">
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>42</v>
@@ -9630,35 +10023,29 @@
           <t>Max Gain%</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G15" t="n">
+        <v>0.95</v>
       </c>
       <c r="H15" t="n">
         <v>42</v>
@@ -9670,35 +10057,29 @@
           <t>Max DD%</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G16" t="n">
+        <v>-8.4</v>
       </c>
       <c r="H16" t="n">
         <v>42</v>
@@ -9710,35 +10091,29 @@
           <t>Remaining Upside%</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G17" t="n">
+        <v>21.02</v>
       </c>
       <c r="H17" t="n">
         <v>42</v>
@@ -9750,35 +10125,29 @@
           <t>Holding Days</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="G18" t="n">
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>42</v>
@@ -9890,45 +10259,37 @@
           <t>≥ 70.10  (n=14)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>64.90 – 70.10  (n=13)</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>≤ 64.90  (n=15)</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>64.90 – 70.10  (n=13)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>≤ 64.90  (n=15)</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -9942,45 +10303,37 @@
           <t>≥ 63.68  (n=14)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>39.92 – 63.68  (n=13)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>≤ 39.92  (n=15)</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>39.92 – 63.68  (n=13)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>≤ 39.92  (n=15)</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -9994,45 +10347,37 @@
           <t>≥ 83.80  (n=14)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>81.90 – 83.80  (n=13)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>≤ 81.90  (n=15)</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>81.90 – 83.80  (n=13)</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>≤ 81.90  (n=15)</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -10046,45 +10391,37 @@
           <t>≥ 1.83  (n=14)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.43 – 1.83  (n=11)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>≤ 1.43  (n=17)</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1.43 – 1.83  (n=11)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>≤ 1.43  (n=17)</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -10098,10 +10435,8 @@
           <t>≥ 0.00  (n=42)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C29" t="n">
+        <v>0</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -10150,45 +10485,37 @@
           <t>≥ 6.79  (n=14)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.00 – 6.79  (n=5)</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>≤ 0.00  (n=23)</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0.00 – 6.79  (n=5)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>≤ 0.00  (n=23)</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -10202,519 +10529,37 @@
           <t>≥ 0.17  (n=15)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.00 – 0.17  (n=7)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>≤ 0.00  (n=20)</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0.00 – 0.17  (n=7)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>≤ 0.00  (n=20)</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Portfolio-level Risk Snapshot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Open Positions</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Active Runners</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Total Exposure %</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Avg Return% (open)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Std Return% (open)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Worst Open Return %</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>VaR-95 (1-day, %)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Last Updated</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-07-05 12:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>── Top-5 Positions by symbol ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Days Held</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Return %</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>UTKARSHBNK.NS</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SETL.NS</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SIKA.NS</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>GINNIFILA.NS</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>HIKAL.NS</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Strategy vs Benchmark (1Y)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Benchmark symbol</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>^NSEI</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>^NSEI 1Y return %</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>-4.47</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Strategy avg return % (closed)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Alpha (strategy − benchmark)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>4.47</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>✓ Positive alpha</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Last Updated</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-07-05 12:32</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Equity Curve &amp; Risk-Adjusted Return</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Starting capital (₹)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Ending capital (₹)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Total P&amp;L (₹)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Total P&amp;L %</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Trades counted</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Avg trade return %</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Std trade return %</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sharpe (annualised)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sortino (annualised)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Max drawdown %</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Position size % used</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Last Updated</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-07-05 12:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Trade Return %</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>P&amp;L (₹)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Equity (₹)</t>
-        </is>
+      <c r="J31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10961,19 +10806,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -11146,27 +10978,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -11467,9 +11278,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -11557,7 +11365,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -11638,7 +11445,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -11653,7 +11459,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -11717,7 +11522,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -11772,7 +11576,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
@@ -11801,7 +11604,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -11848,7 +11650,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>

--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -3951,7 +3951,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -6530,7 +6529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9177,6 +9176,2568 @@
         <v>2</v>
       </c>
       <c r="Q43" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>UTKARSHBNK.NS</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>14.64000034332275</v>
+      </c>
+      <c r="F44" t="n">
+        <v>15.22999954223633</v>
+      </c>
+      <c r="G44" t="n">
+        <v>14.44999980926514</v>
+      </c>
+      <c r="H44" t="n">
+        <v>7931196</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-2.85</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="L44" t="b">
+        <v>0</v>
+      </c>
+      <c r="M44" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44" t="b">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="P44" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SETL.NS</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>267.7000122070312</v>
+      </c>
+      <c r="F45" t="n">
+        <v>275.7999877929688</v>
+      </c>
+      <c r="G45" t="n">
+        <v>267.7000122070312</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1858827</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="J45" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" t="b">
+        <v>0</v>
+      </c>
+      <c r="N45" t="b">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="P45" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SIKA.NS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1168.5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1258.800048828125</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1142.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>204929</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-4.28</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-8.84</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="b">
+        <v>0</v>
+      </c>
+      <c r="N46" t="b">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GINNIFILA.NS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>54.65000152587891</v>
+      </c>
+      <c r="F47" t="n">
+        <v>57.84999847412109</v>
+      </c>
+      <c r="G47" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>359433</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-9.42</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" t="b">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="P47" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HIKAL.NS</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>220.1799926757812</v>
+      </c>
+      <c r="F48" t="n">
+        <v>224.8999938964844</v>
+      </c>
+      <c r="G48" t="n">
+        <v>218.5399932861328</v>
+      </c>
+      <c r="H48" t="n">
+        <v>169987</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48" t="b">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TARSONS.NS</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>293.1499938964844</v>
+      </c>
+      <c r="F49" t="n">
+        <v>312.7999877929688</v>
+      </c>
+      <c r="G49" t="n">
+        <v>262</v>
+      </c>
+      <c r="H49" t="n">
+        <v>8219943</v>
+      </c>
+      <c r="I49" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="J49" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="L49" t="b">
+        <v>1</v>
+      </c>
+      <c r="M49" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49" t="b">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="P49" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>T1_HIT_ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MUTHOOTMF.NS</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>215.3200073242188</v>
+      </c>
+      <c r="F50" t="n">
+        <v>225.1000061035156</v>
+      </c>
+      <c r="G50" t="n">
+        <v>213.5599975585938</v>
+      </c>
+      <c r="H50" t="n">
+        <v>395942</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-3.21</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" t="b">
+        <v>0</v>
+      </c>
+      <c r="N50" t="b">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P50" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AEQUS.NS</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>231.8899993896484</v>
+      </c>
+      <c r="F51" t="n">
+        <v>243.8000030517578</v>
+      </c>
+      <c r="G51" t="n">
+        <v>230.6999969482422</v>
+      </c>
+      <c r="H51" t="n">
+        <v>7572649</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="b">
+        <v>0</v>
+      </c>
+      <c r="N51" t="b">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="P51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>GODREJPROP.NS</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2046.400024414062</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2051.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2001.400024414062</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1382000</v>
+      </c>
+      <c r="I52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" t="b">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LTF.NS</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>335.6000061035156</v>
+      </c>
+      <c r="F53" t="n">
+        <v>336.2999877929688</v>
+      </c>
+      <c r="G53" t="n">
+        <v>325.0499877929688</v>
+      </c>
+      <c r="H53" t="n">
+        <v>6784022</v>
+      </c>
+      <c r="I53" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J53" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-4.97</v>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AMAGI.NS</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>522.9000244140625</v>
+      </c>
+      <c r="F54" t="n">
+        <v>538.2999877929688</v>
+      </c>
+      <c r="G54" t="n">
+        <v>521.1500244140625</v>
+      </c>
+      <c r="H54" t="n">
+        <v>89074</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="J54" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" t="b">
+        <v>0</v>
+      </c>
+      <c r="N54" t="b">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>33</v>
+      </c>
+      <c r="P54" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CREDITACC.NS</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1587.099975585938</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1608.099975585938</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1533.300048828125</v>
+      </c>
+      <c r="H55" t="n">
+        <v>576927</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="K55" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="b">
+        <v>0</v>
+      </c>
+      <c r="N55" t="b">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>18</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>APLLTD.NS</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>835.6500244140625</v>
+      </c>
+      <c r="F56" t="n">
+        <v>839</v>
+      </c>
+      <c r="G56" t="n">
+        <v>821.2999877929688</v>
+      </c>
+      <c r="H56" t="n">
+        <v>226133</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" t="b">
+        <v>0</v>
+      </c>
+      <c r="N56" t="b">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>COSMOFIRST.NS</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="n">
+        <v>856.5</v>
+      </c>
+      <c r="F57" t="n">
+        <v>874.7999877929688</v>
+      </c>
+      <c r="G57" t="n">
+        <v>851.4500122070312</v>
+      </c>
+      <c r="H57" t="n">
+        <v>184989</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57" t="b">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="P57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>INDOCO.NS</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>235.6399993896484</v>
+      </c>
+      <c r="F58" t="n">
+        <v>246</v>
+      </c>
+      <c r="G58" t="n">
+        <v>234.1000061035156</v>
+      </c>
+      <c r="H58" t="n">
+        <v>61709</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-3.43</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-3.43</v>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" t="b">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="P58" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NACLIND.NS</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="n">
+        <v>223.6199951171875</v>
+      </c>
+      <c r="F59" t="n">
+        <v>227.8999938964844</v>
+      </c>
+      <c r="G59" t="n">
+        <v>214.4499969482422</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1767567</v>
+      </c>
+      <c r="I59" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="L59" t="b">
+        <v>0</v>
+      </c>
+      <c r="M59" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59" t="b">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="P59" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>LODHA.NS</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1095.900024414062</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1098.699951171875</v>
+      </c>
+      <c r="G60" t="n">
+        <v>1049.099975585938</v>
+      </c>
+      <c r="H60" t="n">
+        <v>6269393</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" t="b">
+        <v>0</v>
+      </c>
+      <c r="N60" t="b">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="P60" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>IBULLSLTD.NS</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" t="n">
+        <v>30.15999984741211</v>
+      </c>
+      <c r="F61" t="n">
+        <v>30.76000022888184</v>
+      </c>
+      <c r="G61" t="n">
+        <v>28.98999977111816</v>
+      </c>
+      <c r="H61" t="n">
+        <v>24537208</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K61" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" t="b">
+        <v>0</v>
+      </c>
+      <c r="N61" t="b">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="P61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>DLF.NS</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>673.2999877929688</v>
+      </c>
+      <c r="F62" t="n">
+        <v>684.2000122070312</v>
+      </c>
+      <c r="G62" t="n">
+        <v>670.0999755859375</v>
+      </c>
+      <c r="H62" t="n">
+        <v>6412136</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" t="b">
+        <v>0</v>
+      </c>
+      <c r="N62" t="b">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>16</v>
+      </c>
+      <c r="P62" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>JAGSNPHARM.NS</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>236.9299926757812</v>
+      </c>
+      <c r="F63" t="n">
+        <v>243.3999938964844</v>
+      </c>
+      <c r="G63" t="n">
+        <v>235.6100006103516</v>
+      </c>
+      <c r="H63" t="n">
+        <v>221917</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K63" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63" t="b">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="P63" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>IPCALAB.NS</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1782.400024414062</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1812.5</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1760.400024414062</v>
+      </c>
+      <c r="H64" t="n">
+        <v>393646</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K64" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="L64" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" t="b">
+        <v>0</v>
+      </c>
+      <c r="N64" t="b">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="P64" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>WEWORK.NS</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="n">
+        <v>737.1500244140625</v>
+      </c>
+      <c r="F65" t="n">
+        <v>756.6500244140625</v>
+      </c>
+      <c r="G65" t="n">
+        <v>731.0499877929688</v>
+      </c>
+      <c r="H65" t="n">
+        <v>266300</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-6.81</v>
+      </c>
+      <c r="L65" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" t="b">
+        <v>0</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="P65" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>AVG.NS</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>215.0800018310547</v>
+      </c>
+      <c r="F66" t="n">
+        <v>234.5500030517578</v>
+      </c>
+      <c r="G66" t="n">
+        <v>213.0299987792969</v>
+      </c>
+      <c r="H66" t="n">
+        <v>58190</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-4.08</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" t="b">
+        <v>0</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="P66" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD.NS</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2105.800048828125</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2118</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2030</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1840827</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K67" t="n">
+        <v>-4.83</v>
+      </c>
+      <c r="L67" t="b">
+        <v>0</v>
+      </c>
+      <c r="M67" t="b">
+        <v>0</v>
+      </c>
+      <c r="N67" t="b">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="P67" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OPTIEMUS.NS</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>522.4000244140625</v>
+      </c>
+      <c r="F68" t="n">
+        <v>538.75</v>
+      </c>
+      <c r="G68" t="n">
+        <v>512.4500122070312</v>
+      </c>
+      <c r="H68" t="n">
+        <v>292390</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K68" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="L68" t="b">
+        <v>0</v>
+      </c>
+      <c r="M68" t="b">
+        <v>0</v>
+      </c>
+      <c r="N68" t="b">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="P68" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>FUSION.NS</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>226.1900024414062</v>
+      </c>
+      <c r="F69" t="n">
+        <v>234.9799957275391</v>
+      </c>
+      <c r="G69" t="n">
+        <v>224.1999969482422</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1059909</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>-17.09</v>
+      </c>
+      <c r="L69" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69" t="b">
+        <v>0</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="P69" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SAKSOFT.NS</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" t="n">
+        <v>169.7899932861328</v>
+      </c>
+      <c r="F70" t="n">
+        <v>180.8000030517578</v>
+      </c>
+      <c r="G70" t="n">
+        <v>167</v>
+      </c>
+      <c r="H70" t="n">
+        <v>3526129</v>
+      </c>
+      <c r="I70" t="n">
+        <v>-5.13</v>
+      </c>
+      <c r="J70" t="n">
+        <v>15.49</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-5.13</v>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" t="b">
+        <v>0</v>
+      </c>
+      <c r="N70" t="b">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="P70" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PRESTIGE.NS</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>3</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1703.5</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1718.5</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1666.900024414062</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1573008</v>
+      </c>
+      <c r="I71" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K71" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="L71" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" t="b">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="P71" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>VIPULLTD.NS</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" t="n">
+        <v>14.69999980926514</v>
+      </c>
+      <c r="F72" t="n">
+        <v>15.60000038146973</v>
+      </c>
+      <c r="G72" t="n">
+        <v>14.67000007629395</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1092404</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K72" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="L72" t="b">
+        <v>0</v>
+      </c>
+      <c r="M72" t="b">
+        <v>0</v>
+      </c>
+      <c r="N72" t="b">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="P72" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM.NS</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="n">
+        <v>820.9500122070312</v>
+      </c>
+      <c r="F73" t="n">
+        <v>894.4500122070312</v>
+      </c>
+      <c r="G73" t="n">
+        <v>817.5999755859375</v>
+      </c>
+      <c r="H73" t="n">
+        <v>401695</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="L73" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73" t="b">
+        <v>0</v>
+      </c>
+      <c r="N73" t="b">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P73" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SHILPAMED.NS</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" t="n">
+        <v>596.7000122070312</v>
+      </c>
+      <c r="F74" t="n">
+        <v>611.9500122070312</v>
+      </c>
+      <c r="G74" t="n">
+        <v>593.5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>588952</v>
+      </c>
+      <c r="I74" t="n">
+        <v>-2.01</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="L74" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74" t="b">
+        <v>0</v>
+      </c>
+      <c r="N74" t="b">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="P74" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EMIL.NS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>133.9600067138672</v>
+      </c>
+      <c r="F75" t="n">
+        <v>140.6000061035156</v>
+      </c>
+      <c r="G75" t="n">
+        <v>132.3099975585938</v>
+      </c>
+      <c r="H75" t="n">
+        <v>2777351</v>
+      </c>
+      <c r="I75" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-13.47</v>
+      </c>
+      <c r="L75" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75" t="b">
+        <v>0</v>
+      </c>
+      <c r="N75" t="b">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="P75" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY.NS</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1953.400024414062</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1986.099975585938</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1946</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1591401</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K76" t="n">
+        <v>-8.539999999999999</v>
+      </c>
+      <c r="L76" t="b">
+        <v>0</v>
+      </c>
+      <c r="M76" t="b">
+        <v>0</v>
+      </c>
+      <c r="N76" t="b">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="P76" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>IKS.NS</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1877.099975585938</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1901</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1831.599975585938</v>
+      </c>
+      <c r="H77" t="n">
+        <v>304717</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-9.77</v>
+      </c>
+      <c r="L77" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77" t="b">
+        <v>0</v>
+      </c>
+      <c r="N77" t="b">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="P77" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>AADHARHFC.NS</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>3</v>
+      </c>
+      <c r="E78" t="n">
+        <v>556.5</v>
+      </c>
+      <c r="F78" t="n">
+        <v>563</v>
+      </c>
+      <c r="G78" t="n">
+        <v>550.5999755859375</v>
+      </c>
+      <c r="H78" t="n">
+        <v>725104</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K78" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="L78" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78" t="b">
+        <v>0</v>
+      </c>
+      <c r="N78" t="b">
+        <v>0</v>
+      </c>
+      <c r="O78" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="P78" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>DELHIVERY.NS</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" t="n">
+        <v>519.6500244140625</v>
+      </c>
+      <c r="F79" t="n">
+        <v>523</v>
+      </c>
+      <c r="G79" t="n">
+        <v>508.1499938964844</v>
+      </c>
+      <c r="H79" t="n">
+        <v>7200591</v>
+      </c>
+      <c r="I79" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J79" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K79" t="n">
+        <v>-6.98</v>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79" t="b">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NUVAMA.NS</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1869.400024414062</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1887.099975585938</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1846</v>
+      </c>
+      <c r="H80" t="n">
+        <v>324470</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="L80" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="P80" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RISHABH.NS</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E81" t="n">
+        <v>651</v>
+      </c>
+      <c r="F81" t="n">
+        <v>692.7999877929688</v>
+      </c>
+      <c r="G81" t="n">
+        <v>639.5</v>
+      </c>
+      <c r="H81" t="n">
+        <v>229556</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K81" t="n">
+        <v>-11.92</v>
+      </c>
+      <c r="L81" t="b">
+        <v>0</v>
+      </c>
+      <c r="M81" t="b">
+        <v>0</v>
+      </c>
+      <c r="N81" t="b">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="P81" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>VIYASH.NS</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" t="n">
+        <v>289.8500061035156</v>
+      </c>
+      <c r="F82" t="n">
+        <v>298</v>
+      </c>
+      <c r="G82" t="n">
+        <v>285.1499938964844</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1690014</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="J82" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>-5.92</v>
+      </c>
+      <c r="L82" t="b">
+        <v>0</v>
+      </c>
+      <c r="M82" t="b">
+        <v>0</v>
+      </c>
+      <c r="N82" t="b">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="P82" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG.NS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" t="n">
+        <v>626.5</v>
+      </c>
+      <c r="F83" t="n">
+        <v>641.25</v>
+      </c>
+      <c r="G83" t="n">
+        <v>611.25</v>
+      </c>
+      <c r="H83" t="n">
+        <v>267248</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J83" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K83" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="L83" t="b">
+        <v>0</v>
+      </c>
+      <c r="M83" t="b">
+        <v>0</v>
+      </c>
+      <c r="N83" t="b">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="P83" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL.NS</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" t="n">
+        <v>110.5699996948242</v>
+      </c>
+      <c r="F84" t="n">
+        <v>111.7399978637695</v>
+      </c>
+      <c r="G84" t="n">
+        <v>105.2799987792969</v>
+      </c>
+      <c r="H84" t="n">
+        <v>1561038</v>
+      </c>
+      <c r="I84" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="J84" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K84" t="n">
+        <v>-9.01</v>
+      </c>
+      <c r="L84" t="b">
+        <v>0</v>
+      </c>
+      <c r="M84" t="b">
+        <v>0</v>
+      </c>
+      <c r="N84" t="b">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>17</v>
+      </c>
+      <c r="P84" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BANSALWIRE.NS</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" t="n">
+        <v>362.6499938964844</v>
+      </c>
+      <c r="F85" t="n">
+        <v>370</v>
+      </c>
+      <c r="G85" t="n">
+        <v>357</v>
+      </c>
+      <c r="H85" t="n">
+        <v>173524</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="L85" t="b">
+        <v>0</v>
+      </c>
+      <c r="M85" t="b">
+        <v>0</v>
+      </c>
+      <c r="N85" t="b">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>19</v>
+      </c>
+      <c r="P85" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q85" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -9203,6 +11764,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -9240,7 +11802,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="7">
@@ -9250,7 +11812,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -9260,7 +11822,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>-5.43</v>
       </c>
     </row>
     <row r="9">
@@ -9270,7 +11832,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="10">
@@ -9281,10 +11843,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-05 12:32</t>
-        </is>
-      </c>
-    </row>
+          <t>2026-07-06 11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -9317,32 +11881,32 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UTKARSHBNK.NS</t>
+          <t>TARSONS.NS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>T1_HIT_ACTIVE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SETL.NS</t>
+          <t>LODHA.NS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -9353,14 +11917,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SIKA.NS</t>
+          <t>GHCLTEXTIL.NS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -9371,14 +11935,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GINNIFILA.NS</t>
+          <t>IBULLSLTD.NS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -9389,14 +11953,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HIKAL.NS</t>
+          <t>PHOENIXLTD.NS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9425,6 +11989,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -9444,7 +12009,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.47</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="5">
@@ -9464,7 +12029,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.47</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="7">
@@ -9487,7 +12052,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-05 12:32</t>
+          <t>2026-07-06 11:02</t>
         </is>
       </c>
     </row>
@@ -9512,6 +12077,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -9630,10 +12196,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-05 12:32</t>
-        </is>
-      </c>
-    </row>
+          <t>2026-07-06 11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -9668,7 +12236,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -10746,7 +13314,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-05 12:32</t>
+          <t>2026-07-06 11:02</t>
         </is>
       </c>
     </row>
@@ -11338,7 +13906,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>

--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -2809,7 +2809,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>STOPPED</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q85"/>
+  <dimension ref="A1:Q127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10741,7 +10741,7 @@
         <v>-1.4</v>
       </c>
       <c r="J69" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
         <v>-17.09</v>
@@ -10985,7 +10985,7 @@
         <v>-5.43</v>
       </c>
       <c r="J73" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>-5.43</v>
@@ -11107,7 +11107,7 @@
         <v>-4.78</v>
       </c>
       <c r="J75" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>-13.47</v>
@@ -11534,7 +11534,7 @@
         <v>-1.46</v>
       </c>
       <c r="J82" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>-5.92</v>
@@ -11717,7 +11717,7 @@
         <v>-0.86</v>
       </c>
       <c r="J85" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
         <v>-6.96</v>
@@ -11738,6 +11738,2568 @@
         <v>3</v>
       </c>
       <c r="Q85" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>UTKARSHBNK.NS</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>4</v>
+      </c>
+      <c r="E86" t="n">
+        <v>14.57999992370605</v>
+      </c>
+      <c r="F86" t="n">
+        <v>14.69999980926514</v>
+      </c>
+      <c r="G86" t="n">
+        <v>14.39999961853027</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4969338</v>
+      </c>
+      <c r="I86" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K86" t="n">
+        <v>-3.25</v>
+      </c>
+      <c r="L86" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" t="b">
+        <v>0</v>
+      </c>
+      <c r="N86" t="b">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="P86" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SETL.NS</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" t="n">
+        <v>261.0499877929688</v>
+      </c>
+      <c r="F87" t="n">
+        <v>281.0499877929688</v>
+      </c>
+      <c r="G87" t="n">
+        <v>258.0499877929688</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1713075</v>
+      </c>
+      <c r="I87" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="J87" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K87" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="L87" t="b">
+        <v>0</v>
+      </c>
+      <c r="M87" t="b">
+        <v>0</v>
+      </c>
+      <c r="N87" t="b">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="P87" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SIKA.NS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1191.199951171875</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1202.900024414062</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1130.5</v>
+      </c>
+      <c r="H88" t="n">
+        <v>191375</v>
+      </c>
+      <c r="I88" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-8.84</v>
+      </c>
+      <c r="L88" t="b">
+        <v>0</v>
+      </c>
+      <c r="M88" t="b">
+        <v>0</v>
+      </c>
+      <c r="N88" t="b">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="P88" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>GINNIFILA.NS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" t="n">
+        <v>51.61999893188477</v>
+      </c>
+      <c r="F89" t="n">
+        <v>54.79999923706055</v>
+      </c>
+      <c r="G89" t="n">
+        <v>51.09999847412109</v>
+      </c>
+      <c r="H89" t="n">
+        <v>223254</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-5.54</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>-9.42</v>
+      </c>
+      <c r="L89" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" t="b">
+        <v>0</v>
+      </c>
+      <c r="N89" t="b">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>33</v>
+      </c>
+      <c r="P89" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>HIKAL.NS</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>4</v>
+      </c>
+      <c r="E90" t="n">
+        <v>217.3999938964844</v>
+      </c>
+      <c r="F90" t="n">
+        <v>222.7899932861328</v>
+      </c>
+      <c r="G90" t="n">
+        <v>216.2100067138672</v>
+      </c>
+      <c r="H90" t="n">
+        <v>123059</v>
+      </c>
+      <c r="I90" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="L90" t="b">
+        <v>0</v>
+      </c>
+      <c r="M90" t="b">
+        <v>0</v>
+      </c>
+      <c r="N90" t="b">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="P90" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>TARSONS.NS</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>4</v>
+      </c>
+      <c r="E91" t="n">
+        <v>296.3999938964844</v>
+      </c>
+      <c r="F91" t="n">
+        <v>304</v>
+      </c>
+      <c r="G91" t="n">
+        <v>277.25</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2050654</v>
+      </c>
+      <c r="I91" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="J91" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="K91" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="L91" t="b">
+        <v>0</v>
+      </c>
+      <c r="M91" t="b">
+        <v>0</v>
+      </c>
+      <c r="N91" t="b">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="P91" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MUTHOOTMF.NS</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>4</v>
+      </c>
+      <c r="E92" t="n">
+        <v>213.4100036621094</v>
+      </c>
+      <c r="F92" t="n">
+        <v>217.4499969482422</v>
+      </c>
+      <c r="G92" t="n">
+        <v>210.3099975585938</v>
+      </c>
+      <c r="H92" t="n">
+        <v>150219</v>
+      </c>
+      <c r="I92" t="n">
+        <v>-3.64</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>-3.64</v>
+      </c>
+      <c r="L92" t="b">
+        <v>0</v>
+      </c>
+      <c r="M92" t="b">
+        <v>0</v>
+      </c>
+      <c r="N92" t="b">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="P92" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>AEQUS.NS</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>4</v>
+      </c>
+      <c r="E93" t="n">
+        <v>242.4299926757812</v>
+      </c>
+      <c r="F93" t="n">
+        <v>246.6600036621094</v>
+      </c>
+      <c r="G93" t="n">
+        <v>232.2400054931641</v>
+      </c>
+      <c r="H93" t="n">
+        <v>23357977</v>
+      </c>
+      <c r="I93" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="J93" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="K93" t="n">
+        <v>-2.58</v>
+      </c>
+      <c r="L93" t="b">
+        <v>0</v>
+      </c>
+      <c r="M93" t="b">
+        <v>0</v>
+      </c>
+      <c r="N93" t="b">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="P93" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>GODREJPROP.NS</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>4</v>
+      </c>
+      <c r="E94" t="n">
+        <v>2043.099975585938</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2061.800048828125</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2009</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1055434</v>
+      </c>
+      <c r="I94" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J94" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K94" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="L94" t="b">
+        <v>0</v>
+      </c>
+      <c r="M94" t="b">
+        <v>0</v>
+      </c>
+      <c r="N94" t="b">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="P94" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>LTF.NS</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>4</v>
+      </c>
+      <c r="E95" t="n">
+        <v>334.2000122070312</v>
+      </c>
+      <c r="F95" t="n">
+        <v>338.6000061035156</v>
+      </c>
+      <c r="G95" t="n">
+        <v>331.1499938964844</v>
+      </c>
+      <c r="H95" t="n">
+        <v>4054003</v>
+      </c>
+      <c r="I95" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J95" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="K95" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="L95" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" t="b">
+        <v>0</v>
+      </c>
+      <c r="N95" t="b">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>17</v>
+      </c>
+      <c r="P95" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>AMAGI.NS</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>4</v>
+      </c>
+      <c r="E96" t="n">
+        <v>534</v>
+      </c>
+      <c r="F96" t="n">
+        <v>548.9500122070312</v>
+      </c>
+      <c r="G96" t="n">
+        <v>522.9000244140625</v>
+      </c>
+      <c r="H96" t="n">
+        <v>365384</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K96" t="n">
+        <v>-1.82</v>
+      </c>
+      <c r="L96" t="b">
+        <v>0</v>
+      </c>
+      <c r="M96" t="b">
+        <v>0</v>
+      </c>
+      <c r="N96" t="b">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="P96" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CREDITACC.NS</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>4</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1582.199951171875</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1599</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1547.300048828125</v>
+      </c>
+      <c r="H97" t="n">
+        <v>402703</v>
+      </c>
+      <c r="I97" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="K97" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="L97" t="b">
+        <v>0</v>
+      </c>
+      <c r="M97" t="b">
+        <v>0</v>
+      </c>
+      <c r="N97" t="b">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="P97" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>APLLTD.NS</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>4</v>
+      </c>
+      <c r="E98" t="n">
+        <v>829.3499755859375</v>
+      </c>
+      <c r="F98" t="n">
+        <v>841.9500122070312</v>
+      </c>
+      <c r="G98" t="n">
+        <v>824.2999877929688</v>
+      </c>
+      <c r="H98" t="n">
+        <v>81542</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="K98" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="L98" t="b">
+        <v>0</v>
+      </c>
+      <c r="M98" t="b">
+        <v>0</v>
+      </c>
+      <c r="N98" t="b">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="P98" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>COSMOFIRST.NS</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>4</v>
+      </c>
+      <c r="E99" t="n">
+        <v>852.9500122070312</v>
+      </c>
+      <c r="F99" t="n">
+        <v>866.4500122070312</v>
+      </c>
+      <c r="G99" t="n">
+        <v>850</v>
+      </c>
+      <c r="H99" t="n">
+        <v>106645</v>
+      </c>
+      <c r="I99" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K99" t="n">
+        <v>-6.92</v>
+      </c>
+      <c r="L99" t="b">
+        <v>0</v>
+      </c>
+      <c r="M99" t="b">
+        <v>0</v>
+      </c>
+      <c r="N99" t="b">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="P99" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>INDOCO.NS</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>4</v>
+      </c>
+      <c r="E100" t="n">
+        <v>240.6199951171875</v>
+      </c>
+      <c r="F100" t="n">
+        <v>247.8000030517578</v>
+      </c>
+      <c r="G100" t="n">
+        <v>235.2700042724609</v>
+      </c>
+      <c r="H100" t="n">
+        <v>211550</v>
+      </c>
+      <c r="I100" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K100" t="n">
+        <v>-3.43</v>
+      </c>
+      <c r="L100" t="b">
+        <v>0</v>
+      </c>
+      <c r="M100" t="b">
+        <v>0</v>
+      </c>
+      <c r="N100" t="b">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="P100" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>NACLIND.NS</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>4</v>
+      </c>
+      <c r="E101" t="n">
+        <v>220.0299987792969</v>
+      </c>
+      <c r="F101" t="n">
+        <v>226.4400024414062</v>
+      </c>
+      <c r="G101" t="n">
+        <v>216.2200012207031</v>
+      </c>
+      <c r="H101" t="n">
+        <v>611769</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K101" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="L101" t="b">
+        <v>0</v>
+      </c>
+      <c r="M101" t="b">
+        <v>0</v>
+      </c>
+      <c r="N101" t="b">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="P101" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>LODHA.NS</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>4</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1102.550048828125</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1107.599975585938</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1086.199951171875</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2537815</v>
+      </c>
+      <c r="I102" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="J102" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="K102" t="n">
+        <v>-6.12</v>
+      </c>
+      <c r="L102" t="b">
+        <v>0</v>
+      </c>
+      <c r="M102" t="b">
+        <v>0</v>
+      </c>
+      <c r="N102" t="b">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>17</v>
+      </c>
+      <c r="P102" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>IBULLSLTD.NS</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>4</v>
+      </c>
+      <c r="E103" t="n">
+        <v>29.04999923706055</v>
+      </c>
+      <c r="F103" t="n">
+        <v>30.60000038146973</v>
+      </c>
+      <c r="G103" t="n">
+        <v>28.65999984741211</v>
+      </c>
+      <c r="H103" t="n">
+        <v>12483447</v>
+      </c>
+      <c r="I103" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="J103" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K103" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="L103" t="b">
+        <v>0</v>
+      </c>
+      <c r="M103" t="b">
+        <v>0</v>
+      </c>
+      <c r="N103" t="b">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="P103" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>DLF.NS</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>4</v>
+      </c>
+      <c r="E104" t="n">
+        <v>651.0999755859375</v>
+      </c>
+      <c r="F104" t="n">
+        <v>673.2999877929688</v>
+      </c>
+      <c r="G104" t="n">
+        <v>649.9000244140625</v>
+      </c>
+      <c r="H104" t="n">
+        <v>5693501</v>
+      </c>
+      <c r="I104" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="L104" t="b">
+        <v>0</v>
+      </c>
+      <c r="M104" t="b">
+        <v>0</v>
+      </c>
+      <c r="N104" t="b">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>20</v>
+      </c>
+      <c r="P104" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>JAGSNPHARM.NS</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>4</v>
+      </c>
+      <c r="E105" t="n">
+        <v>238.7200012207031</v>
+      </c>
+      <c r="F105" t="n">
+        <v>244.3999938964844</v>
+      </c>
+      <c r="G105" t="n">
+        <v>229.1000061035156</v>
+      </c>
+      <c r="H105" t="n">
+        <v>214992</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K105" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="L105" t="b">
+        <v>0</v>
+      </c>
+      <c r="M105" t="b">
+        <v>0</v>
+      </c>
+      <c r="N105" t="b">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="P105" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>IPCALAB.NS</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>4</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1793.099975585938</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1767.5</v>
+      </c>
+      <c r="H106" t="n">
+        <v>139834</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K106" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="L106" t="b">
+        <v>0</v>
+      </c>
+      <c r="M106" t="b">
+        <v>0</v>
+      </c>
+      <c r="N106" t="b">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="P106" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>WEWORK.NS</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>4</v>
+      </c>
+      <c r="E107" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="F107" t="n">
+        <v>767</v>
+      </c>
+      <c r="G107" t="n">
+        <v>732.2999877929688</v>
+      </c>
+      <c r="H107" t="n">
+        <v>688761</v>
+      </c>
+      <c r="I107" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="L107" t="b">
+        <v>0</v>
+      </c>
+      <c r="M107" t="b">
+        <v>0</v>
+      </c>
+      <c r="N107" t="b">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="P107" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>AVG.NS</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>4</v>
+      </c>
+      <c r="E108" t="n">
+        <v>204.3300018310547</v>
+      </c>
+      <c r="F108" t="n">
+        <v>212</v>
+      </c>
+      <c r="G108" t="n">
+        <v>204.3300018310547</v>
+      </c>
+      <c r="H108" t="n">
+        <v>40917</v>
+      </c>
+      <c r="I108" t="n">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="L108" t="b">
+        <v>0</v>
+      </c>
+      <c r="M108" t="b">
+        <v>0</v>
+      </c>
+      <c r="N108" t="b">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="P108" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD.NS</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>4</v>
+      </c>
+      <c r="E109" t="n">
+        <v>2075.10009765625</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2134.699951171875</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2056.10009765625</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2598961</v>
+      </c>
+      <c r="I109" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="J109" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K109" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="L109" t="b">
+        <v>0</v>
+      </c>
+      <c r="M109" t="b">
+        <v>0</v>
+      </c>
+      <c r="N109" t="b">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="P109" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>OPTIEMUS.NS</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>4</v>
+      </c>
+      <c r="E110" t="n">
+        <v>520.7999877929688</v>
+      </c>
+      <c r="F110" t="n">
+        <v>525.75</v>
+      </c>
+      <c r="G110" t="n">
+        <v>512.0999755859375</v>
+      </c>
+      <c r="H110" t="n">
+        <v>155491</v>
+      </c>
+      <c r="I110" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K110" t="n">
+        <v>-6.93</v>
+      </c>
+      <c r="L110" t="b">
+        <v>0</v>
+      </c>
+      <c r="M110" t="b">
+        <v>0</v>
+      </c>
+      <c r="N110" t="b">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="P110" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>FUSION.NS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>4</v>
+      </c>
+      <c r="E111" t="n">
+        <v>226.0200042724609</v>
+      </c>
+      <c r="F111" t="n">
+        <v>228.8500061035156</v>
+      </c>
+      <c r="G111" t="n">
+        <v>220.4199981689453</v>
+      </c>
+      <c r="H111" t="n">
+        <v>613964</v>
+      </c>
+      <c r="I111" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="J111" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>-11.11</v>
+      </c>
+      <c r="L111" t="b">
+        <v>0</v>
+      </c>
+      <c r="M111" t="b">
+        <v>0</v>
+      </c>
+      <c r="N111" t="b">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="P111" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SAKSOFT.NS</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>4</v>
+      </c>
+      <c r="E112" t="n">
+        <v>176.6000061035156</v>
+      </c>
+      <c r="F112" t="n">
+        <v>186.7599945068359</v>
+      </c>
+      <c r="G112" t="n">
+        <v>170</v>
+      </c>
+      <c r="H112" t="n">
+        <v>8227797</v>
+      </c>
+      <c r="I112" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="J112" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="K112" t="n">
+        <v>-5.13</v>
+      </c>
+      <c r="L112" t="b">
+        <v>0</v>
+      </c>
+      <c r="M112" t="b">
+        <v>0</v>
+      </c>
+      <c r="N112" t="b">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>33</v>
+      </c>
+      <c r="P112" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>PRESTIGE.NS</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1673.300048828125</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1715</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1659.400024414062</v>
+      </c>
+      <c r="H113" t="n">
+        <v>1493032</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K113" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="L113" t="b">
+        <v>0</v>
+      </c>
+      <c r="M113" t="b">
+        <v>0</v>
+      </c>
+      <c r="N113" t="b">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>16</v>
+      </c>
+      <c r="P113" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>VIPULLTD.NS</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>4</v>
+      </c>
+      <c r="E114" t="n">
+        <v>15.42000007629395</v>
+      </c>
+      <c r="F114" t="n">
+        <v>15.43000030517578</v>
+      </c>
+      <c r="G114" t="n">
+        <v>13.97000026702881</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2259301</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K114" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="L114" t="b">
+        <v>0</v>
+      </c>
+      <c r="M114" t="b">
+        <v>0</v>
+      </c>
+      <c r="N114" t="b">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="P114" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM.NS</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>4</v>
+      </c>
+      <c r="E115" t="n">
+        <v>810.9500122070312</v>
+      </c>
+      <c r="F115" t="n">
+        <v>837.0499877929688</v>
+      </c>
+      <c r="G115" t="n">
+        <v>788.3499755859375</v>
+      </c>
+      <c r="H115" t="n">
+        <v>236115</v>
+      </c>
+      <c r="I115" t="n">
+        <v>-6.58</v>
+      </c>
+      <c r="J115" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>-6.58</v>
+      </c>
+      <c r="L115" t="b">
+        <v>0</v>
+      </c>
+      <c r="M115" t="b">
+        <v>0</v>
+      </c>
+      <c r="N115" t="b">
+        <v>1</v>
+      </c>
+      <c r="O115" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="P115" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>STOPPED</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SHILPAMED.NS</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>4</v>
+      </c>
+      <c r="E116" t="n">
+        <v>599.7999877929688</v>
+      </c>
+      <c r="F116" t="n">
+        <v>603.2000122070312</v>
+      </c>
+      <c r="G116" t="n">
+        <v>589.5</v>
+      </c>
+      <c r="H116" t="n">
+        <v>392930</v>
+      </c>
+      <c r="I116" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>-6.27</v>
+      </c>
+      <c r="L116" t="b">
+        <v>0</v>
+      </c>
+      <c r="M116" t="b">
+        <v>0</v>
+      </c>
+      <c r="N116" t="b">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="P116" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>EMIL.NS</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" t="n">
+        <v>133.7100067138672</v>
+      </c>
+      <c r="F117" t="n">
+        <v>136.0599975585938</v>
+      </c>
+      <c r="G117" t="n">
+        <v>132.6000061035156</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1058530</v>
+      </c>
+      <c r="I117" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="J117" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="L117" t="b">
+        <v>0</v>
+      </c>
+      <c r="M117" t="b">
+        <v>0</v>
+      </c>
+      <c r="N117" t="b">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="P117" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY.NS</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1906.400024414062</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1968.400024414062</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1902.099975585938</v>
+      </c>
+      <c r="H118" t="n">
+        <v>930375</v>
+      </c>
+      <c r="I118" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="K118" t="n">
+        <v>-6.71</v>
+      </c>
+      <c r="L118" t="b">
+        <v>0</v>
+      </c>
+      <c r="M118" t="b">
+        <v>0</v>
+      </c>
+      <c r="N118" t="b">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="P118" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>IKS.NS</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>4</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1890.5</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1898.800048828125</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1832</v>
+      </c>
+      <c r="H119" t="n">
+        <v>354680</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="K119" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="L119" t="b">
+        <v>0</v>
+      </c>
+      <c r="M119" t="b">
+        <v>0</v>
+      </c>
+      <c r="N119" t="b">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="P119" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>AADHARHFC.NS</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>4</v>
+      </c>
+      <c r="E120" t="n">
+        <v>545.7999877929688</v>
+      </c>
+      <c r="F120" t="n">
+        <v>554</v>
+      </c>
+      <c r="G120" t="n">
+        <v>540.25</v>
+      </c>
+      <c r="H120" t="n">
+        <v>388701</v>
+      </c>
+      <c r="I120" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K120" t="n">
+        <v>-6.81</v>
+      </c>
+      <c r="L120" t="b">
+        <v>0</v>
+      </c>
+      <c r="M120" t="b">
+        <v>0</v>
+      </c>
+      <c r="N120" t="b">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="P120" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>DELHIVERY.NS</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>4</v>
+      </c>
+      <c r="E121" t="n">
+        <v>517.9000244140625</v>
+      </c>
+      <c r="F121" t="n">
+        <v>522.5999755859375</v>
+      </c>
+      <c r="G121" t="n">
+        <v>513.0499877929688</v>
+      </c>
+      <c r="H121" t="n">
+        <v>5629181</v>
+      </c>
+      <c r="I121" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="J121" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="b">
+        <v>0</v>
+      </c>
+      <c r="M121" t="b">
+        <v>0</v>
+      </c>
+      <c r="N121" t="b">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="P121" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NUVAMA.NS</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>4</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1917.099975585938</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1927.800048828125</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1860.099975585938</v>
+      </c>
+      <c r="H122" t="n">
+        <v>482265</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="K122" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="L122" t="b">
+        <v>0</v>
+      </c>
+      <c r="M122" t="b">
+        <v>0</v>
+      </c>
+      <c r="N122" t="b">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>13</v>
+      </c>
+      <c r="P122" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>RISHABH.NS</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>4</v>
+      </c>
+      <c r="E123" t="n">
+        <v>629.5999755859375</v>
+      </c>
+      <c r="F123" t="n">
+        <v>660.7000122070312</v>
+      </c>
+      <c r="G123" t="n">
+        <v>617.4500122070312</v>
+      </c>
+      <c r="H123" t="n">
+        <v>231143</v>
+      </c>
+      <c r="I123" t="n">
+        <v>-3.06</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K123" t="n">
+        <v>-9.949999999999999</v>
+      </c>
+      <c r="L123" t="b">
+        <v>0</v>
+      </c>
+      <c r="M123" t="b">
+        <v>0</v>
+      </c>
+      <c r="N123" t="b">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="P123" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>VIYASH.NS</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>4</v>
+      </c>
+      <c r="E124" t="n">
+        <v>278.8999938964844</v>
+      </c>
+      <c r="F124" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="G124" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1666869</v>
+      </c>
+      <c r="I124" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="J124" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>-5.18</v>
+      </c>
+      <c r="L124" t="b">
+        <v>0</v>
+      </c>
+      <c r="M124" t="b">
+        <v>0</v>
+      </c>
+      <c r="N124" t="b">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="P124" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG.NS</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>4</v>
+      </c>
+      <c r="E125" t="n">
+        <v>636.3499755859375</v>
+      </c>
+      <c r="F125" t="n">
+        <v>639.5999755859375</v>
+      </c>
+      <c r="G125" t="n">
+        <v>617.5499877929688</v>
+      </c>
+      <c r="H125" t="n">
+        <v>71145</v>
+      </c>
+      <c r="I125" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="J125" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="b">
+        <v>0</v>
+      </c>
+      <c r="M125" t="b">
+        <v>0</v>
+      </c>
+      <c r="N125" t="b">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="P125" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL.NS</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>4</v>
+      </c>
+      <c r="E126" t="n">
+        <v>110.7200012207031</v>
+      </c>
+      <c r="F126" t="n">
+        <v>113</v>
+      </c>
+      <c r="G126" t="n">
+        <v>107.6500015258789</v>
+      </c>
+      <c r="H126" t="n">
+        <v>974234</v>
+      </c>
+      <c r="I126" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="J126" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-9.01</v>
+      </c>
+      <c r="L126" t="b">
+        <v>0</v>
+      </c>
+      <c r="M126" t="b">
+        <v>0</v>
+      </c>
+      <c r="N126" t="b">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="P126" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BANSALWIRE.NS</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>4</v>
+      </c>
+      <c r="E127" t="n">
+        <v>354.1499938964844</v>
+      </c>
+      <c r="F127" t="n">
+        <v>365.6499938964844</v>
+      </c>
+      <c r="G127" t="n">
+        <v>352</v>
+      </c>
+      <c r="H127" t="n">
+        <v>102740</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-3.18</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="L127" t="b">
+        <v>0</v>
+      </c>
+      <c r="M127" t="b">
+        <v>0</v>
+      </c>
+      <c r="N127" t="b">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="P127" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q127" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -11802,7 +14364,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.29</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="7">
@@ -11812,7 +14374,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="8">
@@ -11822,7 +14384,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-5.43</v>
+        <v>-8.880000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -11832,7 +14394,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.08</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="10">
@@ -11843,7 +14405,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-06 11:02</t>
+          <t>2026-07-07 11:02</t>
         </is>
       </c>
     </row>
@@ -11885,14 +14447,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>9.960000000000001</v>
+        <v>11.18</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>T1_HIT_ACTIVE</t>
+          <t>ACTIVE</t>
         </is>
       </c>
     </row>
@@ -11903,10 +14465,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>3.68</v>
+        <v>4.31</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -11921,10 +14483,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -11935,14 +14497,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IBULLSLTD.NS</t>
+          <t>AEQUS.NS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>2.94</v>
+        <v>2.49</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -11953,14 +14515,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PHOENIXLTD.NS</t>
+          <t>GODREJPROP.NS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>2.84</v>
+        <v>2.34</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -12009,7 +14571,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.05</v>
+        <v>-4.17</v>
       </c>
     </row>
     <row r="5">
@@ -12019,7 +14581,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-6.58</v>
       </c>
     </row>
     <row r="6">
@@ -12029,7 +14591,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.05</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="7">
@@ -12040,7 +14602,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>✓ Positive alpha</t>
+          <t>⚠ Near-benchmark</t>
         </is>
       </c>
     </row>
@@ -12052,7 +14614,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-06 11:02</t>
+          <t>2026-07-07 11:02</t>
         </is>
       </c>
     </row>
@@ -12067,7 +14629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12095,7 +14657,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>500000</v>
+        <v>498355</v>
       </c>
     </row>
     <row r="5">
@@ -12105,7 +14667,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-1645</v>
       </c>
     </row>
     <row r="6">
@@ -12115,7 +14677,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="7">
@@ -12125,7 +14687,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -12175,7 +14737,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="13">
@@ -12196,7 +14758,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-06 11:02</t>
+          <t>2026-07-07 11:02</t>
         </is>
       </c>
     </row>
@@ -12222,6 +14784,22 @@
         <is>
           <t>Equity (₹)</t>
         </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>-6.58</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-1645</v>
+      </c>
+      <c r="D18" t="n">
+        <v>498355</v>
       </c>
     </row>
   </sheetData>
@@ -13141,7 +15719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13173,7 +15751,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -13183,7 +15761,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -13213,7 +15791,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>-6.58</v>
       </c>
     </row>
     <row r="8">
@@ -13233,7 +15811,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>-6.58</v>
       </c>
     </row>
     <row r="10">
@@ -13273,7 +15851,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>-6.58</v>
       </c>
     </row>
     <row r="14">
@@ -13303,7 +15881,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -13314,7 +15892,108 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-06 11:02</t>
+          <t>2026-07-07 11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>── P&amp;L Attribution ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Exit bucket</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Avg Return %</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>% of trades</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T2_HIT</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RUNNER_STOPPED</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STOPPED</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-6.58</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>

--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -1,36 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily Tracking" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Performance Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Confidence Analysis" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sector Analysis" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Regime Analysis" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Monthly Report" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Weekday Analysis" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Holding Period Analysis" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Category Comparison" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Conf x TQ Matrix" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Catalyst Analysis" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Fail Reason Analysis" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Regime x Sector" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Confidence Trajectory" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Delivery Flow" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Sector Rotation" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Portfolio Metrics" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Backtest vs Live" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Portfolio Risk" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Benchmark" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Equity Curve" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Weekly Factor Summary" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Rejected" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Tracking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence Analysis" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector Analysis" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regime Analysis" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Report" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekday Analysis" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holding Period Analysis" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Comparison" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conf x TQ Matrix" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalyst Analysis" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fail Reason Analysis" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regime x Sector" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence Trajectory" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Delivery Flow" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector Rotation" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Metrics" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest vs Live" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Risk" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity Curve" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Factor Summary" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:T76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6029,6 +6029,166 @@
         </is>
       </c>
       <c r="T74" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GANESHHOU.NS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>GANESHHOU</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NEAR_MISS</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="F75" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I75" t="n">
+        <v>845.2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>750.51</v>
+      </c>
+      <c r="K75" t="n">
+        <v>912.83</v>
+      </c>
+      <c r="L75" t="n">
+        <v>987.24</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>RR_FAIL(got 1.42, need 2.0)</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ARKADE.NS</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ARKADE</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NEAR_MISS</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="F76" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="G76" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I76" t="n">
+        <v>131.06</v>
+      </c>
+      <c r="J76" t="n">
+        <v>118.75</v>
+      </c>
+      <c r="K76" t="n">
+        <v>140.29</v>
+      </c>
+      <c r="L76" t="n">
+        <v>149.52</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 76.0, need 80), RR_FAIL(got 1.28, need 2.0)</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
@@ -15624,7 +15784,7 @@
         <v>-1.47</v>
       </c>
       <c r="J111" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
         <v>-11.11</v>
@@ -15868,7 +16028,7 @@
         <v>-6.58</v>
       </c>
       <c r="J115" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
         <v>-6.58</v>
@@ -15990,7 +16150,7 @@
         <v>-4.95</v>
       </c>
       <c r="J117" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
         <v>-9.140000000000001</v>
@@ -16417,7 +16577,7 @@
         <v>-5.18</v>
       </c>
       <c r="J124" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
         <v>-5.18</v>
@@ -16600,7 +16760,7 @@
         <v>-3.18</v>
       </c>
       <c r="J127" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
         <v>-5.88</v>
@@ -18538,7 +18698,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -18621,8 +18780,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -18763,7 +18920,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -18851,7 +19007,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -18974,8 +19129,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -19026,7 +19179,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -19931,7 +20084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T90"/>
+  <dimension ref="A1:T208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26706,6 +26859,9446 @@
         </is>
       </c>
       <c r="T90" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>PANAMAPET.NS</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>PANAMAPET</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="E91" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="F91" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="H91" t="n">
+        <v>433.2</v>
+      </c>
+      <c r="I91" t="n">
+        <v>396.21</v>
+      </c>
+      <c r="J91" t="n">
+        <v>504.46</v>
+      </c>
+      <c r="K91" t="n">
+        <v>575.72</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>TQ_FAIL(got 61.3, need 73), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>TSFINV.NS</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TSFINV</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="E92" t="n">
+        <v>87.64</v>
+      </c>
+      <c r="F92" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H92" t="n">
+        <v>461.95</v>
+      </c>
+      <c r="I92" t="n">
+        <v>407.43</v>
+      </c>
+      <c r="J92" t="n">
+        <v>500.89</v>
+      </c>
+      <c r="K92" t="n">
+        <v>543.73</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(8.2%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>QUESS.NS</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>QUESS</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="E93" t="n">
+        <v>86.05</v>
+      </c>
+      <c r="F93" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H93" t="n">
+        <v>299.25</v>
+      </c>
+      <c r="I93" t="n">
+        <v>261.47</v>
+      </c>
+      <c r="J93" t="n">
+        <v>326.23</v>
+      </c>
+      <c r="K93" t="n">
+        <v>355.92</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>TQ_FAIL(got 57.1, need 73), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>UNITDSPR.NS</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E94" t="n">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="F94" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1439.4</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1324.25</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1519.78</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1612.13</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>TQ_FAIL(got 65.5, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>POLYPLEX.NS</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>POLYPLEX</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="E95" t="n">
+        <v>84.77</v>
+      </c>
+      <c r="F95" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1025.05</v>
+      </c>
+      <c r="I95" t="n">
+        <v>945.45</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1122.6</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1220.16</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(1.1%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>CANFINHOME.NS</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>CANFINHOME</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="E96" t="n">
+        <v>84.59</v>
+      </c>
+      <c r="F96" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H96" t="n">
+        <v>909.8</v>
+      </c>
+      <c r="I96" t="n">
+        <v>822.49</v>
+      </c>
+      <c r="J96" t="n">
+        <v>972.17</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1040.76</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="P96" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>UPTREND, DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>TQ_FAIL(got 63.2, need 73), RR_FAIL(got 1.40, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>HDFCAMC.NS</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>71</v>
+      </c>
+      <c r="E97" t="n">
+        <v>84.28</v>
+      </c>
+      <c r="F97" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2783.4</v>
+      </c>
+      <c r="I97" t="n">
+        <v>2581.43</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2931.77</v>
+      </c>
+      <c r="K97" t="n">
+        <v>3086.36</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>TQ_FAIL(got 65.2, need 73), RR_FAIL(got 1.40, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG.NS</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TTKPRESTIG</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="E98" t="n">
+        <v>84.06</v>
+      </c>
+      <c r="F98" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="G98" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H98" t="n">
+        <v>636.35</v>
+      </c>
+      <c r="I98" t="n">
+        <v>550.37</v>
+      </c>
+      <c r="J98" t="n">
+        <v>697.76</v>
+      </c>
+      <c r="K98" t="n">
+        <v>765.3200000000001</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>TQ_FAIL(got 64.9, need 73), RR_FAIL(got 1.39, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>JBCHEPHARM.NS</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>JBCHEPHARM</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="E99" t="n">
+        <v>83.80500000000001</v>
+      </c>
+      <c r="F99" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G99" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2422</v>
+      </c>
+      <c r="I99" t="n">
+        <v>2228.24</v>
+      </c>
+      <c r="J99" t="n">
+        <v>2533.84</v>
+      </c>
+      <c r="K99" t="n">
+        <v>2712.64</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>HEALTHCARE</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=18&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>GRANULES.NS</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="E100" t="n">
+        <v>83.36500000000001</v>
+      </c>
+      <c r="F100" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H100" t="n">
+        <v>863.55</v>
+      </c>
+      <c r="I100" t="n">
+        <v>773.9400000000001</v>
+      </c>
+      <c r="J100" t="n">
+        <v>927.5599999999999</v>
+      </c>
+      <c r="K100" t="n">
+        <v>997.96</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=15&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>TEXINFRA.NS</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>TEXINFRA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="E101" t="n">
+        <v>83.31</v>
+      </c>
+      <c r="F101" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="G101" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H101" t="n">
+        <v>115.18</v>
+      </c>
+      <c r="I101" t="n">
+        <v>105.97</v>
+      </c>
+      <c r="J101" t="n">
+        <v>125.23</v>
+      </c>
+      <c r="K101" t="n">
+        <v>135.28</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(0.9%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>DLF.NS</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="E102" t="n">
+        <v>83.12</v>
+      </c>
+      <c r="F102" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H102" t="n">
+        <v>651.1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>605.61</v>
+      </c>
+      <c r="J102" t="n">
+        <v>689.84</v>
+      </c>
+      <c r="K102" t="n">
+        <v>728.58</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(9.6%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>GCSL.NS</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>GCSL</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="E103" t="n">
+        <v>83.03</v>
+      </c>
+      <c r="F103" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="G103" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H103" t="n">
+        <v>486.1</v>
+      </c>
+      <c r="I103" t="n">
+        <v>429.4</v>
+      </c>
+      <c r="J103" t="n">
+        <v>526.6</v>
+      </c>
+      <c r="K103" t="n">
+        <v>571.15</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(8.6%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>FIVESTAR.NS</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>FIVESTAR</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="E104" t="n">
+        <v>82.55</v>
+      </c>
+      <c r="F104" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="G104" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H104" t="n">
+        <v>548.55</v>
+      </c>
+      <c r="I104" t="n">
+        <v>479.42</v>
+      </c>
+      <c r="J104" t="n">
+        <v>597.9299999999999</v>
+      </c>
+      <c r="K104" t="n">
+        <v>652.24</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>16</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>TQ_FAIL(got 58.4, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>RAYMOND.NS</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="E105" t="n">
+        <v>82.11</v>
+      </c>
+      <c r="F105" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H105" t="n">
+        <v>610.35</v>
+      </c>
+      <c r="I105" t="n">
+        <v>575.36</v>
+      </c>
+      <c r="J105" t="n">
+        <v>650.74</v>
+      </c>
+      <c r="K105" t="n">
+        <v>691.14</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>TEXTILES</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>168</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>TQ_FAIL(got 70.8, need 73), SECTOR_RANK_TOO_LOW(rank=26&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>EXIDEIND.NS</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="E106" t="n">
+        <v>81.97</v>
+      </c>
+      <c r="F106" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H106" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="I106" t="n">
+        <v>374.02</v>
+      </c>
+      <c r="J106" t="n">
+        <v>444.24</v>
+      </c>
+      <c r="K106" t="n">
+        <v>475.22</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(6.0%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>PNBHOUSING.NS</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>PNBHOUSING</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="E107" t="n">
+        <v>81.73999999999999</v>
+      </c>
+      <c r="F107" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G107" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1109.7</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1019.2</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1174.34</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1245.45</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="P107" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH(2.77&gt;1.50)</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>JAMNAAUTO.NS</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>JAMNAAUTO</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="E108" t="n">
+        <v>81.44</v>
+      </c>
+      <c r="F108" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H108" t="n">
+        <v>135.38</v>
+      </c>
+      <c r="I108" t="n">
+        <v>128.51</v>
+      </c>
+      <c r="J108" t="n">
+        <v>143.62</v>
+      </c>
+      <c r="K108" t="n">
+        <v>151.87</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>TQ_FAIL(got 66.8, need 73), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SKMEGGPROD.NS</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SKMEGGPROD</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="E109" t="n">
+        <v>81.18000000000001</v>
+      </c>
+      <c r="F109" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H109" t="n">
+        <v>310.55</v>
+      </c>
+      <c r="I109" t="n">
+        <v>263.97</v>
+      </c>
+      <c r="J109" t="n">
+        <v>352.62</v>
+      </c>
+      <c r="K109" t="n">
+        <v>394.68</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>TQ_FAIL(got 50.6, need 73), RR_FAIL(got 1.73, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>PATELRMART.NS</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PATELRMART</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="E110" t="n">
+        <v>80.98999999999999</v>
+      </c>
+      <c r="F110" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H110" t="n">
+        <v>223.66</v>
+      </c>
+      <c r="I110" t="n">
+        <v>206.87</v>
+      </c>
+      <c r="J110" t="n">
+        <v>245.19</v>
+      </c>
+      <c r="K110" t="n">
+        <v>266.72</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>TQ_FAIL(got 68.5, need 73), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>EPL.NS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>EPL</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>73</v>
+      </c>
+      <c r="E111" t="n">
+        <v>80.97</v>
+      </c>
+      <c r="F111" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H111" t="n">
+        <v>245.09</v>
+      </c>
+      <c r="I111" t="n">
+        <v>224.04</v>
+      </c>
+      <c r="J111" t="n">
+        <v>260.13</v>
+      </c>
+      <c r="K111" t="n">
+        <v>276.67</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>RR_FAIL(got 1.39, need 2.0), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>MUNJALAU.NS</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>MUNJALAU</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="E112" t="n">
+        <v>80.43000000000001</v>
+      </c>
+      <c r="F112" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="G112" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H112" t="n">
+        <v>103.94</v>
+      </c>
+      <c r="I112" t="n">
+        <v>90.27</v>
+      </c>
+      <c r="J112" t="n">
+        <v>115.57</v>
+      </c>
+      <c r="K112" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(8.2%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RADICO.NS</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="E113" t="n">
+        <v>80.265</v>
+      </c>
+      <c r="F113" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="G113" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H113" t="n">
+        <v>4098.6</v>
+      </c>
+      <c r="I113" t="n">
+        <v>3750.53</v>
+      </c>
+      <c r="J113" t="n">
+        <v>4347.22</v>
+      </c>
+      <c r="K113" t="n">
+        <v>4620.71</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>AGRI_FOOD</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_DOWN, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>TQ_FAIL(got 69.7, need 73), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=9&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CREDITACC.NS</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CREDITACC</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="E114" t="n">
+        <v>79.97</v>
+      </c>
+      <c r="F114" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1582.2</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1413.05</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1703.02</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1835.93</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="P114" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 80.0, need 80), TQ_FAIL(got 66.9, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>STYL.NS</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>STYL</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="E115" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="F115" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="G115" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H115" t="n">
+        <v>347.75</v>
+      </c>
+      <c r="I115" t="n">
+        <v>303.87</v>
+      </c>
+      <c r="J115" t="n">
+        <v>379.09</v>
+      </c>
+      <c r="K115" t="n">
+        <v>413.57</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 79.9, need 80), TQ_FAIL(got 71.2, need 73), RR_FAIL(got 1.39, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>360ONE.NS</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="E116" t="n">
+        <v>79.75</v>
+      </c>
+      <c r="F116" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="G116" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H116" t="n">
+        <v>1150.1</v>
+      </c>
+      <c r="I116" t="n">
+        <v>1056.4</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1217.03</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1290.65</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 79.8, need 80), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>AGI.NS</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>AGI</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="E117" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="F117" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>709.15</v>
+      </c>
+      <c r="I117" t="n">
+        <v>670.6799999999999</v>
+      </c>
+      <c r="J117" t="n">
+        <v>753.8</v>
+      </c>
+      <c r="K117" t="n">
+        <v>798.4400000000001</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 79.5, need 80), TQ_FAIL(got 68.6, need 73), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NITCO.NS</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>NITCO</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="E118" t="n">
+        <v>79.39</v>
+      </c>
+      <c r="F118" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G118" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="H118" t="n">
+        <v>112.71</v>
+      </c>
+      <c r="I118" t="n">
+        <v>104.48</v>
+      </c>
+      <c r="J118" t="n">
+        <v>127.07</v>
+      </c>
+      <c r="K118" t="n">
+        <v>141.44</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 79.4, need 80), TQ_FAIL(got 66.2, need 73), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>GNA.NS</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>GNA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="E119" t="n">
+        <v>79.33</v>
+      </c>
+      <c r="F119" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H119" t="n">
+        <v>469.75</v>
+      </c>
+      <c r="I119" t="n">
+        <v>406.46</v>
+      </c>
+      <c r="J119" t="n">
+        <v>522.37</v>
+      </c>
+      <c r="K119" t="n">
+        <v>574.99</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 79.3, need 80), TQ_FAIL(got 64.6, need 73), RR_FAIL(got 1.59, need 2.0), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>AADHARHFC.NS</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AADHARHFC</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>68</v>
+      </c>
+      <c r="E120" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="F120" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H120" t="n">
+        <v>545.8</v>
+      </c>
+      <c r="I120" t="n">
+        <v>486.56</v>
+      </c>
+      <c r="J120" t="n">
+        <v>590.23</v>
+      </c>
+      <c r="K120" t="n">
+        <v>634.66</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="P120" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 79.2, need 80), TQ_FAIL(got 63.3, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>PAISALO.NS</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PAISALO</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="E121" t="n">
+        <v>79.145</v>
+      </c>
+      <c r="F121" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G121" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H121" t="n">
+        <v>69.54000000000001</v>
+      </c>
+      <c r="I121" t="n">
+        <v>60.35</v>
+      </c>
+      <c r="J121" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="K121" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="P121" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH(2.43&gt;1.50)</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SOBHA.NS</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SOBHA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="E122" t="n">
+        <v>79.045</v>
+      </c>
+      <c r="F122" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H122" t="n">
+        <v>1454.2</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1366.23</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1543.88</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1633.56</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(4.2%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>MOREPENLAB.NS</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>MOREPENLAB</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>66</v>
+      </c>
+      <c r="E123" t="n">
+        <v>79.01000000000001</v>
+      </c>
+      <c r="F123" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H123" t="n">
+        <v>61.19</v>
+      </c>
+      <c r="I123" t="n">
+        <v>52.01</v>
+      </c>
+      <c r="J123" t="n">
+        <v>68.06999999999999</v>
+      </c>
+      <c r="K123" t="n">
+        <v>74.95999999999999</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(6.2%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>AKUMS.NS</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AKUMS</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="E124" t="n">
+        <v>78.98999999999999</v>
+      </c>
+      <c r="F124" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H124" t="n">
+        <v>649.85</v>
+      </c>
+      <c r="I124" t="n">
+        <v>601.72</v>
+      </c>
+      <c r="J124" t="n">
+        <v>689.8200000000001</v>
+      </c>
+      <c r="K124" t="n">
+        <v>729.78</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>HEALTHCARE</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(8.4%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>INDHOTEL.NS</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="E125" t="n">
+        <v>78.72</v>
+      </c>
+      <c r="F125" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="G125" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H125" t="n">
+        <v>745.95</v>
+      </c>
+      <c r="I125" t="n">
+        <v>697.59</v>
+      </c>
+      <c r="J125" t="n">
+        <v>779.22</v>
+      </c>
+      <c r="K125" t="n">
+        <v>818.49</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 78.7, need 80), TQ_FAIL(got 70.5, need 73), RR_FAIL(got 1.39, need 2.0), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SCODATUBES.NS</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SCODATUBES</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>78.65000000000001</v>
+      </c>
+      <c r="F126" t="n">
+        <v>67</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H126" t="n">
+        <v>150.7</v>
+      </c>
+      <c r="I126" t="n">
+        <v>141.59</v>
+      </c>
+      <c r="J126" t="n">
+        <v>162.86</v>
+      </c>
+      <c r="K126" t="n">
+        <v>175.03</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>14.37</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 78.7, need 80), TQ_FAIL(got 67.0, need 73), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>TIRUPATIFL.NS</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>TIRUPATIFL</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="E127" t="n">
+        <v>78.62</v>
+      </c>
+      <c r="F127" t="n">
+        <v>52</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H127" t="n">
+        <v>70.22</v>
+      </c>
+      <c r="I127" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="J127" t="n">
+        <v>80.45999999999999</v>
+      </c>
+      <c r="K127" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(5.2%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>NYKAA.NS</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="E128" t="n">
+        <v>78.44499999999999</v>
+      </c>
+      <c r="F128" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H128" t="n">
+        <v>315.2</v>
+      </c>
+      <c r="I128" t="n">
+        <v>298.65</v>
+      </c>
+      <c r="J128" t="n">
+        <v>333.46</v>
+      </c>
+      <c r="K128" t="n">
+        <v>351.71</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 78.4, need 80), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>IKS.NS</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>IKS</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>71</v>
+      </c>
+      <c r="E129" t="n">
+        <v>78.34</v>
+      </c>
+      <c r="F129" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H129" t="n">
+        <v>1890.5</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1708.65</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2020.39</v>
+      </c>
+      <c r="K129" t="n">
+        <v>2163.27</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>HEALTHCARE</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 78.3, need 80), RR_FAIL(got 1.40, need 2.0), SECTOR_RANK_TOO_LOW(rank=18&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SOUTHBANK.NS</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SOUTHBANK</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="E130" t="n">
+        <v>78.25</v>
+      </c>
+      <c r="F130" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H130" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="I130" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="J130" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="K130" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 78.2, need 80), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>OPTIEMUS.NS</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>OPTIEMUS</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="E131" t="n">
+        <v>78.18000000000001</v>
+      </c>
+      <c r="F131" t="n">
+        <v>60</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H131" t="n">
+        <v>520.8</v>
+      </c>
+      <c r="I131" t="n">
+        <v>448.75</v>
+      </c>
+      <c r="J131" t="n">
+        <v>574.84</v>
+      </c>
+      <c r="K131" t="n">
+        <v>628.87</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(9.2%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>VENUSPIPES.NS</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>VENUSPIPES</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="E132" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="F132" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="G132" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H132" t="n">
+        <v>1845.4</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1637.27</v>
+      </c>
+      <c r="J132" t="n">
+        <v>2001.5</v>
+      </c>
+      <c r="K132" t="n">
+        <v>2157.6</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>BUILDING_MAT</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 78.2, need 80), TQ_FAIL(got 70.8, need 73), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=16&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>DELHIVERY.NS</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="F133" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H133" t="n">
+        <v>517.9</v>
+      </c>
+      <c r="I133" t="n">
+        <v>461.65</v>
+      </c>
+      <c r="J133" t="n">
+        <v>558.08</v>
+      </c>
+      <c r="K133" t="n">
+        <v>602.28</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>LOGISTICS</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(1.9%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SUVEN.NS</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SUVEN</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>69</v>
+      </c>
+      <c r="E134" t="n">
+        <v>78.045</v>
+      </c>
+      <c r="F134" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H134" t="n">
+        <v>319.35</v>
+      </c>
+      <c r="I134" t="n">
+        <v>271.45</v>
+      </c>
+      <c r="J134" t="n">
+        <v>357.96</v>
+      </c>
+      <c r="K134" t="n">
+        <v>396.57</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>-78.8</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 78.0, need 80), TQ_FAIL(got 67.3, need 73), RR_FAIL(got 1.56, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>NIACL.NS</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>NIACL</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="E135" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="F135" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G135" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="H135" t="n">
+        <v>185</v>
+      </c>
+      <c r="I135" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="J135" t="n">
+        <v>210.46</v>
+      </c>
+      <c r="K135" t="n">
+        <v>235.92</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(4.4%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CDSL.NS</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CDSL</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E136" t="n">
+        <v>77.73999999999999</v>
+      </c>
+      <c r="F136" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H136" t="n">
+        <v>1360</v>
+      </c>
+      <c r="I136" t="n">
+        <v>1288.62</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1431.44</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1502.88</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 77.7, need 80), TQ_FAIL(got 65.8, need 73), RR_FAIL(got 1.84, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>RITES.NS</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>RITES</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>77.72499999999999</v>
+      </c>
+      <c r="F137" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H137" t="n">
+        <v>235.43</v>
+      </c>
+      <c r="I137" t="n">
+        <v>202.42</v>
+      </c>
+      <c r="J137" t="n">
+        <v>259.39</v>
+      </c>
+      <c r="K137" t="n">
+        <v>284.95</v>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 77.7, need 80), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>RELTD.NS</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>RELTD</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="E138" t="n">
+        <v>77.67</v>
+      </c>
+      <c r="F138" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H138" t="n">
+        <v>183.08</v>
+      </c>
+      <c r="I138" t="n">
+        <v>156.3</v>
+      </c>
+      <c r="J138" t="n">
+        <v>207.74</v>
+      </c>
+      <c r="K138" t="n">
+        <v>232.4</v>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="P138" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH(3.66&gt;1.50)</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>JTLIND.NS</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>JTLIND</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>75</v>
+      </c>
+      <c r="E139" t="n">
+        <v>77.52</v>
+      </c>
+      <c r="F139" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="G139" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="H139" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="I139" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="J139" t="n">
+        <v>91.44</v>
+      </c>
+      <c r="K139" t="n">
+        <v>100.44</v>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>METALS</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>7.28</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(7.3%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>PICCADIL.NS</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PICCADIL</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="E140" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="F140" t="n">
+        <v>64</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H140" t="n">
+        <v>659.45</v>
+      </c>
+      <c r="I140" t="n">
+        <v>593.41</v>
+      </c>
+      <c r="J140" t="n">
+        <v>706.62</v>
+      </c>
+      <c r="K140" t="n">
+        <v>758.51</v>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 77.5, need 80), TQ_FAIL(got 64.0, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>GODREJPROP.NS</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="E141" t="n">
+        <v>77.485</v>
+      </c>
+      <c r="F141" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H141" t="n">
+        <v>2043.1</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1879.65</v>
+      </c>
+      <c r="J141" t="n">
+        <v>2159.15</v>
+      </c>
+      <c r="K141" t="n">
+        <v>2288.27</v>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 77.5, need 80), TQ_FAIL(got 69.9, need 73), RR_FAIL(got 1.41, need 2.0)</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>TQ_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>RAYMONDREL.NS</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>RAYMONDREL</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>75</v>
+      </c>
+      <c r="E142" t="n">
+        <v>77.43000000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="G142" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H142" t="n">
+        <v>671.95</v>
+      </c>
+      <c r="I142" t="n">
+        <v>612.0700000000001</v>
+      </c>
+      <c r="J142" t="n">
+        <v>746.03</v>
+      </c>
+      <c r="K142" t="n">
+        <v>820.11</v>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 77.4, need 80), TQ_FAIL(got 70.2, need 73), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>RISHABH.NS</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>RISHABH</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="E143" t="n">
+        <v>77</v>
+      </c>
+      <c r="F143" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H143" t="n">
+        <v>629.6</v>
+      </c>
+      <c r="I143" t="n">
+        <v>557.5</v>
+      </c>
+      <c r="J143" t="n">
+        <v>694.1799999999999</v>
+      </c>
+      <c r="K143" t="n">
+        <v>758.77</v>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>12</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 77.0, need 80), TQ_FAIL(got 60.7, need 73), RR_FAIL(got 1.70, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PNCINFRA.NS</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>PNCINFRA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="E144" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="F144" t="n">
+        <v>61</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H144" t="n">
+        <v>239.44</v>
+      </c>
+      <c r="I144" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="J144" t="n">
+        <v>255.85</v>
+      </c>
+      <c r="K144" t="n">
+        <v>272.26</v>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>7</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(7.0%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>IOLCP.NS</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>IOLCP</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="E145" t="n">
+        <v>76.70999999999999</v>
+      </c>
+      <c r="F145" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H145" t="n">
+        <v>165.04</v>
+      </c>
+      <c r="I145" t="n">
+        <v>140.28</v>
+      </c>
+      <c r="J145" t="n">
+        <v>183.61</v>
+      </c>
+      <c r="K145" t="n">
+        <v>202.18</v>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>HEALTHCARE</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(8.4%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>TBZ.NS</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>TBZ</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="E146" t="n">
+        <v>76.62</v>
+      </c>
+      <c r="F146" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G146" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H146" t="n">
+        <v>198.71</v>
+      </c>
+      <c r="I146" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="J146" t="n">
+        <v>216.94</v>
+      </c>
+      <c r="K146" t="n">
+        <v>235.17</v>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="P146" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 76.6, need 80), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>POONAWALLA.NS</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="E147" t="n">
+        <v>76.62</v>
+      </c>
+      <c r="F147" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H147" t="n">
+        <v>471.75</v>
+      </c>
+      <c r="I147" t="n">
+        <v>420.25</v>
+      </c>
+      <c r="J147" t="n">
+        <v>508.54</v>
+      </c>
+      <c r="K147" t="n">
+        <v>549</v>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="P147" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(5.9%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB.NS</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="E148" t="n">
+        <v>76.61499999999999</v>
+      </c>
+      <c r="F148" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H148" t="n">
+        <v>215.15</v>
+      </c>
+      <c r="I148" t="n">
+        <v>191.82</v>
+      </c>
+      <c r="J148" t="n">
+        <v>237.62</v>
+      </c>
+      <c r="K148" t="n">
+        <v>260.09</v>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(3.9%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>MANAPPURAM.NS</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="E149" t="n">
+        <v>76.56999999999999</v>
+      </c>
+      <c r="F149" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H149" t="n">
+        <v>342.1</v>
+      </c>
+      <c r="I149" t="n">
+        <v>307.8</v>
+      </c>
+      <c r="J149" t="n">
+        <v>367.83</v>
+      </c>
+      <c r="K149" t="n">
+        <v>393.55</v>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="P149" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(7.0%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>INDUSINDBK.NS</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="E150" t="n">
+        <v>76.56</v>
+      </c>
+      <c r="F150" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H150" t="n">
+        <v>1022.25</v>
+      </c>
+      <c r="I150" t="n">
+        <v>939.62</v>
+      </c>
+      <c r="J150" t="n">
+        <v>1081.27</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1146.2</v>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>BANKING</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(1.4%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>PSPPROJECT.NS</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>PSPPROJECT</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="E151" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="F151" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H151" t="n">
+        <v>1071.3</v>
+      </c>
+      <c r="I151" t="n">
+        <v>955.25</v>
+      </c>
+      <c r="J151" t="n">
+        <v>1174.01</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1276.73</v>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="P151" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(4.5%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>WEWORK.NS</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>WEWORK</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="E152" t="n">
+        <v>76.39</v>
+      </c>
+      <c r="F152" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H152" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="I152" t="n">
+        <v>629.4400000000001</v>
+      </c>
+      <c r="J152" t="n">
+        <v>814.6900000000001</v>
+      </c>
+      <c r="K152" t="n">
+        <v>899.59</v>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="P152" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH(18.55&gt;1.50)</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>RAMCOSYS.NS</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>RAMCOSYS</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="E153" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="F153" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H153" t="n">
+        <v>880.05</v>
+      </c>
+      <c r="I153" t="n">
+        <v>748.04</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1012.58</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1145.1</v>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>18</v>
+      </c>
+      <c r="P153" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 76.4, need 80), TQ_FAIL(got 51.4, need 73), RR_FAIL(got 1.95, need 2.0), INSTITUTIONAL_EXIT</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>TQ_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>PWL.NS</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>PWL</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="E154" t="n">
+        <v>76.33499999999999</v>
+      </c>
+      <c r="F154" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H154" t="n">
+        <v>148.78</v>
+      </c>
+      <c r="I154" t="n">
+        <v>126.46</v>
+      </c>
+      <c r="J154" t="n">
+        <v>165.52</v>
+      </c>
+      <c r="K154" t="n">
+        <v>182.26</v>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 76.3, need 80), TQ_FAIL(got 62.4, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SPARC.NS</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>SPARC</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="E155" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="F155" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H155" t="n">
+        <v>266.34</v>
+      </c>
+      <c r="I155" t="n">
+        <v>226.39</v>
+      </c>
+      <c r="J155" t="n">
+        <v>295.22</v>
+      </c>
+      <c r="K155" t="n">
+        <v>326.26</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>279</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 75.8, need 80), TQ_FAIL(got 65.3, need 73), RR_FAIL(got 1.45, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6), INSTITUTIONAL_EXIT</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>TRIVENI.NS</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>TRIVENI</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="E156" t="n">
+        <v>75.53</v>
+      </c>
+      <c r="F156" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H156" t="n">
+        <v>459.1</v>
+      </c>
+      <c r="I156" t="n">
+        <v>405.61</v>
+      </c>
+      <c r="J156" t="n">
+        <v>499.22</v>
+      </c>
+      <c r="K156" t="n">
+        <v>539.34</v>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(8.7%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SATIN.NS</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SATIN</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="E157" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F157" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H157" t="n">
+        <v>263.29</v>
+      </c>
+      <c r="I157" t="n">
+        <v>228.35</v>
+      </c>
+      <c r="J157" t="n">
+        <v>288.25</v>
+      </c>
+      <c r="K157" t="n">
+        <v>315.7</v>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="P157" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH(3.83&gt;1.50)</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>CUPID.NS</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>CUPID</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="E158" t="n">
+        <v>74.93000000000001</v>
+      </c>
+      <c r="F158" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="G158" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H158" t="n">
+        <v>221.11</v>
+      </c>
+      <c r="I158" t="n">
+        <v>196.79</v>
+      </c>
+      <c r="J158" t="n">
+        <v>238.48</v>
+      </c>
+      <c r="K158" t="n">
+        <v>257.59</v>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 74.9, need 80), TQ_FAIL(got 61.4, need 73), RR_FAIL(got 1.44, need 2.0), SUSPECT_PUMP_LOW_DELIVERY</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>TQ_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>GEMAROMA.NS</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>GEMAROMA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E159" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="F159" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="G159" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H159" t="n">
+        <v>194.02</v>
+      </c>
+      <c r="I159" t="n">
+        <v>176.12</v>
+      </c>
+      <c r="J159" t="n">
+        <v>212.96</v>
+      </c>
+      <c r="K159" t="n">
+        <v>231.9</v>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>METALS</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="P159" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(0.4%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>BHARATSE.NS</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>BHARATSE</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="E160" t="n">
+        <v>74.67</v>
+      </c>
+      <c r="F160" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="G160" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H160" t="n">
+        <v>234.81</v>
+      </c>
+      <c r="I160" t="n">
+        <v>199.59</v>
+      </c>
+      <c r="J160" t="n">
+        <v>262.17</v>
+      </c>
+      <c r="K160" t="n">
+        <v>289.53</v>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 74.7, need 80), TQ_FAIL(got 62.1, need 73), RR_FAIL(got 1.49, need 2.0), SECTOR_RANK_TOO_LOW(rank=8&gt;top6), INSTITUTIONAL_EXIT</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SPANDANA.NS</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SPANDANA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="E161" t="n">
+        <v>74.45</v>
+      </c>
+      <c r="F161" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G161" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H161" t="n">
+        <v>296.55</v>
+      </c>
+      <c r="I161" t="n">
+        <v>255.28</v>
+      </c>
+      <c r="J161" t="n">
+        <v>326.03</v>
+      </c>
+      <c r="K161" t="n">
+        <v>358.46</v>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>-29.4</v>
+      </c>
+      <c r="P161" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH(1.85&gt;1.50)</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>TEXRAIL.NS</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>TEXRAIL</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="E162" t="n">
+        <v>74.28</v>
+      </c>
+      <c r="F162" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G162" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H162" t="n">
+        <v>118.77</v>
+      </c>
+      <c r="I162" t="n">
+        <v>106.47</v>
+      </c>
+      <c r="J162" t="n">
+        <v>128</v>
+      </c>
+      <c r="K162" t="n">
+        <v>137.22</v>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(7.6%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>COMSYN.NS</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>COMSYN</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="E163" t="n">
+        <v>73.81999999999999</v>
+      </c>
+      <c r="F163" t="n">
+        <v>59</v>
+      </c>
+      <c r="G163" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H163" t="n">
+        <v>191.86</v>
+      </c>
+      <c r="I163" t="n">
+        <v>163.08</v>
+      </c>
+      <c r="J163" t="n">
+        <v>221.56</v>
+      </c>
+      <c r="K163" t="n">
+        <v>251.25</v>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 73.8, need 80), TQ_FAIL(got 59.0, need 73), RR_FAIL(got 1.99, need 2.0), SECTOR_RANK_TOO_LOW(rank=8&gt;top6), INSTITUTIONAL_EXIT</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>MAHLIFE.NS</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>MAHLIFE</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="E164" t="n">
+        <v>73.65000000000001</v>
+      </c>
+      <c r="F164" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="G164" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H164" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="I164" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="J164" t="n">
+        <v>391.44</v>
+      </c>
+      <c r="K164" t="n">
+        <v>411.99</v>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(9.9%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>IBULLSLTD.NS</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>IBULLSLTD</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="E165" t="n">
+        <v>71.81</v>
+      </c>
+      <c r="F165" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H165" t="n">
+        <v>29.05</v>
+      </c>
+      <c r="I165" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="J165" t="n">
+        <v>32.15</v>
+      </c>
+      <c r="K165" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 71.8, need 80), TQ_FAIL(got 53.4, need 73), RR_FAIL(got 1.49, need 2.0)</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>TQ_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>NUVAMA.NS</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E166" t="n">
+        <v>71.08</v>
+      </c>
+      <c r="F166" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H166" t="n">
+        <v>1917.1</v>
+      </c>
+      <c r="I166" t="n">
+        <v>1726.9</v>
+      </c>
+      <c r="J166" t="n">
+        <v>2052.96</v>
+      </c>
+      <c r="K166" t="n">
+        <v>2202.4</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="P166" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH(2.82&gt;1.50)</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>ASKAUTOLTD.NS</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ASKAUTOLTD</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="E167" t="n">
+        <v>66.94000000000001</v>
+      </c>
+      <c r="F167" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="G167" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H167" t="n">
+        <v>467.95</v>
+      </c>
+      <c r="I167" t="n">
+        <v>438.8</v>
+      </c>
+      <c r="J167" t="n">
+        <v>497.74</v>
+      </c>
+      <c r="K167" t="n">
+        <v>527.54</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 66.9, need 80), RR_FAIL(got 1.78, need 2.0), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>IXIGO.NS</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>IXIGO</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="E168" t="n">
+        <v>66.45</v>
+      </c>
+      <c r="F168" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H168" t="n">
+        <v>213.58</v>
+      </c>
+      <c r="I168" t="n">
+        <v>184.92</v>
+      </c>
+      <c r="J168" t="n">
+        <v>234.05</v>
+      </c>
+      <c r="K168" t="n">
+        <v>256.57</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(5.5%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>BANSALWIRE.NS</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>BANSALWIRE</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="E169" t="n">
+        <v>64.98999999999999</v>
+      </c>
+      <c r="F169" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="G169" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H169" t="n">
+        <v>354.15</v>
+      </c>
+      <c r="I169" t="n">
+        <v>310.44</v>
+      </c>
+      <c r="J169" t="n">
+        <v>386.93</v>
+      </c>
+      <c r="K169" t="n">
+        <v>419.71</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>METALS</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 65.0, need 80), TQ_FAIL(got 63.9, need 73), RR_FAIL(got 1.39, need 2.0), SECTOR_RANK_TOO_LOW(rank=13&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ESAFSFB.NS</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ESAFSFB</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="E170" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="F170" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="G170" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H170" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="I170" t="n">
+        <v>31.52</v>
+      </c>
+      <c r="J170" t="n">
+        <v>38.17</v>
+      </c>
+      <c r="K170" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>-8.91</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 63.3, need 80), TQ_FAIL(got 65.6, need 73), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>BLUEJET.NS</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>BLUEJET</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="E171" t="n">
+        <v>63.03</v>
+      </c>
+      <c r="F171" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H171" t="n">
+        <v>579.15</v>
+      </c>
+      <c r="I171" t="n">
+        <v>506.31</v>
+      </c>
+      <c r="J171" t="n">
+        <v>633.12</v>
+      </c>
+      <c r="K171" t="n">
+        <v>688.41</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 63.0, need 80), TQ_FAIL(got 72.9, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=15&gt;top6), SUSPECT_PUMP_LOW_DELIVERY</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CGCL.NS</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>CGCL</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="E172" t="n">
+        <v>60.21</v>
+      </c>
+      <c r="F172" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H172" t="n">
+        <v>237.47</v>
+      </c>
+      <c r="I172" t="n">
+        <v>214.17</v>
+      </c>
+      <c r="J172" t="n">
+        <v>254.78</v>
+      </c>
+      <c r="K172" t="n">
+        <v>272.42</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="P172" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 60.2, need 80), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>CARTRADE.NS</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>CARTRADE</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>61</v>
+      </c>
+      <c r="E173" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="F173" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="G173" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H173" t="n">
+        <v>2783.4</v>
+      </c>
+      <c r="I173" t="n">
+        <v>2568.39</v>
+      </c>
+      <c r="J173" t="n">
+        <v>3028.25</v>
+      </c>
+      <c r="K173" t="n">
+        <v>3273.1</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(9.7%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD.NS</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="E174" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="F174" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H174" t="n">
+        <v>2075.1</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1884.33</v>
+      </c>
+      <c r="J174" t="n">
+        <v>2211.37</v>
+      </c>
+      <c r="K174" t="n">
+        <v>2361.26</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_DOWN, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 59.0, need 80), TQ_FAIL(got 70.7, need 73), RR_FAIL(got 1.42, need 2.0)</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>TQ_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY.NS</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>59</v>
+      </c>
+      <c r="E175" t="n">
+        <v>58.74</v>
+      </c>
+      <c r="F175" t="n">
+        <v>69</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H175" t="n">
+        <v>1906.4</v>
+      </c>
+      <c r="I175" t="n">
+        <v>1741.28</v>
+      </c>
+      <c r="J175" t="n">
+        <v>2024.35</v>
+      </c>
+      <c r="K175" t="n">
+        <v>2154.08</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 58.7, need 80), TQ_FAIL(got 69.0, need 73), RR_FAIL(got 1.42, need 2.0)</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>TQ_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>PAYTM.NS</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="E176" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="F176" t="n">
+        <v>75</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H176" t="n">
+        <v>1246</v>
+      </c>
+      <c r="I176" t="n">
+        <v>1134.6</v>
+      </c>
+      <c r="J176" t="n">
+        <v>1325.57</v>
+      </c>
+      <c r="K176" t="n">
+        <v>1413.1</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(4.7%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>TITAN.NS</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="E177" t="n">
+        <v>58.065</v>
+      </c>
+      <c r="F177" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H177" t="n">
+        <v>4604.2</v>
+      </c>
+      <c r="I177" t="n">
+        <v>4235.86</v>
+      </c>
+      <c r="J177" t="n">
+        <v>4825.45</v>
+      </c>
+      <c r="K177" t="n">
+        <v>5156.71</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="P177" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH(1.95&gt;1.50)</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>CHOICEIN.NS</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CHOICEIN</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="E178" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="F178" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H178" t="n">
+        <v>778.15</v>
+      </c>
+      <c r="I178" t="n">
+        <v>712.9</v>
+      </c>
+      <c r="J178" t="n">
+        <v>824.76</v>
+      </c>
+      <c r="K178" t="n">
+        <v>876.02</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 57.4, need 80), TQ_FAIL(got 64.1, need 73), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>BAJFINANCE.NS</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="E179" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="F179" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H179" t="n">
+        <v>1042.5</v>
+      </c>
+      <c r="I179" t="n">
+        <v>959.1</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1096.91</v>
+      </c>
+      <c r="K179" t="n">
+        <v>1167.6</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="P179" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, DISTRIBUTION</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 57.2, need 80), TQ_FAIL(got 66.4, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>HOMEFIRST.NS</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>HOMEFIRST</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="E180" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="F180" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H180" t="n">
+        <v>1209.7</v>
+      </c>
+      <c r="I180" t="n">
+        <v>1121.66</v>
+      </c>
+      <c r="J180" t="n">
+        <v>1303.14</v>
+      </c>
+      <c r="K180" t="n">
+        <v>1396.58</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="P180" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 56.9, need 80), TQ_FAIL(got 60.9, need 73), RR_FAIL(got 1.96, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>HUHTAMAKI.NS</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>HUHTAMAKI</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="E181" t="n">
+        <v>56.93</v>
+      </c>
+      <c r="F181" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H181" t="n">
+        <v>213.23</v>
+      </c>
+      <c r="I181" t="n">
+        <v>190.93</v>
+      </c>
+      <c r="J181" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="K181" t="n">
+        <v>246.68</v>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="O181" t="n">
+        <v>13</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 56.9, need 80), TQ_FAIL(got 58.3, need 73), RR_FAIL(got 1.30, need 2.0), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>CHOLAFIN.NS</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="E182" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="F182" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="G182" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H182" t="n">
+        <v>1853.4</v>
+      </c>
+      <c r="I182" t="n">
+        <v>1712.39</v>
+      </c>
+      <c r="J182" t="n">
+        <v>1947.74</v>
+      </c>
+      <c r="K182" t="n">
+        <v>2064.92</v>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="P182" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 56.7, need 80), TQ_FAIL(got 70.3, need 73), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>ITCHOTELS.NS</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>ITCHOTELS</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="E183" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="F183" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="G183" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H183" t="n">
+        <v>186.79</v>
+      </c>
+      <c r="I183" t="n">
+        <v>172.04</v>
+      </c>
+      <c r="J183" t="n">
+        <v>199.98</v>
+      </c>
+      <c r="K183" t="n">
+        <v>213.18</v>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(7.8%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SGFIN.NS</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SGFIN</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="E184" t="n">
+        <v>54.605</v>
+      </c>
+      <c r="F184" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="G184" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H184" t="n">
+        <v>675.3</v>
+      </c>
+      <c r="I184" t="n">
+        <v>586.14</v>
+      </c>
+      <c r="J184" t="n">
+        <v>738.99</v>
+      </c>
+      <c r="K184" t="n">
+        <v>809.04</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="P184" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 54.6, need 80), TQ_FAIL(got 57.9, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>EMIL.NS</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>EMIL</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>56</v>
+      </c>
+      <c r="E185" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="F185" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H185" t="n">
+        <v>133.71</v>
+      </c>
+      <c r="I185" t="n">
+        <v>115.23</v>
+      </c>
+      <c r="J185" t="n">
+        <v>147.57</v>
+      </c>
+      <c r="K185" t="n">
+        <v>161.43</v>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P185" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(6.5%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>FUSION.NS</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>FUSION</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="E186" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="F186" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H186" t="n">
+        <v>226.02</v>
+      </c>
+      <c r="I186" t="n">
+        <v>192.12</v>
+      </c>
+      <c r="J186" t="n">
+        <v>251.44</v>
+      </c>
+      <c r="K186" t="n">
+        <v>276.87</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P186" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(0.7%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ABCAPITAL.NS</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="E187" t="n">
+        <v>54.275</v>
+      </c>
+      <c r="F187" t="n">
+        <v>62</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H187" t="n">
+        <v>405.4</v>
+      </c>
+      <c r="I187" t="n">
+        <v>379.94</v>
+      </c>
+      <c r="J187" t="n">
+        <v>426.42</v>
+      </c>
+      <c r="K187" t="n">
+        <v>447.43</v>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="P187" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 54.3, need 80), TQ_FAIL(got 62.0, need 73), RR_FAIL(got 1.53, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ABREL.NS</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ABREL</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E188" t="n">
+        <v>54.205</v>
+      </c>
+      <c r="F188" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H188" t="n">
+        <v>1409.8</v>
+      </c>
+      <c r="I188" t="n">
+        <v>1282.06</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1516.64</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1623.49</v>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="P188" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH(1.52&gt;1.50)</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>DE_TOO_HIGH</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>FILATEX.NS</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>FILATEX</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="E189" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="F189" t="n">
+        <v>64</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H189" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="I189" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="J189" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="K189" t="n">
+        <v>67.39</v>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 52.9, need 80), TQ_FAIL(got 64.0, need 73), RR_FAIL(got 1.37, need 2.0), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>LTF.NS</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="E190" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="F190" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H190" t="n">
+        <v>334.2</v>
+      </c>
+      <c r="I190" t="n">
+        <v>304.26</v>
+      </c>
+      <c r="J190" t="n">
+        <v>355.58</v>
+      </c>
+      <c r="K190" t="n">
+        <v>379.11</v>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="P190" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 52.7, need 80), TQ_FAIL(got 61.2, need 73), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6), EVENT_BLOCK_RESULTS_IN_3D, INSTITUTIONAL_EXIT</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>JAYBARMARU.NS</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>JAYBARMARU</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="E191" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="F191" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H191" t="n">
+        <v>187.6</v>
+      </c>
+      <c r="I191" t="n">
+        <v>159.46</v>
+      </c>
+      <c r="J191" t="n">
+        <v>208.7</v>
+      </c>
+      <c r="K191" t="n">
+        <v>229.81</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 46.0, need 80), TQ_FAIL(got 59.7, need 73), RR_FAIL(got 1.44, need 2.0), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>LODHA.NS</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="E192" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="F192" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H192" t="n">
+        <v>1102.55</v>
+      </c>
+      <c r="I192" t="n">
+        <v>997.2</v>
+      </c>
+      <c r="J192" t="n">
+        <v>1177.8</v>
+      </c>
+      <c r="K192" t="n">
+        <v>1260.57</v>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 45.9, need 80), TQ_FAIL(got 61.3, need 73), RR_FAIL(got 1.43, need 2.0)</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>TQ_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>IRISDOREME.NS</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>IRISDOREME</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="E193" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="F193" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H193" t="n">
+        <v>45.02</v>
+      </c>
+      <c r="I193" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="J193" t="n">
+        <v>50.26</v>
+      </c>
+      <c r="K193" t="n">
+        <v>55.51</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 44.4, need 80), TQ_FAIL(got 67.3, need 73), RR_FAIL(got 1.42, need 2.0), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>PRESTIGE.NS</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="E194" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="F194" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H194" t="n">
+        <v>1673.3</v>
+      </c>
+      <c r="I194" t="n">
+        <v>1508.9</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1790.73</v>
+      </c>
+      <c r="K194" t="n">
+        <v>1919.9</v>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>REALTY</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>7.54</v>
+      </c>
+      <c r="P194" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_DOWN, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(7.5%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>ANANDRATHI.NS</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="E195" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="F195" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H195" t="n">
+        <v>2052</v>
+      </c>
+      <c r="I195" t="n">
+        <v>1838.76</v>
+      </c>
+      <c r="J195" t="n">
+        <v>2211.93</v>
+      </c>
+      <c r="K195" t="n">
+        <v>2371.86</v>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 43.5, need 80), TQ_FAIL(got 63.3, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ETERNAL.NS</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="E196" t="n">
+        <v>43.42</v>
+      </c>
+      <c r="F196" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H196" t="n">
+        <v>289.4</v>
+      </c>
+      <c r="I196" t="n">
+        <v>264.6</v>
+      </c>
+      <c r="J196" t="n">
+        <v>307.11</v>
+      </c>
+      <c r="K196" t="n">
+        <v>326.6</v>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(1.2%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>DHANBANK.NS</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>DHANBANK</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="E197" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="F197" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H197" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="I197" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="J197" t="n">
+        <v>39.86</v>
+      </c>
+      <c r="K197" t="n">
+        <v>43.84</v>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(7.2%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>GABRIEL.NS</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>GABRIEL</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="E198" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="F198" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="G198" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H198" t="n">
+        <v>1266.4</v>
+      </c>
+      <c r="I198" t="n">
+        <v>1190.42</v>
+      </c>
+      <c r="J198" t="n">
+        <v>1373.71</v>
+      </c>
+      <c r="K198" t="n">
+        <v>1481.02</v>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 43.2, need 80), TQ_FAIL(got 64.2, need 73), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>JTEKTINDIA.NS</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>JTEKTINDIA</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>53</v>
+      </c>
+      <c r="E199" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="G199" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H199" t="n">
+        <v>144.74</v>
+      </c>
+      <c r="I199" t="n">
+        <v>131.44</v>
+      </c>
+      <c r="J199" t="n">
+        <v>159.16</v>
+      </c>
+      <c r="K199" t="n">
+        <v>173.57</v>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 42.1, need 80), TQ_FAIL(got 61.2, need 73), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>CUB.NS</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>CUB</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>50</v>
+      </c>
+      <c r="E200" t="n">
+        <v>41.98</v>
+      </c>
+      <c r="F200" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H200" t="n">
+        <v>227.97</v>
+      </c>
+      <c r="I200" t="n">
+        <v>204.21</v>
+      </c>
+      <c r="J200" t="n">
+        <v>244.94</v>
+      </c>
+      <c r="K200" t="n">
+        <v>263.61</v>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N200" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="P200" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>UPTREND</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 42.0, need 80), TQ_FAIL(got 64.8, need 73), RR_FAIL(got 1.43, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN.NS</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="E201" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="F201" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H201" t="n">
+        <v>1066.8</v>
+      </c>
+      <c r="I201" t="n">
+        <v>981.46</v>
+      </c>
+      <c r="J201" t="n">
+        <v>1123.07</v>
+      </c>
+      <c r="K201" t="n">
+        <v>1194.81</v>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="P201" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 41.3, need 80), RR_FAIL(got 1.41, need 2.0), SECTOR_RANK_TOO_LOW(rank=7&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL.NS</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>GHCLTEXTIL</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="E202" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="F202" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H202" t="n">
+        <v>110.72</v>
+      </c>
+      <c r="I202" t="n">
+        <v>95.48999999999999</v>
+      </c>
+      <c r="J202" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="K202" t="n">
+        <v>133.56</v>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(4.8%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>GANECOS.NS</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>GANECOS</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="E203" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="F203" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H203" t="n">
+        <v>1101.6</v>
+      </c>
+      <c r="I203" t="n">
+        <v>969.3200000000001</v>
+      </c>
+      <c r="J203" t="n">
+        <v>1196.08</v>
+      </c>
+      <c r="K203" t="n">
+        <v>1300.02</v>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW(3.1%&lt;10%)</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>ROE_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>AEQUS.NS</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>AEQUS</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="E204" t="n">
+        <v>40.905</v>
+      </c>
+      <c r="F204" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="G204" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H204" t="n">
+        <v>242.43</v>
+      </c>
+      <c r="I204" t="n">
+        <v>221.89</v>
+      </c>
+      <c r="J204" t="n">
+        <v>273.8</v>
+      </c>
+      <c r="K204" t="n">
+        <v>305.18</v>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N204" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="n">
+        <v>-9.99</v>
+      </c>
+      <c r="P204" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 40.9, need 80), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>COSMOFIRST.NS</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>COSMOFIRST</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="E205" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="F205" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H205" t="n">
+        <v>852.95</v>
+      </c>
+      <c r="I205" t="n">
+        <v>777.64</v>
+      </c>
+      <c r="J205" t="n">
+        <v>915.66</v>
+      </c>
+      <c r="K205" t="n">
+        <v>978.36</v>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>CONSUMER</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N205" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="P205" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 40.1, need 80), TQ_FAIL(got 68.9, need 73), RR_FAIL(got 1.55, need 2.0), SECTOR_RANK_TOO_LOW(rank=8&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>WABAG.NS</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>WABAG</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="E206" t="n">
+        <v>38.83</v>
+      </c>
+      <c r="F206" t="n">
+        <v>63</v>
+      </c>
+      <c r="G206" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H206" t="n">
+        <v>2203.2</v>
+      </c>
+      <c r="I206" t="n">
+        <v>1975.08</v>
+      </c>
+      <c r="J206" t="n">
+        <v>2438.36</v>
+      </c>
+      <c r="K206" t="n">
+        <v>2673.51</v>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="P206" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, NEAR_52W_HIGH, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 38.8, need 80), TQ_FAIL(got 63.0, need 73), RR_FAIL(got 1.98, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6)</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>OMAXE.NS</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>OMAXE</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="E207" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="F207" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="G207" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H207" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="I207" t="n">
+        <v>76.59</v>
+      </c>
+      <c r="J207" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="K207" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>DIVERSIFIED</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N207" t="n">
+        <v>0</v>
+      </c>
+      <c r="O207" t="n">
+        <v>0</v>
+      </c>
+      <c r="P207" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_DOWN, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>CONF_FAIL(got 37.6, need 80), TQ_FAIL(got 70.1, need 73), RR_FAIL(got 1.92, need 2.0), SECTOR_RANK_TOO_LOW(rank=11&gt;top6), INSTITUTIONAL_EXIT</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>SECTOR_RANK_TOO_LOW</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>63MOONS.NS</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>63MOONS</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H208" t="n">
+        <v>712.65</v>
+      </c>
+      <c r="I208" t="n">
+        <v>646.75</v>
+      </c>
+      <c r="J208" t="n">
+        <v>763.3</v>
+      </c>
+      <c r="K208" t="n">
+        <v>813.96</v>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>FINANCE</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>SIDEWAYS</t>
+        </is>
+      </c>
+      <c r="N208" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="P208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>VOL_SURGE_UP, VOL_SURGE, UPTREND, ACCUMULATION</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>BLACK_SWAN_NEWS</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
@@ -27588,7 +37181,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>

--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -1,30 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Tracking" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rejected" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Performance Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence Analysis" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TQ Analysis" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opp Score Analysis" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector Analysis" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regime Analysis" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Report" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekday Analysis" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holding Period Analysis" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Comparison" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conf x TQ Matrix" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalyst Analysis" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fail Reason Analysis" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regime x Sector" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Confidence Trajectory" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Recommendations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily Tracking" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Rejected" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Performance Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Confidence Analysis" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="TQ Analysis" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Opp Score Analysis" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sector Analysis" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Regime Analysis" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Monthly Report" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Weekday Analysis" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Holding Period Analysis" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Category Comparison" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Conf x TQ Matrix" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Catalyst Analysis" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Fail Reason Analysis" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Regime x Sector" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Confidence Trajectory" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Portfolio Risk" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Benchmark" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Equity Curve" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -657,6 +660,138 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Portfolio-level Risk Snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Open Positions</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Active Runners</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Exposure %</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Avg Return% (open)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Std Return% (open)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Worst Open Return %</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VaR-95 (1-day, %)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-08 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>── Top-5 Positions by symbol ──</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Days Held</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Return %</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -750,6 +885,258 @@
       <c r="Q1" t="inlineStr">
         <is>
           <t>Status</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Strategy vs Benchmark (1Y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Benchmark symbol</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>^NSEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>^NSEI 1Y return %</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-6.43</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Strategy avg return % (closed)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Alpha (strategy − benchmark)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>✓ Strong alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-08 11:01</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Equity Curve &amp; Risk-Adjusted Return</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Starting capital (₹)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Ending capital (₹)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total P&amp;L (₹)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total P&amp;L %</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Trades counted</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Avg trade return %</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Std trade return %</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sharpe (annualised)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sortino (annualised)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Max drawdown %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Position size % used</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-08 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Trade Return %</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>P&amp;L (₹)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Equity (₹)</t>
         </is>
       </c>
     </row>
@@ -10480,7 +10867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10492,6 +10879,168 @@
       <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total Tracked</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Runners Active</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Win Rate %</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Avg Return %</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Avg Win %</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Avg Loss %</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Avg Runner Ret%</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Avg T2-Exit Ret%</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Avg Max Gain %</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Avg Max DD %</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T1 Hit Rate %</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T2 Hit Rate %</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Stop Hit Rate %</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-08 11:01</t>
         </is>
       </c>
     </row>

--- a/recommendation_tracker.xlsx
+++ b/recommendation_tracker.xlsx
@@ -676,6 +676,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -754,10 +755,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-08 11:01</t>
-        </is>
-      </c>
-    </row>
+          <t>2026-07-09 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -909,6 +912,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -928,7 +932,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-6.43</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="5">
@@ -948,7 +952,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.43</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="7">
@@ -971,7 +975,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-08 11:01</t>
+          <t>2026-07-09 11:01</t>
         </is>
       </c>
     </row>
@@ -996,6 +1000,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1114,10 +1119,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-08 11:01</t>
-        </is>
-      </c>
-    </row>
+          <t>2026-07-09 11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -11040,7 +11047,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-08 11:01</t>
+          <t>2026-07-09 11:01</t>
         </is>
       </c>
     </row>
